--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/be-her/1869436845</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/other-side/1867923704</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/shadows/1875373696</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E93" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L94"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Always Everywhere</v>
+        <v>Casual Lady</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
+        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-16</v>
@@ -451,36 +451,36 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Wuthering Heights</v>
+        <v>Casual Lady - Single</v>
       </c>
       <c r="G2" t="str">
-        <v>3:03</v>
+        <v>3:14</v>
       </c>
       <c r="H2" t="str">
-        <v>Charli xcx</v>
+        <v>flowerovlove</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/always-everywhere/1852566184</v>
+        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
       </c>
       <c r="L2" t="str">
-        <v>Always Everywhere - Charli xcx</v>
+        <v>Casual Lady - flowerovlove</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Be Her</v>
+        <v>Always Everywhere</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://music.apple.com/us/song/be-her/1869436845</v>
+        <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-16</v>
@@ -489,36 +489,36 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>Dandelion</v>
+        <v>Wuthering Heights</v>
       </c>
       <c r="G3" t="str">
-        <v>3:37</v>
+        <v>3:03</v>
       </c>
       <c r="H3" t="str">
-        <v>Ella Langley</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="K3" t="str">
-        <v>https://music.apple.com/us/album/be-her/1869436835</v>
+        <v>https://music.apple.com/us/album/always-everywhere/1852566184</v>
       </c>
       <c r="L3" t="str">
-        <v>Be Her - Ella Langley</v>
+        <v>Always Everywhere - Charli xcx</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>other side.</v>
+        <v>Be Her</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>https://music.apple.com/us/song/other-side/1867923704</v>
+        <v>https://music.apple.com/us/song/be-her/1869436845</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-16</v>
@@ -527,36 +527,36 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>Icon</v>
+        <v>Dandelion</v>
       </c>
       <c r="G4" t="str">
-        <v>3:15</v>
+        <v>3:37</v>
       </c>
       <c r="H4" t="str">
-        <v>Brent Faiyaz</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K4" t="str">
-        <v>https://music.apple.com/us/album/other-side/1867923697</v>
+        <v>https://music.apple.com/us/album/be-her/1869436835</v>
       </c>
       <c r="L4" t="str">
-        <v>other side. - Brent Faiyaz</v>
+        <v>Be Her - Ella Langley</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SHADOWS</v>
+        <v>other side.</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/shadows/1875373696</v>
+        <v>https://music.apple.com/us/song/other-side/1867923704</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-16</v>
@@ -565,36 +565,36 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>SHADOWS - Single</v>
+        <v>Icon</v>
       </c>
       <c r="G5" t="str">
-        <v>3:22</v>
+        <v>3:15</v>
       </c>
       <c r="H5" t="str">
-        <v>John Summit</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/shadows/1875373695</v>
+        <v>https://music.apple.com/us/album/other-side/1867923697</v>
       </c>
       <c r="L5" t="str">
-        <v>SHADOWS - John Summit</v>
+        <v>other side. - Brent Faiyaz</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Mention Me (From The Movie "GOAT")</v>
+        <v>SHADOWS</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
+        <v>https://music.apple.com/us/song/shadows/1875373696</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-16</v>
@@ -603,36 +603,36 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>SHADOWS - Single</v>
       </c>
       <c r="G6" t="str">
-        <v>3:00</v>
+        <v>3:22</v>
       </c>
       <c r="H6" t="str">
-        <v>CORTIS</v>
+        <v>John Summit</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/shadows/1875373695</v>
       </c>
       <c r="L6" t="str">
-        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
+        <v>SHADOWS - John Summit</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>I Had a Dream She Took My Hand</v>
+        <v>Mention Me (From The Movie "GOAT")</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
+        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-16</v>
@@ -641,36 +641,36 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>Trying Times</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G7" t="str">
-        <v>3:40</v>
+        <v>3:00</v>
       </c>
       <c r="H7" t="str">
-        <v>James Blake</v>
+        <v>CORTIS</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
+        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L7" t="str">
-        <v>I Had a Dream She Took My Hand - James Blake</v>
+        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Let Me</v>
+        <v>I Had a Dream She Took My Hand</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/let-me/1874386210</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-16</v>
@@ -679,36 +679,36 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>Let Me - Single</v>
+        <v>Trying Times</v>
       </c>
       <c r="G8" t="str">
-        <v>4:51</v>
+        <v>3:40</v>
       </c>
       <c r="H8" t="str">
-        <v>Victoria Monét</v>
+        <v>James Blake</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/let-me/1874386209</v>
+        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
       </c>
       <c r="L8" t="str">
-        <v>Let Me - Victoria Monét</v>
+        <v>I Had a Dream She Took My Hand - James Blake</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Woman In Love</v>
+        <v>Let Me</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
+        <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-16</v>
@@ -717,36 +717,36 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Woman In Love - Single</v>
+        <v>Let Me - Single</v>
       </c>
       <c r="G9" t="str">
-        <v>2:43</v>
+        <v>4:51</v>
       </c>
       <c r="H9" t="str">
-        <v>Perrie</v>
+        <v>Victoria Monét</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
+        <v>https://music.apple.com/us/album/let-me/1874386209</v>
       </c>
       <c r="L9" t="str">
-        <v>Woman In Love - Perrie</v>
+        <v>Let Me - Victoria Monét</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
+        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-16</v>
@@ -755,36 +755,36 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love - Single</v>
       </c>
       <c r="G10" t="str">
-        <v>4:03</v>
+        <v>2:43</v>
       </c>
       <c r="H10" t="str">
-        <v>MUNA</v>
+        <v>Perrie</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
+        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
       </c>
       <c r="L10" t="str">
-        <v>Dancing On The Wall - MUNA</v>
+        <v>Woman In Love - Perrie</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Adrenaline (NO1 Ver.)</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
+        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-16</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>Adrenaline (Remix) - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G11" t="str">
-        <v>3:18</v>
+        <v>4:03</v>
       </c>
       <c r="H11" t="str">
-        <v>ATEEZ</v>
+        <v>MUNA</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
+        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
       </c>
       <c r="L11" t="str">
-        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
+        <v>Dancing On The Wall - MUNA</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ICEMAN FREESTYLE</v>
+        <v>Adrenaline (NO1 Ver.)</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
+        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-16</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>ICEMAN FREESTYLE - Single</v>
+        <v>Adrenaline (Remix) - Single</v>
       </c>
       <c r="G12" t="str">
-        <v>3:06</v>
+        <v>3:18</v>
       </c>
       <c r="H12" t="str">
-        <v>Central Cee</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
+        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
       </c>
       <c r="L12" t="str">
-        <v>ICEMAN FREESTYLE - Central Cee</v>
+        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Mírame Baby</v>
+        <v>ICEMAN FREESTYLE</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
+        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-16</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Mírame Baby - Single</v>
+        <v>ICEMAN FREESTYLE - Single</v>
       </c>
       <c r="G13" t="str">
-        <v>3:59</v>
+        <v>3:06</v>
       </c>
       <c r="H13" t="str">
-        <v>Arcángel</v>
+        <v>Central Cee</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
+        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
       </c>
       <c r="L13" t="str">
-        <v>Mírame Baby - Arcángel</v>
+        <v>ICEMAN FREESTYLE - Central Cee</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Lights Burn Dimmer</v>
+        <v>Mírame Baby</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
+        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-16</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Lights Burn Dimmer - Single</v>
+        <v>Mírame Baby - Single</v>
       </c>
       <c r="G14" t="str">
-        <v>4:20</v>
+        <v>3:59</v>
       </c>
       <c r="H14" t="str">
-        <v>Fred again..</v>
+        <v>Arcángel</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
+        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
       </c>
       <c r="L14" t="str">
-        <v>Lights Burn Dimmer - Fred again..</v>
+        <v>Mírame Baby - Arcángel</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Two Hearts</v>
+        <v>Lights Burn Dimmer</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
+        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-16</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Cerulean</v>
+        <v>Lights Burn Dimmer - Single</v>
       </c>
       <c r="G15" t="str">
-        <v>3:52</v>
+        <v>4:20</v>
       </c>
       <c r="H15" t="str">
-        <v>Danny L Harle</v>
+        <v>Fred again..</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
+        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
       </c>
       <c r="L15" t="str">
-        <v>Two Hearts - Danny L Harle</v>
+        <v>Lights Burn Dimmer - Fred again..</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Be By You</v>
+        <v>Two Hearts</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
+        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-16</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>The Way I Am</v>
+        <v>Cerulean</v>
       </c>
       <c r="G16" t="str">
-        <v>3:17</v>
+        <v>3:52</v>
       </c>
       <c r="H16" t="str">
-        <v>Luke Combs</v>
+        <v>Danny L Harle</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
+        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
       </c>
       <c r="L16" t="str">
-        <v>Be By You - Luke Combs</v>
+        <v>Two Hearts - Danny L Harle</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>you and forever</v>
+        <v>Be By You</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
+        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-16</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>everyone for ten minutes</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G17" t="str">
-        <v>3:54</v>
+        <v>3:17</v>
       </c>
       <c r="H17" t="str">
-        <v>Bleachers</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
+        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
       </c>
       <c r="L17" t="str">
-        <v>you and forever - Bleachers</v>
+        <v>Be By You - Luke Combs</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ROOMS</v>
+        <v>you and forever</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/rooms/1874675856</v>
+        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-16</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>ROOMS - Single</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G18" t="str">
-        <v>3:52</v>
+        <v>3:54</v>
       </c>
       <c r="H18" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Bleachers</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/rooms/1874675853</v>
+        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
       </c>
       <c r="L18" t="str">
-        <v>ROOMS - Mike WiLL Made-It</v>
+        <v>you and forever - Bleachers</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>I Just Might (Austin Millz Remix)</v>
+        <v>ROOMS</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
+        <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-16</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>I Just Might (Austin Millz Remix) - Single</v>
+        <v>ROOMS - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>3:16</v>
+        <v>3:52</v>
       </c>
       <c r="H19" t="str">
-        <v>Bruno Mars</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
+        <v>https://music.apple.com/us/album/rooms/1874675853</v>
       </c>
       <c r="L19" t="str">
-        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
+        <v>ROOMS - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>MI$ LLAMADA$</v>
+        <v>I Just Might (Austin Millz Remix)</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
+        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-16</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>DEPR&lt;/3$$ED MFKZ</v>
+        <v>I Just Might (Austin Millz Remix) - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>3:11</v>
+        <v>3:16</v>
       </c>
       <c r="H20" t="str">
-        <v>Junior H</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
+        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
       </c>
       <c r="L20" t="str">
-        <v>MI$ LLAMADA$ - Junior H</v>
+        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Con el Corazón</v>
+        <v>MI$ LLAMADA$</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
+        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-16</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Con el Corazón - Single</v>
+        <v>DEPR&lt;/3$$ED MFKZ</v>
       </c>
       <c r="G21" t="str">
-        <v>3:09</v>
+        <v>3:11</v>
       </c>
       <c r="H21" t="str">
-        <v>Maluma</v>
+        <v>Junior H</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
+        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
       </c>
       <c r="L21" t="str">
-        <v>Con el Corazón - Maluma</v>
+        <v>MI$ LLAMADA$ - Junior H</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Get In Girl</v>
+        <v>Con el Corazón</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
+        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-16</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Toy With Me</v>
+        <v>Con el Corazón - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>3:26</v>
+        <v>3:09</v>
       </c>
       <c r="H22" t="str">
-        <v>Meghan Trainor</v>
+        <v>Maluma</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
+        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
       </c>
       <c r="L22" t="str">
-        <v>Get In Girl - Meghan Trainor</v>
+        <v>Con el Corazón - Maluma</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>London Foolishly</v>
+        <v>Get In Girl</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
+        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-16</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Sunday Best (Deluxe)</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G23" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H23" t="str">
-        <v>Nick Jonas</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
+        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
       </c>
       <c r="L23" t="str">
-        <v>London Foolishly - Nick Jonas</v>
+        <v>Get In Girl - Meghan Trainor</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Thorns</v>
+        <v>London Foolishly</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/thorns/1875330576</v>
+        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-16</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Thorns - Single</v>
+        <v>Sunday Best (Deluxe)</v>
       </c>
       <c r="G24" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H24" t="str">
-        <v>Jelly Roll</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/thorns/1875330145</v>
+        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
       </c>
       <c r="L24" t="str">
-        <v>Thorns - Jelly Roll</v>
+        <v>London Foolishly - Nick Jonas</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Thinkin Bout You</v>
+        <v>Thorns</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
+        <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-16</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Honora</v>
+        <v>Thorns - Single</v>
       </c>
       <c r="G25" t="str">
-        <v>4:10</v>
+        <v>3:10</v>
       </c>
       <c r="H25" t="str">
-        <v>Flea</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
+        <v>https://music.apple.com/us/album/thorns/1875330145</v>
       </c>
       <c r="L25" t="str">
-        <v>Thinkin Bout You - Flea</v>
+        <v>Thorns - Jelly Roll</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>JUICY</v>
+        <v>Thinkin Bout You</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/juicy/1869398762</v>
+        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-16</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>JUICY - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G26" t="str">
-        <v>3:31</v>
+        <v>4:10</v>
       </c>
       <c r="H26" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Flea</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/juicy/1869398760</v>
+        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
       </c>
       <c r="L26" t="str">
-        <v>JUICY - Lenny Tavárez</v>
+        <v>Thinkin Bout You - Flea</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>All They Type</v>
+        <v>JUICY</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
+        <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-16</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>All They Type - Single</v>
+        <v>JUICY - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>2:52</v>
+        <v>3:31</v>
       </c>
       <c r="H27" t="str">
-        <v>Keke Palmer</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
+        <v>https://music.apple.com/us/album/juicy/1869398760</v>
       </c>
       <c r="L27" t="str">
-        <v>All They Type - Keke Palmer</v>
+        <v>JUICY - Lenny Tavárez</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>More Than A Lover</v>
+        <v>All They Type</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
+        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-16</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>More Than A Lover - Single</v>
+        <v>All They Type - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>4:05</v>
+        <v>2:52</v>
       </c>
       <c r="H28" t="str">
-        <v>Mary J. Blige</v>
+        <v>Keke Palmer</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
+        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
       </c>
       <c r="L28" t="str">
-        <v>More Than A Lover - Mary J. Blige</v>
+        <v>All They Type - Keke Palmer</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>City</v>
+        <v>More Than A Lover</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/city/1847721298</v>
+        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-16</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>My Lover</v>
+        <v>More Than A Lover - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>3:16</v>
+        <v>4:05</v>
       </c>
       <c r="H29" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/city/1847721296</v>
+        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
       </c>
       <c r="L29" t="str">
-        <v>City - Claire Rosinkranz</v>
+        <v>More Than A Lover - Mary J. Blige</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Eyes Closed</v>
+        <v>City</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
+        <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-16</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>My Lover</v>
       </c>
       <c r="G30" t="str">
-        <v>2:25</v>
+        <v>3:16</v>
       </c>
       <c r="H30" t="str">
-        <v>Mimi Webb</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
+        <v>https://music.apple.com/us/album/city/1847721296</v>
       </c>
       <c r="L30" t="str">
-        <v>Eyes Closed - Mimi Webb</v>
+        <v>City - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Go For Broke</v>
+        <v>Eyes Closed</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
+        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-16</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Go For Broke - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G31" t="str">
-        <v>2:50</v>
+        <v>2:25</v>
       </c>
       <c r="H31" t="str">
-        <v>Knox</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
+        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
       </c>
       <c r="L31" t="str">
-        <v>Go For Broke - Knox</v>
+        <v>Eyes Closed - Mimi Webb</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>somebody you're supposed to love</v>
+        <v>Go For Broke</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
+        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-16</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>THE ART OF BEING A MESS (DELUXE)</v>
+        <v>Go For Broke - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H32" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Knox</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
+        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
       </c>
       <c r="L32" t="str">
-        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
+        <v>Go For Broke - Knox</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Kentucky Too Long</v>
+        <v>somebody you're supposed to love</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
+        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-16</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Kentucky Too Long - Single</v>
+        <v>THE ART OF BEING A MESS (DELUXE)</v>
       </c>
       <c r="G33" t="str">
-        <v>3:38</v>
+        <v>3:10</v>
       </c>
       <c r="H33" t="str">
-        <v>Charley Crockett</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
+        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
       </c>
       <c r="L33" t="str">
-        <v>Kentucky Too Long - Charley Crockett</v>
+        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Somewhere Down in Georgia</v>
+        <v>Kentucky Too Long</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
+        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-16</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Somewhere Down in Georgia - Single</v>
+        <v>Kentucky Too Long - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H34" t="str">
-        <v>Mon Rovîa</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
+        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
       </c>
       <c r="L34" t="str">
-        <v>Somewhere Down in Georgia - Mon Rovîa</v>
+        <v>Kentucky Too Long - Charley Crockett</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>BANG BANG</v>
+        <v>Somewhere Down in Georgia</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
+        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-16</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>BANG BANG - Single</v>
+        <v>Somewhere Down in Georgia - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>2:58</v>
+        <v>2:57</v>
       </c>
       <c r="H35" t="str">
-        <v>IVE</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
+        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
       </c>
       <c r="L35" t="str">
-        <v>BANG BANG - IVE</v>
+        <v>Somewhere Down in Georgia - Mon Rovîa</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
+        <v>BANG BANG</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
+        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-16</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
+        <v>BANG BANG - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>3:15</v>
+        <v>2:58</v>
       </c>
       <c r="H36" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>IVE</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
+        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
       </c>
       <c r="L36" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
+        <v>BANG BANG - IVE</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
+        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-16</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>5:21</v>
+        <v>3:15</v>
       </c>
       <c r="H37" t="str">
-        <v>Don Broco</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
+        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
       </c>
       <c r="L37" t="str">
-        <v>Nightmare Tripping - Don Broco</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Hive Mind (feat. Denzel Curry)</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
+        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-16</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Single</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="G38" t="str">
-        <v>3:26</v>
+        <v>5:21</v>
       </c>
       <c r="H38" t="str">
-        <v>Knocked Loose</v>
+        <v>Don Broco</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
+        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
+        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
       </c>
       <c r="L38" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
+        <v>Nightmare Tripping - Don Broco</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>for your love</v>
+        <v>Hive Mind (feat. Denzel Curry)</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
+        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-16</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>for your love - Single</v>
+        <v>Hive Mind (feat. Denzel Curry) - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>3:05</v>
+        <v>3:26</v>
       </c>
       <c r="H39" t="str">
-        <v>Cruz Beckham</v>
+        <v>Knocked Loose</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
+        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
       </c>
       <c r="L39" t="str">
-        <v>for your love - Cruz Beckham</v>
+        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Somebody</v>
+        <v>for your love</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873193244</v>
+        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-16</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Somebody - Single</v>
+        <v>for your love - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>3:23</v>
+        <v>3:05</v>
       </c>
       <c r="H40" t="str">
-        <v>Jamie Foxx</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873193243</v>
+        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
       </c>
       <c r="L40" t="str">
-        <v>Somebody - Jamie Foxx</v>
+        <v>for your love - Cruz Beckham</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>BIG FEELING (NO MAKEUP)</v>
+        <v>Somebody</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
+        <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-16</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>BIG FEELING (NO MAKEUP) - Single</v>
+        <v>Somebody - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>1:55</v>
+        <v>3:23</v>
       </c>
       <c r="H41" t="str">
-        <v>BKTHERULA</v>
+        <v>Jamie Foxx</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
+        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
+        <v>https://music.apple.com/us/album/somebody/1873193243</v>
       </c>
       <c r="L41" t="str">
-        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
+        <v>Somebody - Jamie Foxx</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>On and On</v>
+        <v>BIG FEELING (NO MAKEUP)</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
+        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-16</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Work of Heart</v>
+        <v>BIG FEELING (NO MAKEUP) - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>3:43</v>
+        <v>1:55</v>
       </c>
       <c r="H42" t="str">
-        <v>Flatland Cavalry</v>
+        <v>BKTHERULA</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
+        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
       </c>
       <c r="L42" t="str">
-        <v>On and On - Flatland Cavalry</v>
+        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Push My Luck</v>
+        <v>On and On</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
+        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-16</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Push My Luck / All I Ever Need - EP</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G43" t="str">
-        <v>2:44</v>
+        <v>3:43</v>
       </c>
       <c r="H43" t="str">
-        <v>Cold War Kids</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
+        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
       </c>
       <c r="L43" t="str">
-        <v>Push My Luck - Cold War Kids</v>
+        <v>On and On - Flatland Cavalry</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Memphis Players</v>
+        <v>Push My Luck</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
+        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-16</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>AK Cuts: Vol. 2 - EP</v>
+        <v>Push My Luck / All I Ever Need - EP</v>
       </c>
       <c r="G44" t="str">
-        <v>2:46</v>
+        <v>2:44</v>
       </c>
       <c r="H44" t="str">
-        <v>Anish Kumar</v>
+        <v>Cold War Kids</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
+        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
       </c>
       <c r="L44" t="str">
-        <v>Memphis Players - Anish Kumar</v>
+        <v>Push My Luck - Cold War Kids</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Somebody</v>
+        <v>Memphis Players</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873982451</v>
+        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-16</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Blue Sky Mentality (Complete Edition)</v>
+        <v>AK Cuts: Vol. 2 - EP</v>
       </c>
       <c r="G45" t="str">
-        <v>2:49</v>
+        <v>2:46</v>
       </c>
       <c r="H45" t="str">
-        <v>Good Neighbours</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873982325</v>
+        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
       </c>
       <c r="L45" t="str">
-        <v>Somebody - Good Neighbours</v>
+        <v>Memphis Players - Anish Kumar</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>If I Didn't Know You</v>
+        <v>Somebody</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
+        <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-16</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>If I Didn't Know You - Single</v>
+        <v>Blue Sky Mentality (Complete Edition)</v>
       </c>
       <c r="G46" t="str">
-        <v>3:28</v>
+        <v>2:49</v>
       </c>
       <c r="H46" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Good Neighbours</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
+        <v>https://music.apple.com/us/album/somebody/1873982325</v>
       </c>
       <c r="L46" t="str">
-        <v>If I Didn't Know You - The Red Clay Strays</v>
+        <v>Somebody - Good Neighbours</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Seven Seas</v>
+        <v>If I Didn't Know You</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
+        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-16</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Seven Seas - Single</v>
+        <v>If I Didn't Know You - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>3:01</v>
+        <v>3:28</v>
       </c>
       <c r="H47" t="str">
-        <v>Dirty Heads</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
+        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
       </c>
       <c r="L47" t="str">
-        <v>Seven Seas - Dirty Heads</v>
+        <v>If I Didn't Know You - The Red Clay Strays</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>1000 Ways</v>
+        <v>Seven Seas</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
+        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-16</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>A Love For Strangers</v>
+        <v>Seven Seas - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>4:04</v>
+        <v>3:01</v>
       </c>
       <c r="H48" t="str">
-        <v>Chet Faker</v>
+        <v>Dirty Heads</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
+        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
       </c>
       <c r="L48" t="str">
-        <v>1000 Ways - Chet Faker</v>
+        <v>Seven Seas - Dirty Heads</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Beatback</v>
+        <v>1000 Ways</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/beatback/1861895138</v>
+        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-16</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Ö</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G49" t="str">
-        <v>2:19</v>
+        <v>4:04</v>
       </c>
       <c r="H49" t="str">
-        <v>Fcukers</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/beatback/1861895134</v>
+        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
       </c>
       <c r="L49" t="str">
-        <v>Beatback - Fcukers</v>
+        <v>1000 Ways - Chet Faker</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>GANG</v>
+        <v>Beatback</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/gang/1872243101</v>
+        <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-16</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>GANG - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G50" t="str">
-        <v>3:44</v>
+        <v>2:19</v>
       </c>
       <c r="H50" t="str">
-        <v>Tink</v>
+        <v>Fcukers</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/gang/1872243100</v>
+        <v>https://music.apple.com/us/album/beatback/1861895134</v>
       </c>
       <c r="L50" t="str">
-        <v>GANG - Tink</v>
+        <v>Beatback - Fcukers</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>a love song for u</v>
+        <v>GANG</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
+        <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-16</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>a love song for u - EP</v>
+        <v>GANG - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>1:40</v>
+        <v>3:44</v>
       </c>
       <c r="H51" t="str">
-        <v>Eem Triplin</v>
+        <v>Tink</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
+        <v>https://music.apple.com/us/album/gang/1872243100</v>
       </c>
       <c r="L51" t="str">
-        <v>a love song for u - Eem Triplin</v>
+        <v>GANG - Tink</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>See Through</v>
+        <v>a love song for u</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/see-through/1840712229</v>
+        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-16</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>A.R.S.O.N.</v>
+        <v>a love song for u - EP</v>
       </c>
       <c r="G52" t="str">
-        <v>2:38</v>
+        <v>1:40</v>
       </c>
       <c r="H52" t="str">
-        <v>Story of the Year</v>
+        <v>Eem Triplin</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
+        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/see-through/1840712224</v>
+        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
       </c>
       <c r="L52" t="str">
-        <v>See Through - Story of the Year</v>
+        <v>a love song for u - Eem Triplin</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>be the girl!</v>
+        <v>See Through</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
+        <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-16</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>the apple tree under the sea</v>
+        <v>A.R.S.O.N.</v>
       </c>
       <c r="G53" t="str">
-        <v>5:33</v>
+        <v>2:38</v>
       </c>
       <c r="H53" t="str">
-        <v>hemlocke springs</v>
+        <v>Story of the Year</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
+        <v>https://music.apple.com/us/album/see-through/1840712224</v>
       </c>
       <c r="L53" t="str">
-        <v>be the girl! - hemlocke springs</v>
+        <v>See Through - Story of the Year</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>be the girl!</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-16</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G54" t="str">
-        <v>3:33</v>
+        <v>5:33</v>
       </c>
       <c r="H54" t="str">
-        <v>Erin LeCount</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
       </c>
       <c r="L54" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>be the girl! - hemlocke springs</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-16</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>3:40</v>
+        <v>3:33</v>
       </c>
       <c r="H55" t="str">
-        <v>Kid Sistr</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L55" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ARCADE</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-16</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>ARCADE - Single</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>2:52</v>
+        <v>3:40</v>
       </c>
       <c r="H56" t="str">
-        <v>Deb Never</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L56" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Girls Just Wanna</v>
+        <v>ARCADE</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-16</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Girlhood - EP</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H57" t="str">
-        <v>Morgan St. Jean</v>
+        <v>Deb Never</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L57" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>you special.</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-16</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>you special. - Single</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G58" t="str">
-        <v>2:08</v>
+        <v>2:16</v>
       </c>
       <c r="H58" t="str">
-        <v>YFN Lucci</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L58" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Bass Dhol</v>
+        <v>you special.</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-16</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>3:38</v>
+        <v>2:08</v>
       </c>
       <c r="H59" t="str">
-        <v>Ahadadream</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L59" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-16</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>3:31</v>
+        <v>3:38</v>
       </c>
       <c r="H60" t="str">
-        <v>Charles Kelley</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L60" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>If I See Her Again</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-16</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>2:43</v>
+        <v>3:31</v>
       </c>
       <c r="H61" t="str">
-        <v>Maddox Batson</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L61" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-16</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Under The Sun</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H62" t="str">
-        <v>Sun-El Musician</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L62" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>To B Honest</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-16</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>To Whom This May Concern</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G63" t="str">
-        <v>4:30</v>
+        <v>4:43</v>
       </c>
       <c r="H63" t="str">
-        <v>Jill Scott</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L63" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>lil xan goes to washington</v>
+        <v>To B Honest</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-16</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>the beltway is burning</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G64" t="str">
-        <v>2:41</v>
+        <v>4:30</v>
       </c>
       <c r="H64" t="str">
-        <v>Ekko Astral</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L64" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Koneko</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-16</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Kurage - Single</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G65" t="str">
-        <v>4:08</v>
+        <v>2:41</v>
       </c>
       <c r="H65" t="str">
-        <v>Liana Flores</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L65" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Cupid's Call</v>
+        <v>Koneko</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-16</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>2:58</v>
+        <v>4:08</v>
       </c>
       <c r="H66" t="str">
-        <v>Dizzy Fae</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L66" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Come Back 2 Me</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-16</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>3:13</v>
+        <v>2:58</v>
       </c>
       <c r="H67" t="str">
-        <v>Chloé Caillet</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L67" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Pop Off</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-16</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Pop Off - Single</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>3:16</v>
+        <v>3:13</v>
       </c>
       <c r="H68" t="str">
-        <v>GRiZ</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L68" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>dreams</v>
+        <v>Pop Off</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-16</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>dreams - Single</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>3:31</v>
+        <v>3:16</v>
       </c>
       <c r="H69" t="str">
-        <v>Azzecca</v>
+        <v>GRiZ</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L69" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Love Hate Love</v>
+        <v>dreams</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-16</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>2:55</v>
+        <v>3:31</v>
       </c>
       <c r="H70" t="str">
-        <v>Owen Riegling</v>
+        <v>Azzecca</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L70" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Do It All Alone</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-16</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>2:52</v>
+        <v>2:55</v>
       </c>
       <c r="H71" t="str">
-        <v>Rend Collective</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L71" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>She Makes Me Real</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-16</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Masquerade</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>2:58</v>
+        <v>2:52</v>
       </c>
       <c r="H72" t="str">
-        <v>Cardinals</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L72" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Steady</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-16</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>Masquerade</v>
       </c>
       <c r="G73" t="str">
-        <v>3:26</v>
+        <v>2:58</v>
       </c>
       <c r="H73" t="str">
-        <v>Bella Kay</v>
+        <v>Cardinals</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L73" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>DIRTY TECH</v>
+        <v>Steady</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-16</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>PLAY ME</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:20</v>
+        <v>3:26</v>
       </c>
       <c r="H74" t="str">
-        <v>Kim Gordon</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L74" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Nada Más</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-16</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Nada Más - Single</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G75" t="str">
-        <v>2:19</v>
+        <v>2:20</v>
       </c>
       <c r="H75" t="str">
-        <v>Tombochio</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L75" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Friends Again</v>
+        <v>Nada Más</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-16</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Friends Again - Single</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>3:38</v>
+        <v>2:19</v>
       </c>
       <c r="H76" t="str">
-        <v>Baby Rose</v>
+        <v>Tombochio</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L76" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>W.T.A.</v>
+        <v>Friends Again</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-16</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>W.T.A. - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>3:22</v>
+        <v>3:38</v>
       </c>
       <c r="H77" t="str">
-        <v>Isaia Huron</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L77" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>desire.</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-16</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>November Scorpio</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:15</v>
+        <v>3:22</v>
       </c>
       <c r="H78" t="str">
-        <v>Tiana Major9</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L78" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>desire.</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-16</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G79" t="str">
-        <v>3:12</v>
+        <v>3:15</v>
       </c>
       <c r="H79" t="str">
-        <v>August Ponthier</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L79" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Killer Whale</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-16</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Killer Whale - Single</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G80" t="str">
-        <v>4:00</v>
+        <v>3:12</v>
       </c>
       <c r="H80" t="str">
-        <v>Hayden Everett</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L80" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Waits for Me</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-16</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>You’re Free to Go</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>2:46</v>
+        <v>4:00</v>
       </c>
       <c r="H81" t="str">
-        <v>Anjimile</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L81" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Man's World</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-16</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Mud Blood Bone</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G82" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H82" t="str">
-        <v>Cat Clyde</v>
+        <v>Anjimile</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L82" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>In the Middle of It</v>
+        <v>Man's World</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-16</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G83" t="str">
-        <v>3:13</v>
+        <v>2:42</v>
       </c>
       <c r="H83" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L83" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-16</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Fleeting - EP</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>2:51</v>
+        <v>3:13</v>
       </c>
       <c r="H84" t="str">
-        <v>Sarah Kinsley</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L84" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-16</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G85" t="str">
-        <v>5:23</v>
+        <v>2:51</v>
       </c>
       <c r="H85" t="str">
-        <v>BUNT.</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L85" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>I've Never Met Her</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-16</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:07</v>
+        <v>5:23</v>
       </c>
       <c r="H86" t="str">
-        <v>Ally Salort</v>
+        <v>BUNT.</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L86" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-16</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>The Elephant</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:28</v>
+        <v>3:07</v>
       </c>
       <c r="H87" t="str">
-        <v>Ledbyher</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L87" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Yes</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-16</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Just A Few Folk</v>
+        <v>The Elephant</v>
       </c>
       <c r="G88" t="str">
-        <v>3:21</v>
+        <v>3:28</v>
       </c>
       <c r="H88" t="str">
-        <v>JP Cooper</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L88" t="str">
-        <v>Yes - JP Cooper</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>CHOKEHOLD</v>
+        <v>Yes</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-16</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>CHOKEHOLD - Single</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G89" t="str">
-        <v>2:52</v>
+        <v>3:21</v>
       </c>
       <c r="H89" t="str">
-        <v>WesGhost</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L89" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Bad Faith</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-16</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Love Is Not Enough</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H90" t="str">
-        <v>Converge</v>
+        <v>WesGhost</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L90" t="str">
-        <v>Bad Faith - Converge</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Gimme Some Moore</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-16</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G91" t="str">
-        <v>4:00</v>
+        <v>2:48</v>
       </c>
       <c r="H91" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Converge</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L91" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Angel Eyes</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-16</v>
@@ -3871,68 +3871,106 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>God Forgives - Single</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G92" t="str">
-        <v>2:14</v>
+        <v>4:00</v>
       </c>
       <c r="H92" t="str">
-        <v>Guilt Trip</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L92" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
+        <v>Angel Eyes</v>
+      </c>
+      <c r="B93" t="str">
+        <v/>
+      </c>
+      <c r="C93" t="str">
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+      </c>
+      <c r="D93" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v>God Forgives - Single</v>
+      </c>
+      <c r="G93" t="str">
+        <v>2:14</v>
+      </c>
+      <c r="H93" t="str">
+        <v>Guilt Trip</v>
+      </c>
+      <c r="I93" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J93" t="str">
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+      </c>
+      <c r="K93" t="str">
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+      </c>
+      <c r="L93" t="str">
+        <v>Angel Eyes - Guilt Trip</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
         <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
-      <c r="B93" t="str">
-        <v/>
-      </c>
-      <c r="C93" t="str">
+      <c r="B94" t="str">
+        <v/>
+      </c>
+      <c r="C94" t="str">
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
-      <c r="D93" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E93" t="str">
-        <v/>
-      </c>
-      <c r="F93" t="str">
+      <c r="D94" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
         <v>Savage Imperial Death March</v>
       </c>
-      <c r="G93" t="str">
+      <c r="G94" t="str">
         <v>3:17</v>
       </c>
-      <c r="H93" t="str">
+      <c r="H94" t="str">
         <v>Melvins</v>
       </c>
-      <c r="I93" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J93" t="str">
+      <c r="I94" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J94" t="str">
         <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
-      <c r="K93" t="str">
+      <c r="K94" t="str">
         <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
-      <c r="L93" t="str">
+      <c r="L94" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L93"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L94"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/be-her/1869436845</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/other-side/1867923704</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/shadows/1875373696</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E94" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L95"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Casual Lady</v>
+        <v>Paracosm</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
+        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-17</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Casual Lady - Single</v>
+        <v>Paracosm</v>
       </c>
       <c r="G2" t="str">
-        <v>3:14</v>
+        <v>3:23</v>
       </c>
       <c r="H2" t="str">
-        <v>flowerovlove</v>
+        <v>Absolutely</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
+        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
+        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
       </c>
       <c r="L2" t="str">
-        <v>Casual Lady - flowerovlove</v>
+        <v>Paracosm - Absolutely</v>
       </c>
     </row>
     <row r="3">
@@ -664,13 +664,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>I Had a Dream She Took My Hand</v>
+        <v>Casual Lady</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
+        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-17</v>
@@ -679,36 +679,36 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>Trying Times</v>
+        <v>Casual Lady - Single</v>
       </c>
       <c r="G8" t="str">
-        <v>3:40</v>
+        <v>3:14</v>
       </c>
       <c r="H8" t="str">
-        <v>James Blake</v>
+        <v>flowerovlove</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
+        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
       </c>
       <c r="L8" t="str">
-        <v>I Had a Dream She Took My Hand - James Blake</v>
+        <v>Casual Lady - flowerovlove</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Let Me</v>
+        <v>I Had a Dream She Took My Hand</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/let-me/1874386210</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-17</v>
@@ -717,36 +717,36 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Let Me - Single</v>
+        <v>Trying Times</v>
       </c>
       <c r="G9" t="str">
-        <v>4:51</v>
+        <v>3:40</v>
       </c>
       <c r="H9" t="str">
-        <v>Victoria Monét</v>
+        <v>James Blake</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/let-me/1874386209</v>
+        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
       </c>
       <c r="L9" t="str">
-        <v>Let Me - Victoria Monét</v>
+        <v>I Had a Dream She Took My Hand - James Blake</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Woman In Love</v>
+        <v>Let Me</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
+        <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-17</v>
@@ -755,36 +755,36 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>Woman In Love - Single</v>
+        <v>Let Me - Single</v>
       </c>
       <c r="G10" t="str">
-        <v>2:43</v>
+        <v>4:51</v>
       </c>
       <c r="H10" t="str">
-        <v>Perrie</v>
+        <v>Victoria Monét</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
+        <v>https://music.apple.com/us/album/let-me/1874386209</v>
       </c>
       <c r="L10" t="str">
-        <v>Woman In Love - Perrie</v>
+        <v>Let Me - Victoria Monét</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
+        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-17</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love - Single</v>
       </c>
       <c r="G11" t="str">
-        <v>4:03</v>
+        <v>2:43</v>
       </c>
       <c r="H11" t="str">
-        <v>MUNA</v>
+        <v>Perrie</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
+        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
       </c>
       <c r="L11" t="str">
-        <v>Dancing On The Wall - MUNA</v>
+        <v>Woman In Love - Perrie</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Adrenaline (NO1 Ver.)</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
+        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-17</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>Adrenaline (Remix) - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G12" t="str">
-        <v>3:18</v>
+        <v>4:03</v>
       </c>
       <c r="H12" t="str">
-        <v>ATEEZ</v>
+        <v>MUNA</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
+        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
       </c>
       <c r="L12" t="str">
-        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
+        <v>Dancing On The Wall - MUNA</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ICEMAN FREESTYLE</v>
+        <v>Adrenaline (NO1 Ver.)</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
+        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-17</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>ICEMAN FREESTYLE - Single</v>
+        <v>Adrenaline (Remix) - Single</v>
       </c>
       <c r="G13" t="str">
-        <v>3:06</v>
+        <v>3:18</v>
       </c>
       <c r="H13" t="str">
-        <v>Central Cee</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
+        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
       </c>
       <c r="L13" t="str">
-        <v>ICEMAN FREESTYLE - Central Cee</v>
+        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Mírame Baby</v>
+        <v>ICEMAN FREESTYLE</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
+        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-17</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Mírame Baby - Single</v>
+        <v>ICEMAN FREESTYLE - Single</v>
       </c>
       <c r="G14" t="str">
-        <v>3:59</v>
+        <v>3:06</v>
       </c>
       <c r="H14" t="str">
-        <v>Arcángel</v>
+        <v>Central Cee</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
+        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
       </c>
       <c r="L14" t="str">
-        <v>Mírame Baby - Arcángel</v>
+        <v>ICEMAN FREESTYLE - Central Cee</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Lights Burn Dimmer</v>
+        <v>Mírame Baby</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
+        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-17</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Lights Burn Dimmer - Single</v>
+        <v>Mírame Baby - Single</v>
       </c>
       <c r="G15" t="str">
-        <v>4:20</v>
+        <v>3:59</v>
       </c>
       <c r="H15" t="str">
-        <v>Fred again..</v>
+        <v>Arcángel</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
+        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
       </c>
       <c r="L15" t="str">
-        <v>Lights Burn Dimmer - Fred again..</v>
+        <v>Mírame Baby - Arcángel</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Two Hearts</v>
+        <v>Lights Burn Dimmer</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
+        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-17</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Cerulean</v>
+        <v>Lights Burn Dimmer - Single</v>
       </c>
       <c r="G16" t="str">
-        <v>3:52</v>
+        <v>4:20</v>
       </c>
       <c r="H16" t="str">
-        <v>Danny L Harle</v>
+        <v>Fred again..</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
+        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
       </c>
       <c r="L16" t="str">
-        <v>Two Hearts - Danny L Harle</v>
+        <v>Lights Burn Dimmer - Fred again..</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Be By You</v>
+        <v>Two Hearts</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
+        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-17</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>The Way I Am</v>
+        <v>Cerulean</v>
       </c>
       <c r="G17" t="str">
-        <v>3:17</v>
+        <v>3:52</v>
       </c>
       <c r="H17" t="str">
-        <v>Luke Combs</v>
+        <v>Danny L Harle</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
+        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
       </c>
       <c r="L17" t="str">
-        <v>Be By You - Luke Combs</v>
+        <v>Two Hearts - Danny L Harle</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>you and forever</v>
+        <v>Be By You</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
+        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-17</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>everyone for ten minutes</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G18" t="str">
-        <v>3:54</v>
+        <v>3:17</v>
       </c>
       <c r="H18" t="str">
-        <v>Bleachers</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
+        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
       </c>
       <c r="L18" t="str">
-        <v>you and forever - Bleachers</v>
+        <v>Be By You - Luke Combs</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ROOMS</v>
+        <v>you and forever</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/rooms/1874675856</v>
+        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-17</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>ROOMS - Single</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G19" t="str">
-        <v>3:52</v>
+        <v>3:54</v>
       </c>
       <c r="H19" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Bleachers</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/rooms/1874675853</v>
+        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
       </c>
       <c r="L19" t="str">
-        <v>ROOMS - Mike WiLL Made-It</v>
+        <v>you and forever - Bleachers</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>I Just Might (Austin Millz Remix)</v>
+        <v>ROOMS</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
+        <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-17</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>I Just Might (Austin Millz Remix) - Single</v>
+        <v>ROOMS - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>3:16</v>
+        <v>3:52</v>
       </c>
       <c r="H20" t="str">
-        <v>Bruno Mars</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
+        <v>https://music.apple.com/us/album/rooms/1874675853</v>
       </c>
       <c r="L20" t="str">
-        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
+        <v>ROOMS - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>MI$ LLAMADA$</v>
+        <v>I Just Might (Austin Millz Remix)</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
+        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-17</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>DEPR&lt;/3$$ED MFKZ</v>
+        <v>I Just Might (Austin Millz Remix) - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>3:11</v>
+        <v>3:16</v>
       </c>
       <c r="H21" t="str">
-        <v>Junior H</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
+        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
       </c>
       <c r="L21" t="str">
-        <v>MI$ LLAMADA$ - Junior H</v>
+        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Con el Corazón</v>
+        <v>MI$ LLAMADA$</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
+        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-17</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Con el Corazón - Single</v>
+        <v>DEPR&lt;/3$$ED MFKZ</v>
       </c>
       <c r="G22" t="str">
-        <v>3:09</v>
+        <v>3:11</v>
       </c>
       <c r="H22" t="str">
-        <v>Maluma</v>
+        <v>Junior H</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
+        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
       </c>
       <c r="L22" t="str">
-        <v>Con el Corazón - Maluma</v>
+        <v>MI$ LLAMADA$ - Junior H</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Get In Girl</v>
+        <v>Con el Corazón</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
+        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-17</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Toy With Me</v>
+        <v>Con el Corazón - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>3:26</v>
+        <v>3:09</v>
       </c>
       <c r="H23" t="str">
-        <v>Meghan Trainor</v>
+        <v>Maluma</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
+        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
       </c>
       <c r="L23" t="str">
-        <v>Get In Girl - Meghan Trainor</v>
+        <v>Con el Corazón - Maluma</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>London Foolishly</v>
+        <v>Get In Girl</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
+        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-17</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Sunday Best (Deluxe)</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G24" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H24" t="str">
-        <v>Nick Jonas</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
+        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
       </c>
       <c r="L24" t="str">
-        <v>London Foolishly - Nick Jonas</v>
+        <v>Get In Girl - Meghan Trainor</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Thorns</v>
+        <v>London Foolishly</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/thorns/1875330576</v>
+        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-17</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Thorns - Single</v>
+        <v>Sunday Best (Deluxe)</v>
       </c>
       <c r="G25" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H25" t="str">
-        <v>Jelly Roll</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/thorns/1875330145</v>
+        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
       </c>
       <c r="L25" t="str">
-        <v>Thorns - Jelly Roll</v>
+        <v>London Foolishly - Nick Jonas</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Thinkin Bout You</v>
+        <v>Thorns</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
+        <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-17</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Honora</v>
+        <v>Thorns - Single</v>
       </c>
       <c r="G26" t="str">
-        <v>4:10</v>
+        <v>3:10</v>
       </c>
       <c r="H26" t="str">
-        <v>Flea</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
+        <v>https://music.apple.com/us/album/thorns/1875330145</v>
       </c>
       <c r="L26" t="str">
-        <v>Thinkin Bout You - Flea</v>
+        <v>Thorns - Jelly Roll</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>JUICY</v>
+        <v>Thinkin Bout You</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/juicy/1869398762</v>
+        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-17</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>JUICY - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G27" t="str">
-        <v>3:31</v>
+        <v>4:10</v>
       </c>
       <c r="H27" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Flea</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/juicy/1869398760</v>
+        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
       </c>
       <c r="L27" t="str">
-        <v>JUICY - Lenny Tavárez</v>
+        <v>Thinkin Bout You - Flea</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>All They Type</v>
+        <v>JUICY</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
+        <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-17</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>All They Type - Single</v>
+        <v>JUICY - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>2:52</v>
+        <v>3:31</v>
       </c>
       <c r="H28" t="str">
-        <v>Keke Palmer</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
+        <v>https://music.apple.com/us/album/juicy/1869398760</v>
       </c>
       <c r="L28" t="str">
-        <v>All They Type - Keke Palmer</v>
+        <v>JUICY - Lenny Tavárez</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>More Than A Lover</v>
+        <v>All They Type</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
+        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-17</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>More Than A Lover - Single</v>
+        <v>All They Type - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>4:05</v>
+        <v>2:52</v>
       </c>
       <c r="H29" t="str">
-        <v>Mary J. Blige</v>
+        <v>Keke Palmer</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
+        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
       </c>
       <c r="L29" t="str">
-        <v>More Than A Lover - Mary J. Blige</v>
+        <v>All They Type - Keke Palmer</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>City</v>
+        <v>More Than A Lover</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/city/1847721298</v>
+        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-17</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>My Lover</v>
+        <v>More Than A Lover - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>3:16</v>
+        <v>4:05</v>
       </c>
       <c r="H30" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/city/1847721296</v>
+        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
       </c>
       <c r="L30" t="str">
-        <v>City - Claire Rosinkranz</v>
+        <v>More Than A Lover - Mary J. Blige</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Eyes Closed</v>
+        <v>City</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
+        <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-17</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>My Lover</v>
       </c>
       <c r="G31" t="str">
-        <v>2:25</v>
+        <v>3:16</v>
       </c>
       <c r="H31" t="str">
-        <v>Mimi Webb</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
+        <v>https://music.apple.com/us/album/city/1847721296</v>
       </c>
       <c r="L31" t="str">
-        <v>Eyes Closed - Mimi Webb</v>
+        <v>City - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Go For Broke</v>
+        <v>Eyes Closed</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
+        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-17</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Go For Broke - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G32" t="str">
-        <v>2:50</v>
+        <v>2:25</v>
       </c>
       <c r="H32" t="str">
-        <v>Knox</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
+        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
       </c>
       <c r="L32" t="str">
-        <v>Go For Broke - Knox</v>
+        <v>Eyes Closed - Mimi Webb</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>somebody you're supposed to love</v>
+        <v>Go For Broke</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
+        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-17</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>THE ART OF BEING A MESS (DELUXE)</v>
+        <v>Go For Broke - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H33" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Knox</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
+        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
       </c>
       <c r="L33" t="str">
-        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
+        <v>Go For Broke - Knox</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Kentucky Too Long</v>
+        <v>somebody you're supposed to love</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
+        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-17</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Kentucky Too Long - Single</v>
+        <v>THE ART OF BEING A MESS (DELUXE)</v>
       </c>
       <c r="G34" t="str">
-        <v>3:38</v>
+        <v>3:10</v>
       </c>
       <c r="H34" t="str">
-        <v>Charley Crockett</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
+        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
       </c>
       <c r="L34" t="str">
-        <v>Kentucky Too Long - Charley Crockett</v>
+        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Somewhere Down in Georgia</v>
+        <v>Kentucky Too Long</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
+        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-17</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Somewhere Down in Georgia - Single</v>
+        <v>Kentucky Too Long - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H35" t="str">
-        <v>Mon Rovîa</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
+        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
       </c>
       <c r="L35" t="str">
-        <v>Somewhere Down in Georgia - Mon Rovîa</v>
+        <v>Kentucky Too Long - Charley Crockett</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>BANG BANG</v>
+        <v>Somewhere Down in Georgia</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
+        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-17</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>BANG BANG - Single</v>
+        <v>Somewhere Down in Georgia - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>2:58</v>
+        <v>2:57</v>
       </c>
       <c r="H36" t="str">
-        <v>IVE</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
+        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
       </c>
       <c r="L36" t="str">
-        <v>BANG BANG - IVE</v>
+        <v>Somewhere Down in Georgia - Mon Rovîa</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
+        <v>BANG BANG</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
+        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-17</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
+        <v>BANG BANG - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>3:15</v>
+        <v>2:58</v>
       </c>
       <c r="H37" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>IVE</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
+        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
       </c>
       <c r="L37" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
+        <v>BANG BANG - IVE</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
+        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-17</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>5:21</v>
+        <v>3:15</v>
       </c>
       <c r="H38" t="str">
-        <v>Don Broco</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
+        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
       </c>
       <c r="L38" t="str">
-        <v>Nightmare Tripping - Don Broco</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Hive Mind (feat. Denzel Curry)</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
+        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-17</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Single</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="G39" t="str">
-        <v>3:26</v>
+        <v>5:21</v>
       </c>
       <c r="H39" t="str">
-        <v>Knocked Loose</v>
+        <v>Don Broco</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
+        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
+        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
       </c>
       <c r="L39" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
+        <v>Nightmare Tripping - Don Broco</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>for your love</v>
+        <v>Hive Mind (feat. Denzel Curry)</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
+        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-17</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>for your love - Single</v>
+        <v>Hive Mind (feat. Denzel Curry) - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>3:05</v>
+        <v>3:26</v>
       </c>
       <c r="H40" t="str">
-        <v>Cruz Beckham</v>
+        <v>Knocked Loose</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
+        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
       </c>
       <c r="L40" t="str">
-        <v>for your love - Cruz Beckham</v>
+        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Somebody</v>
+        <v>for your love</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873193244</v>
+        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-17</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Somebody - Single</v>
+        <v>for your love - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>3:23</v>
+        <v>3:05</v>
       </c>
       <c r="H41" t="str">
-        <v>Jamie Foxx</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873193243</v>
+        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
       </c>
       <c r="L41" t="str">
-        <v>Somebody - Jamie Foxx</v>
+        <v>for your love - Cruz Beckham</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>BIG FEELING (NO MAKEUP)</v>
+        <v>Somebody</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
+        <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-17</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>BIG FEELING (NO MAKEUP) - Single</v>
+        <v>Somebody - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>1:55</v>
+        <v>3:23</v>
       </c>
       <c r="H42" t="str">
-        <v>BKTHERULA</v>
+        <v>Jamie Foxx</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
+        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
+        <v>https://music.apple.com/us/album/somebody/1873193243</v>
       </c>
       <c r="L42" t="str">
-        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
+        <v>Somebody - Jamie Foxx</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>On and On</v>
+        <v>BIG FEELING (NO MAKEUP)</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
+        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-17</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Work of Heart</v>
+        <v>BIG FEELING (NO MAKEUP) - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>3:43</v>
+        <v>1:55</v>
       </c>
       <c r="H43" t="str">
-        <v>Flatland Cavalry</v>
+        <v>BKTHERULA</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
+        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
       </c>
       <c r="L43" t="str">
-        <v>On and On - Flatland Cavalry</v>
+        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Push My Luck</v>
+        <v>On and On</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
+        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-17</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Push My Luck / All I Ever Need - EP</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G44" t="str">
-        <v>2:44</v>
+        <v>3:43</v>
       </c>
       <c r="H44" t="str">
-        <v>Cold War Kids</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
+        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
       </c>
       <c r="L44" t="str">
-        <v>Push My Luck - Cold War Kids</v>
+        <v>On and On - Flatland Cavalry</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Memphis Players</v>
+        <v>Push My Luck</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
+        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-17</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>AK Cuts: Vol. 2 - EP</v>
+        <v>Push My Luck / All I Ever Need - EP</v>
       </c>
       <c r="G45" t="str">
-        <v>2:46</v>
+        <v>2:44</v>
       </c>
       <c r="H45" t="str">
-        <v>Anish Kumar</v>
+        <v>Cold War Kids</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
+        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
       </c>
       <c r="L45" t="str">
-        <v>Memphis Players - Anish Kumar</v>
+        <v>Push My Luck - Cold War Kids</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Somebody</v>
+        <v>Memphis Players</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873982451</v>
+        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-17</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Blue Sky Mentality (Complete Edition)</v>
+        <v>AK Cuts: Vol. 2 - EP</v>
       </c>
       <c r="G46" t="str">
-        <v>2:49</v>
+        <v>2:46</v>
       </c>
       <c r="H46" t="str">
-        <v>Good Neighbours</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873982325</v>
+        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
       </c>
       <c r="L46" t="str">
-        <v>Somebody - Good Neighbours</v>
+        <v>Memphis Players - Anish Kumar</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>If I Didn't Know You</v>
+        <v>Somebody</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
+        <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-17</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>If I Didn't Know You - Single</v>
+        <v>Blue Sky Mentality (Complete Edition)</v>
       </c>
       <c r="G47" t="str">
-        <v>3:28</v>
+        <v>2:49</v>
       </c>
       <c r="H47" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Good Neighbours</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
+        <v>https://music.apple.com/us/album/somebody/1873982325</v>
       </c>
       <c r="L47" t="str">
-        <v>If I Didn't Know You - The Red Clay Strays</v>
+        <v>Somebody - Good Neighbours</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Seven Seas</v>
+        <v>If I Didn't Know You</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
+        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-17</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Seven Seas - Single</v>
+        <v>If I Didn't Know You - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>3:01</v>
+        <v>3:28</v>
       </c>
       <c r="H48" t="str">
-        <v>Dirty Heads</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
+        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
       </c>
       <c r="L48" t="str">
-        <v>Seven Seas - Dirty Heads</v>
+        <v>If I Didn't Know You - The Red Clay Strays</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>1000 Ways</v>
+        <v>Seven Seas</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
+        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-17</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>A Love For Strangers</v>
+        <v>Seven Seas - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>4:04</v>
+        <v>3:01</v>
       </c>
       <c r="H49" t="str">
-        <v>Chet Faker</v>
+        <v>Dirty Heads</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
+        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
       </c>
       <c r="L49" t="str">
-        <v>1000 Ways - Chet Faker</v>
+        <v>Seven Seas - Dirty Heads</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Beatback</v>
+        <v>1000 Ways</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/beatback/1861895138</v>
+        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-17</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Ö</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G50" t="str">
-        <v>2:19</v>
+        <v>4:04</v>
       </c>
       <c r="H50" t="str">
-        <v>Fcukers</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/beatback/1861895134</v>
+        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
       </c>
       <c r="L50" t="str">
-        <v>Beatback - Fcukers</v>
+        <v>1000 Ways - Chet Faker</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>GANG</v>
+        <v>Beatback</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/gang/1872243101</v>
+        <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-17</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>GANG - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G51" t="str">
-        <v>3:44</v>
+        <v>2:19</v>
       </c>
       <c r="H51" t="str">
-        <v>Tink</v>
+        <v>Fcukers</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/gang/1872243100</v>
+        <v>https://music.apple.com/us/album/beatback/1861895134</v>
       </c>
       <c r="L51" t="str">
-        <v>GANG - Tink</v>
+        <v>Beatback - Fcukers</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>a love song for u</v>
+        <v>GANG</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
+        <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-17</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>a love song for u - EP</v>
+        <v>GANG - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>1:40</v>
+        <v>3:44</v>
       </c>
       <c r="H52" t="str">
-        <v>Eem Triplin</v>
+        <v>Tink</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
+        <v>https://music.apple.com/us/album/gang/1872243100</v>
       </c>
       <c r="L52" t="str">
-        <v>a love song for u - Eem Triplin</v>
+        <v>GANG - Tink</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>See Through</v>
+        <v>a love song for u</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/see-through/1840712229</v>
+        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-17</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>A.R.S.O.N.</v>
+        <v>a love song for u - EP</v>
       </c>
       <c r="G53" t="str">
-        <v>2:38</v>
+        <v>1:40</v>
       </c>
       <c r="H53" t="str">
-        <v>Story of the Year</v>
+        <v>Eem Triplin</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
+        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/see-through/1840712224</v>
+        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
       </c>
       <c r="L53" t="str">
-        <v>See Through - Story of the Year</v>
+        <v>a love song for u - Eem Triplin</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>be the girl!</v>
+        <v>See Through</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
+        <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-17</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>the apple tree under the sea</v>
+        <v>A.R.S.O.N.</v>
       </c>
       <c r="G54" t="str">
-        <v>5:33</v>
+        <v>2:38</v>
       </c>
       <c r="H54" t="str">
-        <v>hemlocke springs</v>
+        <v>Story of the Year</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
+        <v>https://music.apple.com/us/album/see-through/1840712224</v>
       </c>
       <c r="L54" t="str">
-        <v>be the girl! - hemlocke springs</v>
+        <v>See Through - Story of the Year</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>be the girl!</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-17</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G55" t="str">
-        <v>3:33</v>
+        <v>5:33</v>
       </c>
       <c r="H55" t="str">
-        <v>Erin LeCount</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
       </c>
       <c r="L55" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>be the girl! - hemlocke springs</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-17</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>3:40</v>
+        <v>3:33</v>
       </c>
       <c r="H56" t="str">
-        <v>Kid Sistr</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L56" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ARCADE</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-17</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>ARCADE - Single</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>2:52</v>
+        <v>3:40</v>
       </c>
       <c r="H57" t="str">
-        <v>Deb Never</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L57" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Girls Just Wanna</v>
+        <v>ARCADE</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-17</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Girlhood - EP</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H58" t="str">
-        <v>Morgan St. Jean</v>
+        <v>Deb Never</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L58" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>you special.</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-17</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>you special. - Single</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G59" t="str">
-        <v>2:08</v>
+        <v>2:16</v>
       </c>
       <c r="H59" t="str">
-        <v>YFN Lucci</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L59" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Bass Dhol</v>
+        <v>you special.</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-17</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>3:38</v>
+        <v>2:08</v>
       </c>
       <c r="H60" t="str">
-        <v>Ahadadream</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L60" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-17</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>3:31</v>
+        <v>3:38</v>
       </c>
       <c r="H61" t="str">
-        <v>Charles Kelley</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L61" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>If I See Her Again</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-17</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>2:43</v>
+        <v>3:31</v>
       </c>
       <c r="H62" t="str">
-        <v>Maddox Batson</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L62" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-17</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Under The Sun</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H63" t="str">
-        <v>Sun-El Musician</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L63" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>To B Honest</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-17</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>To Whom This May Concern</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G64" t="str">
-        <v>4:30</v>
+        <v>4:43</v>
       </c>
       <c r="H64" t="str">
-        <v>Jill Scott</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L64" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>lil xan goes to washington</v>
+        <v>To B Honest</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-17</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>the beltway is burning</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G65" t="str">
-        <v>2:41</v>
+        <v>4:30</v>
       </c>
       <c r="H65" t="str">
-        <v>Ekko Astral</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L65" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Koneko</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-17</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Kurage - Single</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G66" t="str">
-        <v>4:08</v>
+        <v>2:41</v>
       </c>
       <c r="H66" t="str">
-        <v>Liana Flores</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L66" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Cupid's Call</v>
+        <v>Koneko</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-17</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>2:58</v>
+        <v>4:08</v>
       </c>
       <c r="H67" t="str">
-        <v>Dizzy Fae</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L67" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Come Back 2 Me</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-17</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>3:13</v>
+        <v>2:58</v>
       </c>
       <c r="H68" t="str">
-        <v>Chloé Caillet</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L68" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Pop Off</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-17</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Pop Off - Single</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>3:16</v>
+        <v>3:13</v>
       </c>
       <c r="H69" t="str">
-        <v>GRiZ</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L69" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>dreams</v>
+        <v>Pop Off</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-17</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>dreams - Single</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>3:31</v>
+        <v>3:16</v>
       </c>
       <c r="H70" t="str">
-        <v>Azzecca</v>
+        <v>GRiZ</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L70" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Love Hate Love</v>
+        <v>dreams</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-17</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>2:55</v>
+        <v>3:31</v>
       </c>
       <c r="H71" t="str">
-        <v>Owen Riegling</v>
+        <v>Azzecca</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L71" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Do It All Alone</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-17</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>2:52</v>
+        <v>2:55</v>
       </c>
       <c r="H72" t="str">
-        <v>Rend Collective</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L72" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>She Makes Me Real</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-17</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Masquerade</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>2:58</v>
+        <v>2:52</v>
       </c>
       <c r="H73" t="str">
-        <v>Cardinals</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L73" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Steady</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-17</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>Masquerade</v>
       </c>
       <c r="G74" t="str">
-        <v>3:26</v>
+        <v>2:58</v>
       </c>
       <c r="H74" t="str">
-        <v>Bella Kay</v>
+        <v>Cardinals</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L74" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>DIRTY TECH</v>
+        <v>Steady</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-17</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>PLAY ME</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>2:20</v>
+        <v>3:26</v>
       </c>
       <c r="H75" t="str">
-        <v>Kim Gordon</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L75" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Nada Más</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-17</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Nada Más - Single</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G76" t="str">
-        <v>2:19</v>
+        <v>2:20</v>
       </c>
       <c r="H76" t="str">
-        <v>Tombochio</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L76" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Friends Again</v>
+        <v>Nada Más</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-17</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Friends Again - Single</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>3:38</v>
+        <v>2:19</v>
       </c>
       <c r="H77" t="str">
-        <v>Baby Rose</v>
+        <v>Tombochio</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L77" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>W.T.A.</v>
+        <v>Friends Again</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-17</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>W.T.A. - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:22</v>
+        <v>3:38</v>
       </c>
       <c r="H78" t="str">
-        <v>Isaia Huron</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L78" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>desire.</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-17</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>November Scorpio</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:15</v>
+        <v>3:22</v>
       </c>
       <c r="H79" t="str">
-        <v>Tiana Major9</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L79" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>desire.</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-17</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G80" t="str">
-        <v>3:12</v>
+        <v>3:15</v>
       </c>
       <c r="H80" t="str">
-        <v>August Ponthier</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L80" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Killer Whale</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-17</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Killer Whale - Single</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G81" t="str">
-        <v>4:00</v>
+        <v>3:12</v>
       </c>
       <c r="H81" t="str">
-        <v>Hayden Everett</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L81" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Waits for Me</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-17</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>You’re Free to Go</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>2:46</v>
+        <v>4:00</v>
       </c>
       <c r="H82" t="str">
-        <v>Anjimile</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L82" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Man's World</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-17</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Mud Blood Bone</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G83" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H83" t="str">
-        <v>Cat Clyde</v>
+        <v>Anjimile</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L83" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>In the Middle of It</v>
+        <v>Man's World</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-17</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G84" t="str">
-        <v>3:13</v>
+        <v>2:42</v>
       </c>
       <c r="H84" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L84" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-17</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Fleeting - EP</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>2:51</v>
+        <v>3:13</v>
       </c>
       <c r="H85" t="str">
-        <v>Sarah Kinsley</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L85" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-17</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G86" t="str">
-        <v>5:23</v>
+        <v>2:51</v>
       </c>
       <c r="H86" t="str">
-        <v>BUNT.</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L86" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>I've Never Met Her</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-17</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:07</v>
+        <v>5:23</v>
       </c>
       <c r="H87" t="str">
-        <v>Ally Salort</v>
+        <v>BUNT.</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L87" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-17</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>The Elephant</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:28</v>
+        <v>3:07</v>
       </c>
       <c r="H88" t="str">
-        <v>Ledbyher</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L88" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Yes</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-17</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Just A Few Folk</v>
+        <v>The Elephant</v>
       </c>
       <c r="G89" t="str">
-        <v>3:21</v>
+        <v>3:28</v>
       </c>
       <c r="H89" t="str">
-        <v>JP Cooper</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L89" t="str">
-        <v>Yes - JP Cooper</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>CHOKEHOLD</v>
+        <v>Yes</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-17</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>CHOKEHOLD - Single</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G90" t="str">
-        <v>2:52</v>
+        <v>3:21</v>
       </c>
       <c r="H90" t="str">
-        <v>WesGhost</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L90" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Bad Faith</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-17</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Love Is Not Enough</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H91" t="str">
-        <v>Converge</v>
+        <v>WesGhost</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L91" t="str">
-        <v>Bad Faith - Converge</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Gimme Some Moore</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-17</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G92" t="str">
-        <v>4:00</v>
+        <v>2:48</v>
       </c>
       <c r="H92" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Converge</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L92" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Angel Eyes</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-17</v>
@@ -3909,68 +3909,106 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>God Forgives - Single</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G93" t="str">
-        <v>2:14</v>
+        <v>4:00</v>
       </c>
       <c r="H93" t="str">
-        <v>Guilt Trip</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L93" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
+        <v>Angel Eyes</v>
+      </c>
+      <c r="B94" t="str">
+        <v/>
+      </c>
+      <c r="C94" t="str">
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+      </c>
+      <c r="D94" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v>God Forgives - Single</v>
+      </c>
+      <c r="G94" t="str">
+        <v>2:14</v>
+      </c>
+      <c r="H94" t="str">
+        <v>Guilt Trip</v>
+      </c>
+      <c r="I94" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J94" t="str">
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+      </c>
+      <c r="K94" t="str">
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+      </c>
+      <c r="L94" t="str">
+        <v>Angel Eyes - Guilt Trip</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
         <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
-      <c r="B94" t="str">
-        <v/>
-      </c>
-      <c r="C94" t="str">
+      <c r="B95" t="str">
+        <v/>
+      </c>
+      <c r="C95" t="str">
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
-      <c r="D94" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E94" t="str">
-        <v/>
-      </c>
-      <c r="F94" t="str">
+      <c r="D95" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
         <v>Savage Imperial Death March</v>
       </c>
-      <c r="G94" t="str">
+      <c r="G95" t="str">
         <v>3:17</v>
       </c>
-      <c r="H94" t="str">
+      <c r="H95" t="str">
         <v>Melvins</v>
       </c>
-      <c r="I94" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J94" t="str">
+      <c r="I95" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J95" t="str">
         <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
-      <c r="K94" t="str">
+      <c r="K95" t="str">
         <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
-      <c r="L94" t="str">
+      <c r="L95" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L94"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L95"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L96"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -512,13 +512,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Be Her</v>
+        <v>White Feather Hawk Tail Deer Hunter</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>https://music.apple.com/us/song/be-her/1869436845</v>
+        <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-17</v>
@@ -527,36 +527,36 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>Dandelion</v>
+        <v>White Feather Hawk Tail Deer Hunter - Single</v>
       </c>
       <c r="G4" t="str">
-        <v>3:37</v>
+        <v>3:54</v>
       </c>
       <c r="H4" t="str">
-        <v>Ella Langley</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
       </c>
       <c r="K4" t="str">
-        <v>https://music.apple.com/us/album/be-her/1869436835</v>
+        <v>https://music.apple.com/us/album/white-feather-hawk-tail-deer-hunter/1877234145</v>
       </c>
       <c r="L4" t="str">
-        <v>Be Her - Ella Langley</v>
+        <v>White Feather Hawk Tail Deer Hunter - Lana Del Rey</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>other side.</v>
+        <v>Be Her</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/other-side/1867923704</v>
+        <v>https://music.apple.com/us/song/be-her/1869436845</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-17</v>
@@ -565,36 +565,36 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>Icon</v>
+        <v>Dandelion</v>
       </c>
       <c r="G5" t="str">
-        <v>3:15</v>
+        <v>3:37</v>
       </c>
       <c r="H5" t="str">
-        <v>Brent Faiyaz</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/other-side/1867923697</v>
+        <v>https://music.apple.com/us/album/be-her/1869436835</v>
       </c>
       <c r="L5" t="str">
-        <v>other side. - Brent Faiyaz</v>
+        <v>Be Her - Ella Langley</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SHADOWS</v>
+        <v>other side.</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/shadows/1875373696</v>
+        <v>https://music.apple.com/us/song/other-side/1867923704</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-17</v>
@@ -603,36 +603,36 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>SHADOWS - Single</v>
+        <v>Icon</v>
       </c>
       <c r="G6" t="str">
-        <v>3:22</v>
+        <v>3:15</v>
       </c>
       <c r="H6" t="str">
-        <v>John Summit</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/shadows/1875373695</v>
+        <v>https://music.apple.com/us/album/other-side/1867923697</v>
       </c>
       <c r="L6" t="str">
-        <v>SHADOWS - John Summit</v>
+        <v>other side. - Brent Faiyaz</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Mention Me (From The Movie "GOAT")</v>
+        <v>SHADOWS</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
+        <v>https://music.apple.com/us/song/shadows/1875373696</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-17</v>
@@ -641,36 +641,36 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>SHADOWS - Single</v>
       </c>
       <c r="G7" t="str">
-        <v>3:00</v>
+        <v>3:22</v>
       </c>
       <c r="H7" t="str">
-        <v>CORTIS</v>
+        <v>John Summit</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/shadows/1875373695</v>
       </c>
       <c r="L7" t="str">
-        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
+        <v>SHADOWS - John Summit</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Casual Lady</v>
+        <v>Mention Me (From The Movie "GOAT")</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
+        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-17</v>
@@ -679,36 +679,36 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>Casual Lady - Single</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G8" t="str">
-        <v>3:14</v>
+        <v>3:00</v>
       </c>
       <c r="H8" t="str">
-        <v>flowerovlove</v>
+        <v>CORTIS</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
+        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L8" t="str">
-        <v>Casual Lady - flowerovlove</v>
+        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>I Had a Dream She Took My Hand</v>
+        <v>Casual Lady</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
+        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-17</v>
@@ -717,36 +717,36 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Trying Times</v>
+        <v>Casual Lady - Single</v>
       </c>
       <c r="G9" t="str">
-        <v>3:40</v>
+        <v>3:14</v>
       </c>
       <c r="H9" t="str">
-        <v>James Blake</v>
+        <v>flowerovlove</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
+        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
       </c>
       <c r="L9" t="str">
-        <v>I Had a Dream She Took My Hand - James Blake</v>
+        <v>Casual Lady - flowerovlove</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Let Me</v>
+        <v>I Had a Dream She Took My Hand</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/let-me/1874386210</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-17</v>
@@ -755,36 +755,36 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>Let Me - Single</v>
+        <v>Trying Times</v>
       </c>
       <c r="G10" t="str">
-        <v>4:51</v>
+        <v>3:40</v>
       </c>
       <c r="H10" t="str">
-        <v>Victoria Monét</v>
+        <v>James Blake</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/let-me/1874386209</v>
+        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
       </c>
       <c r="L10" t="str">
-        <v>Let Me - Victoria Monét</v>
+        <v>I Had a Dream She Took My Hand - James Blake</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Woman In Love</v>
+        <v>Let Me</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
+        <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-17</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>Woman In Love - Single</v>
+        <v>Let Me - Single</v>
       </c>
       <c r="G11" t="str">
-        <v>2:43</v>
+        <v>4:51</v>
       </c>
       <c r="H11" t="str">
-        <v>Perrie</v>
+        <v>Victoria Monét</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
+        <v>https://music.apple.com/us/album/let-me/1874386209</v>
       </c>
       <c r="L11" t="str">
-        <v>Woman In Love - Perrie</v>
+        <v>Let Me - Victoria Monét</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
+        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-17</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love - Single</v>
       </c>
       <c r="G12" t="str">
-        <v>4:03</v>
+        <v>2:43</v>
       </c>
       <c r="H12" t="str">
-        <v>MUNA</v>
+        <v>Perrie</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
+        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
       </c>
       <c r="L12" t="str">
-        <v>Dancing On The Wall - MUNA</v>
+        <v>Woman In Love - Perrie</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Adrenaline (NO1 Ver.)</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
+        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-17</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Adrenaline (Remix) - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G13" t="str">
-        <v>3:18</v>
+        <v>4:03</v>
       </c>
       <c r="H13" t="str">
-        <v>ATEEZ</v>
+        <v>MUNA</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
+        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
       </c>
       <c r="L13" t="str">
-        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
+        <v>Dancing On The Wall - MUNA</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ICEMAN FREESTYLE</v>
+        <v>Adrenaline (NO1 Ver.)</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
+        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-17</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>ICEMAN FREESTYLE - Single</v>
+        <v>Adrenaline (Remix) - Single</v>
       </c>
       <c r="G14" t="str">
-        <v>3:06</v>
+        <v>3:18</v>
       </c>
       <c r="H14" t="str">
-        <v>Central Cee</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
+        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
       </c>
       <c r="L14" t="str">
-        <v>ICEMAN FREESTYLE - Central Cee</v>
+        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Mírame Baby</v>
+        <v>ICEMAN FREESTYLE</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
+        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-17</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Mírame Baby - Single</v>
+        <v>ICEMAN FREESTYLE - Single</v>
       </c>
       <c r="G15" t="str">
-        <v>3:59</v>
+        <v>3:06</v>
       </c>
       <c r="H15" t="str">
-        <v>Arcángel</v>
+        <v>Central Cee</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
+        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
       </c>
       <c r="L15" t="str">
-        <v>Mírame Baby - Arcángel</v>
+        <v>ICEMAN FREESTYLE - Central Cee</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Lights Burn Dimmer</v>
+        <v>Mírame Baby</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
+        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-17</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Lights Burn Dimmer - Single</v>
+        <v>Mírame Baby - Single</v>
       </c>
       <c r="G16" t="str">
-        <v>4:20</v>
+        <v>3:59</v>
       </c>
       <c r="H16" t="str">
-        <v>Fred again..</v>
+        <v>Arcángel</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
+        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
       </c>
       <c r="L16" t="str">
-        <v>Lights Burn Dimmer - Fred again..</v>
+        <v>Mírame Baby - Arcángel</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Two Hearts</v>
+        <v>Lights Burn Dimmer</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
+        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-17</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Cerulean</v>
+        <v>Lights Burn Dimmer - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>3:52</v>
+        <v>4:20</v>
       </c>
       <c r="H17" t="str">
-        <v>Danny L Harle</v>
+        <v>Fred again..</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
+        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
       </c>
       <c r="L17" t="str">
-        <v>Two Hearts - Danny L Harle</v>
+        <v>Lights Burn Dimmer - Fred again..</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Be By You</v>
+        <v>Two Hearts</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
+        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-17</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>The Way I Am</v>
+        <v>Cerulean</v>
       </c>
       <c r="G18" t="str">
-        <v>3:17</v>
+        <v>3:52</v>
       </c>
       <c r="H18" t="str">
-        <v>Luke Combs</v>
+        <v>Danny L Harle</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
+        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
       </c>
       <c r="L18" t="str">
-        <v>Be By You - Luke Combs</v>
+        <v>Two Hearts - Danny L Harle</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>you and forever</v>
+        <v>Be By You</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
+        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-17</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>everyone for ten minutes</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G19" t="str">
-        <v>3:54</v>
+        <v>3:17</v>
       </c>
       <c r="H19" t="str">
-        <v>Bleachers</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
+        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
       </c>
       <c r="L19" t="str">
-        <v>you and forever - Bleachers</v>
+        <v>Be By You - Luke Combs</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ROOMS</v>
+        <v>you and forever</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/rooms/1874675856</v>
+        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-17</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>ROOMS - Single</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G20" t="str">
-        <v>3:52</v>
+        <v>3:54</v>
       </c>
       <c r="H20" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Bleachers</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/rooms/1874675853</v>
+        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
       </c>
       <c r="L20" t="str">
-        <v>ROOMS - Mike WiLL Made-It</v>
+        <v>you and forever - Bleachers</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>I Just Might (Austin Millz Remix)</v>
+        <v>ROOMS</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
+        <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-17</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>I Just Might (Austin Millz Remix) - Single</v>
+        <v>ROOMS - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>3:16</v>
+        <v>3:52</v>
       </c>
       <c r="H21" t="str">
-        <v>Bruno Mars</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
+        <v>https://music.apple.com/us/album/rooms/1874675853</v>
       </c>
       <c r="L21" t="str">
-        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
+        <v>ROOMS - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>MI$ LLAMADA$</v>
+        <v>I Just Might (Austin Millz Remix)</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
+        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-17</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>DEPR&lt;/3$$ED MFKZ</v>
+        <v>I Just Might (Austin Millz Remix) - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>3:11</v>
+        <v>3:16</v>
       </c>
       <c r="H22" t="str">
-        <v>Junior H</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
+        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
       </c>
       <c r="L22" t="str">
-        <v>MI$ LLAMADA$ - Junior H</v>
+        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Con el Corazón</v>
+        <v>MI$ LLAMADA$</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
+        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-17</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Con el Corazón - Single</v>
+        <v>DEPR&lt;/3$$ED MFKZ</v>
       </c>
       <c r="G23" t="str">
-        <v>3:09</v>
+        <v>3:11</v>
       </c>
       <c r="H23" t="str">
-        <v>Maluma</v>
+        <v>Junior H</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
+        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
       </c>
       <c r="L23" t="str">
-        <v>Con el Corazón - Maluma</v>
+        <v>MI$ LLAMADA$ - Junior H</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Get In Girl</v>
+        <v>Con el Corazón</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
+        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-17</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Toy With Me</v>
+        <v>Con el Corazón - Single</v>
       </c>
       <c r="G24" t="str">
-        <v>3:26</v>
+        <v>3:09</v>
       </c>
       <c r="H24" t="str">
-        <v>Meghan Trainor</v>
+        <v>Maluma</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
+        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
       </c>
       <c r="L24" t="str">
-        <v>Get In Girl - Meghan Trainor</v>
+        <v>Con el Corazón - Maluma</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>London Foolishly</v>
+        <v>Get In Girl</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
+        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-17</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Sunday Best (Deluxe)</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G25" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H25" t="str">
-        <v>Nick Jonas</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
+        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
       </c>
       <c r="L25" t="str">
-        <v>London Foolishly - Nick Jonas</v>
+        <v>Get In Girl - Meghan Trainor</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Thorns</v>
+        <v>London Foolishly</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/thorns/1875330576</v>
+        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-17</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Thorns - Single</v>
+        <v>Sunday Best (Deluxe)</v>
       </c>
       <c r="G26" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H26" t="str">
-        <v>Jelly Roll</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/thorns/1875330145</v>
+        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
       </c>
       <c r="L26" t="str">
-        <v>Thorns - Jelly Roll</v>
+        <v>London Foolishly - Nick Jonas</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Thinkin Bout You</v>
+        <v>Thorns</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
+        <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-17</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Honora</v>
+        <v>Thorns - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>4:10</v>
+        <v>3:10</v>
       </c>
       <c r="H27" t="str">
-        <v>Flea</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
+        <v>https://music.apple.com/us/album/thorns/1875330145</v>
       </c>
       <c r="L27" t="str">
-        <v>Thinkin Bout You - Flea</v>
+        <v>Thorns - Jelly Roll</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>JUICY</v>
+        <v>Thinkin Bout You</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/juicy/1869398762</v>
+        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-17</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>JUICY - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G28" t="str">
-        <v>3:31</v>
+        <v>4:10</v>
       </c>
       <c r="H28" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Flea</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/juicy/1869398760</v>
+        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
       </c>
       <c r="L28" t="str">
-        <v>JUICY - Lenny Tavárez</v>
+        <v>Thinkin Bout You - Flea</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>All They Type</v>
+        <v>JUICY</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
+        <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-17</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>All They Type - Single</v>
+        <v>JUICY - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>2:52</v>
+        <v>3:31</v>
       </c>
       <c r="H29" t="str">
-        <v>Keke Palmer</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
+        <v>https://music.apple.com/us/album/juicy/1869398760</v>
       </c>
       <c r="L29" t="str">
-        <v>All They Type - Keke Palmer</v>
+        <v>JUICY - Lenny Tavárez</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>More Than A Lover</v>
+        <v>All They Type</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
+        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-17</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>More Than A Lover - Single</v>
+        <v>All They Type - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>4:05</v>
+        <v>2:52</v>
       </c>
       <c r="H30" t="str">
-        <v>Mary J. Blige</v>
+        <v>Keke Palmer</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
+        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
       </c>
       <c r="L30" t="str">
-        <v>More Than A Lover - Mary J. Blige</v>
+        <v>All They Type - Keke Palmer</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>City</v>
+        <v>More Than A Lover</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/city/1847721298</v>
+        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-17</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>My Lover</v>
+        <v>More Than A Lover - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>3:16</v>
+        <v>4:05</v>
       </c>
       <c r="H31" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/city/1847721296</v>
+        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
       </c>
       <c r="L31" t="str">
-        <v>City - Claire Rosinkranz</v>
+        <v>More Than A Lover - Mary J. Blige</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Eyes Closed</v>
+        <v>City</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
+        <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-17</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>My Lover</v>
       </c>
       <c r="G32" t="str">
-        <v>2:25</v>
+        <v>3:16</v>
       </c>
       <c r="H32" t="str">
-        <v>Mimi Webb</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
+        <v>https://music.apple.com/us/album/city/1847721296</v>
       </c>
       <c r="L32" t="str">
-        <v>Eyes Closed - Mimi Webb</v>
+        <v>City - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Go For Broke</v>
+        <v>Eyes Closed</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
+        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-17</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Go For Broke - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G33" t="str">
-        <v>2:50</v>
+        <v>2:25</v>
       </c>
       <c r="H33" t="str">
-        <v>Knox</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
+        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
       </c>
       <c r="L33" t="str">
-        <v>Go For Broke - Knox</v>
+        <v>Eyes Closed - Mimi Webb</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>somebody you're supposed to love</v>
+        <v>Go For Broke</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
+        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-17</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>THE ART OF BEING A MESS (DELUXE)</v>
+        <v>Go For Broke - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H34" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Knox</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
+        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
       </c>
       <c r="L34" t="str">
-        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
+        <v>Go For Broke - Knox</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Kentucky Too Long</v>
+        <v>somebody you're supposed to love</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
+        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-17</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Kentucky Too Long - Single</v>
+        <v>THE ART OF BEING A MESS (DELUXE)</v>
       </c>
       <c r="G35" t="str">
-        <v>3:38</v>
+        <v>3:10</v>
       </c>
       <c r="H35" t="str">
-        <v>Charley Crockett</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
+        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
       </c>
       <c r="L35" t="str">
-        <v>Kentucky Too Long - Charley Crockett</v>
+        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Somewhere Down in Georgia</v>
+        <v>Kentucky Too Long</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
+        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-17</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Somewhere Down in Georgia - Single</v>
+        <v>Kentucky Too Long - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H36" t="str">
-        <v>Mon Rovîa</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
+        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
       </c>
       <c r="L36" t="str">
-        <v>Somewhere Down in Georgia - Mon Rovîa</v>
+        <v>Kentucky Too Long - Charley Crockett</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>BANG BANG</v>
+        <v>Somewhere Down in Georgia</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
+        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-17</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>BANG BANG - Single</v>
+        <v>Somewhere Down in Georgia - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>2:58</v>
+        <v>2:57</v>
       </c>
       <c r="H37" t="str">
-        <v>IVE</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
+        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
       </c>
       <c r="L37" t="str">
-        <v>BANG BANG - IVE</v>
+        <v>Somewhere Down in Georgia - Mon Rovîa</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
+        <v>BANG BANG</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
+        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-17</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
+        <v>BANG BANG - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>3:15</v>
+        <v>2:58</v>
       </c>
       <c r="H38" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>IVE</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
+        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
       </c>
       <c r="L38" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
+        <v>BANG BANG - IVE</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
+        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-17</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>5:21</v>
+        <v>3:15</v>
       </c>
       <c r="H39" t="str">
-        <v>Don Broco</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
+        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
       </c>
       <c r="L39" t="str">
-        <v>Nightmare Tripping - Don Broco</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Hive Mind (feat. Denzel Curry)</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
+        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-17</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Single</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="G40" t="str">
-        <v>3:26</v>
+        <v>5:21</v>
       </c>
       <c r="H40" t="str">
-        <v>Knocked Loose</v>
+        <v>Don Broco</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
+        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
+        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
       </c>
       <c r="L40" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
+        <v>Nightmare Tripping - Don Broco</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>for your love</v>
+        <v>Hive Mind (feat. Denzel Curry)</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
+        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-17</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>for your love - Single</v>
+        <v>Hive Mind (feat. Denzel Curry) - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>3:05</v>
+        <v>3:26</v>
       </c>
       <c r="H41" t="str">
-        <v>Cruz Beckham</v>
+        <v>Knocked Loose</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
+        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
       </c>
       <c r="L41" t="str">
-        <v>for your love - Cruz Beckham</v>
+        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Somebody</v>
+        <v>for your love</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873193244</v>
+        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-17</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Somebody - Single</v>
+        <v>for your love - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>3:23</v>
+        <v>3:05</v>
       </c>
       <c r="H42" t="str">
-        <v>Jamie Foxx</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873193243</v>
+        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
       </c>
       <c r="L42" t="str">
-        <v>Somebody - Jamie Foxx</v>
+        <v>for your love - Cruz Beckham</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>BIG FEELING (NO MAKEUP)</v>
+        <v>Somebody</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
+        <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-17</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>BIG FEELING (NO MAKEUP) - Single</v>
+        <v>Somebody - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>1:55</v>
+        <v>3:23</v>
       </c>
       <c r="H43" t="str">
-        <v>BKTHERULA</v>
+        <v>Jamie Foxx</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
+        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
+        <v>https://music.apple.com/us/album/somebody/1873193243</v>
       </c>
       <c r="L43" t="str">
-        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
+        <v>Somebody - Jamie Foxx</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>On and On</v>
+        <v>BIG FEELING (NO MAKEUP)</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
+        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-17</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Work of Heart</v>
+        <v>BIG FEELING (NO MAKEUP) - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>3:43</v>
+        <v>1:55</v>
       </c>
       <c r="H44" t="str">
-        <v>Flatland Cavalry</v>
+        <v>BKTHERULA</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
+        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
       </c>
       <c r="L44" t="str">
-        <v>On and On - Flatland Cavalry</v>
+        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Push My Luck</v>
+        <v>On and On</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
+        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-17</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Push My Luck / All I Ever Need - EP</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G45" t="str">
-        <v>2:44</v>
+        <v>3:43</v>
       </c>
       <c r="H45" t="str">
-        <v>Cold War Kids</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
+        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
       </c>
       <c r="L45" t="str">
-        <v>Push My Luck - Cold War Kids</v>
+        <v>On and On - Flatland Cavalry</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Memphis Players</v>
+        <v>Push My Luck</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
+        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-17</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>AK Cuts: Vol. 2 - EP</v>
+        <v>Push My Luck / All I Ever Need - EP</v>
       </c>
       <c r="G46" t="str">
-        <v>2:46</v>
+        <v>2:44</v>
       </c>
       <c r="H46" t="str">
-        <v>Anish Kumar</v>
+        <v>Cold War Kids</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
+        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
       </c>
       <c r="L46" t="str">
-        <v>Memphis Players - Anish Kumar</v>
+        <v>Push My Luck - Cold War Kids</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Somebody</v>
+        <v>Memphis Players</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873982451</v>
+        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-17</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Blue Sky Mentality (Complete Edition)</v>
+        <v>AK Cuts: Vol. 2 - EP</v>
       </c>
       <c r="G47" t="str">
-        <v>2:49</v>
+        <v>2:46</v>
       </c>
       <c r="H47" t="str">
-        <v>Good Neighbours</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873982325</v>
+        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
       </c>
       <c r="L47" t="str">
-        <v>Somebody - Good Neighbours</v>
+        <v>Memphis Players - Anish Kumar</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>If I Didn't Know You</v>
+        <v>Somebody</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
+        <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-17</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>If I Didn't Know You - Single</v>
+        <v>Blue Sky Mentality (Complete Edition)</v>
       </c>
       <c r="G48" t="str">
-        <v>3:28</v>
+        <v>2:49</v>
       </c>
       <c r="H48" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Good Neighbours</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
+        <v>https://music.apple.com/us/album/somebody/1873982325</v>
       </c>
       <c r="L48" t="str">
-        <v>If I Didn't Know You - The Red Clay Strays</v>
+        <v>Somebody - Good Neighbours</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Seven Seas</v>
+        <v>If I Didn't Know You</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
+        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-17</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Seven Seas - Single</v>
+        <v>If I Didn't Know You - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>3:01</v>
+        <v>3:28</v>
       </c>
       <c r="H49" t="str">
-        <v>Dirty Heads</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
+        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
       </c>
       <c r="L49" t="str">
-        <v>Seven Seas - Dirty Heads</v>
+        <v>If I Didn't Know You - The Red Clay Strays</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>1000 Ways</v>
+        <v>Seven Seas</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
+        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-17</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>A Love For Strangers</v>
+        <v>Seven Seas - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>4:04</v>
+        <v>3:01</v>
       </c>
       <c r="H50" t="str">
-        <v>Chet Faker</v>
+        <v>Dirty Heads</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
+        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
       </c>
       <c r="L50" t="str">
-        <v>1000 Ways - Chet Faker</v>
+        <v>Seven Seas - Dirty Heads</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Beatback</v>
+        <v>1000 Ways</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/beatback/1861895138</v>
+        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-17</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Ö</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G51" t="str">
-        <v>2:19</v>
+        <v>4:04</v>
       </c>
       <c r="H51" t="str">
-        <v>Fcukers</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/beatback/1861895134</v>
+        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
       </c>
       <c r="L51" t="str">
-        <v>Beatback - Fcukers</v>
+        <v>1000 Ways - Chet Faker</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>GANG</v>
+        <v>Beatback</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/gang/1872243101</v>
+        <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-17</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>GANG - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G52" t="str">
-        <v>3:44</v>
+        <v>2:19</v>
       </c>
       <c r="H52" t="str">
-        <v>Tink</v>
+        <v>Fcukers</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/gang/1872243100</v>
+        <v>https://music.apple.com/us/album/beatback/1861895134</v>
       </c>
       <c r="L52" t="str">
-        <v>GANG - Tink</v>
+        <v>Beatback - Fcukers</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>a love song for u</v>
+        <v>GANG</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
+        <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-17</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>a love song for u - EP</v>
+        <v>GANG - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>1:40</v>
+        <v>3:44</v>
       </c>
       <c r="H53" t="str">
-        <v>Eem Triplin</v>
+        <v>Tink</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
+        <v>https://music.apple.com/us/album/gang/1872243100</v>
       </c>
       <c r="L53" t="str">
-        <v>a love song for u - Eem Triplin</v>
+        <v>GANG - Tink</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>See Through</v>
+        <v>a love song for u</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/see-through/1840712229</v>
+        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-17</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>A.R.S.O.N.</v>
+        <v>a love song for u - EP</v>
       </c>
       <c r="G54" t="str">
-        <v>2:38</v>
+        <v>1:40</v>
       </c>
       <c r="H54" t="str">
-        <v>Story of the Year</v>
+        <v>Eem Triplin</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
+        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/see-through/1840712224</v>
+        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
       </c>
       <c r="L54" t="str">
-        <v>See Through - Story of the Year</v>
+        <v>a love song for u - Eem Triplin</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>be the girl!</v>
+        <v>See Through</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
+        <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-17</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>the apple tree under the sea</v>
+        <v>A.R.S.O.N.</v>
       </c>
       <c r="G55" t="str">
-        <v>5:33</v>
+        <v>2:38</v>
       </c>
       <c r="H55" t="str">
-        <v>hemlocke springs</v>
+        <v>Story of the Year</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
+        <v>https://music.apple.com/us/album/see-through/1840712224</v>
       </c>
       <c r="L55" t="str">
-        <v>be the girl! - hemlocke springs</v>
+        <v>See Through - Story of the Year</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>be the girl!</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-17</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G56" t="str">
-        <v>3:33</v>
+        <v>5:33</v>
       </c>
       <c r="H56" t="str">
-        <v>Erin LeCount</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
       </c>
       <c r="L56" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>be the girl! - hemlocke springs</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-17</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>3:40</v>
+        <v>3:33</v>
       </c>
       <c r="H57" t="str">
-        <v>Kid Sistr</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L57" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ARCADE</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-17</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>ARCADE - Single</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>2:52</v>
+        <v>3:40</v>
       </c>
       <c r="H58" t="str">
-        <v>Deb Never</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L58" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Girls Just Wanna</v>
+        <v>ARCADE</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-17</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Girlhood - EP</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H59" t="str">
-        <v>Morgan St. Jean</v>
+        <v>Deb Never</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L59" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>you special.</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-17</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>you special. - Single</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G60" t="str">
-        <v>2:08</v>
+        <v>2:16</v>
       </c>
       <c r="H60" t="str">
-        <v>YFN Lucci</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L60" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Bass Dhol</v>
+        <v>you special.</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-17</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>3:38</v>
+        <v>2:08</v>
       </c>
       <c r="H61" t="str">
-        <v>Ahadadream</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L61" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-17</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>3:31</v>
+        <v>3:38</v>
       </c>
       <c r="H62" t="str">
-        <v>Charles Kelley</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L62" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>If I See Her Again</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-17</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>2:43</v>
+        <v>3:31</v>
       </c>
       <c r="H63" t="str">
-        <v>Maddox Batson</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L63" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-17</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Under The Sun</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H64" t="str">
-        <v>Sun-El Musician</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L64" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>To B Honest</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-17</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>To Whom This May Concern</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G65" t="str">
-        <v>4:30</v>
+        <v>4:43</v>
       </c>
       <c r="H65" t="str">
-        <v>Jill Scott</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L65" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>lil xan goes to washington</v>
+        <v>To B Honest</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-17</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>the beltway is burning</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G66" t="str">
-        <v>2:41</v>
+        <v>4:30</v>
       </c>
       <c r="H66" t="str">
-        <v>Ekko Astral</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L66" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Koneko</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-17</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Kurage - Single</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G67" t="str">
-        <v>4:08</v>
+        <v>2:41</v>
       </c>
       <c r="H67" t="str">
-        <v>Liana Flores</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L67" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Cupid's Call</v>
+        <v>Koneko</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-17</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>2:58</v>
+        <v>4:08</v>
       </c>
       <c r="H68" t="str">
-        <v>Dizzy Fae</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L68" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Come Back 2 Me</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-17</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>3:13</v>
+        <v>2:58</v>
       </c>
       <c r="H69" t="str">
-        <v>Chloé Caillet</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L69" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Pop Off</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-17</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Pop Off - Single</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>3:16</v>
+        <v>3:13</v>
       </c>
       <c r="H70" t="str">
-        <v>GRiZ</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L70" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>dreams</v>
+        <v>Pop Off</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-17</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>dreams - Single</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:31</v>
+        <v>3:16</v>
       </c>
       <c r="H71" t="str">
-        <v>Azzecca</v>
+        <v>GRiZ</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L71" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Love Hate Love</v>
+        <v>dreams</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-17</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>2:55</v>
+        <v>3:31</v>
       </c>
       <c r="H72" t="str">
-        <v>Owen Riegling</v>
+        <v>Azzecca</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L72" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Do It All Alone</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-17</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>2:52</v>
+        <v>2:55</v>
       </c>
       <c r="H73" t="str">
-        <v>Rend Collective</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L73" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>She Makes Me Real</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-17</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Masquerade</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:58</v>
+        <v>2:52</v>
       </c>
       <c r="H74" t="str">
-        <v>Cardinals</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L74" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Steady</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-17</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>Masquerade</v>
       </c>
       <c r="G75" t="str">
-        <v>3:26</v>
+        <v>2:58</v>
       </c>
       <c r="H75" t="str">
-        <v>Bella Kay</v>
+        <v>Cardinals</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L75" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DIRTY TECH</v>
+        <v>Steady</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-17</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>PLAY ME</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>2:20</v>
+        <v>3:26</v>
       </c>
       <c r="H76" t="str">
-        <v>Kim Gordon</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L76" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Nada Más</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-17</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Nada Más - Single</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G77" t="str">
-        <v>2:19</v>
+        <v>2:20</v>
       </c>
       <c r="H77" t="str">
-        <v>Tombochio</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L77" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Friends Again</v>
+        <v>Nada Más</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-17</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Friends Again - Single</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:38</v>
+        <v>2:19</v>
       </c>
       <c r="H78" t="str">
-        <v>Baby Rose</v>
+        <v>Tombochio</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L78" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>W.T.A.</v>
+        <v>Friends Again</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-17</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>W.T.A. - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:22</v>
+        <v>3:38</v>
       </c>
       <c r="H79" t="str">
-        <v>Isaia Huron</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L79" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>desire.</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-17</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>November Scorpio</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:15</v>
+        <v>3:22</v>
       </c>
       <c r="H80" t="str">
-        <v>Tiana Major9</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L80" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>desire.</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-17</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G81" t="str">
-        <v>3:12</v>
+        <v>3:15</v>
       </c>
       <c r="H81" t="str">
-        <v>August Ponthier</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L81" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Killer Whale</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-17</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Killer Whale - Single</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G82" t="str">
-        <v>4:00</v>
+        <v>3:12</v>
       </c>
       <c r="H82" t="str">
-        <v>Hayden Everett</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L82" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Waits for Me</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-17</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>You’re Free to Go</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>2:46</v>
+        <v>4:00</v>
       </c>
       <c r="H83" t="str">
-        <v>Anjimile</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L83" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Man's World</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-17</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Mud Blood Bone</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G84" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H84" t="str">
-        <v>Cat Clyde</v>
+        <v>Anjimile</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L84" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>In the Middle of It</v>
+        <v>Man's World</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-17</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G85" t="str">
-        <v>3:13</v>
+        <v>2:42</v>
       </c>
       <c r="H85" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L85" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-17</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Fleeting - EP</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>2:51</v>
+        <v>3:13</v>
       </c>
       <c r="H86" t="str">
-        <v>Sarah Kinsley</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L86" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-17</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G87" t="str">
-        <v>5:23</v>
+        <v>2:51</v>
       </c>
       <c r="H87" t="str">
-        <v>BUNT.</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L87" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>I've Never Met Her</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-17</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:07</v>
+        <v>5:23</v>
       </c>
       <c r="H88" t="str">
-        <v>Ally Salort</v>
+        <v>BUNT.</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L88" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-17</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>The Elephant</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>3:28</v>
+        <v>3:07</v>
       </c>
       <c r="H89" t="str">
-        <v>Ledbyher</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L89" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Yes</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-17</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Just A Few Folk</v>
+        <v>The Elephant</v>
       </c>
       <c r="G90" t="str">
-        <v>3:21</v>
+        <v>3:28</v>
       </c>
       <c r="H90" t="str">
-        <v>JP Cooper</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L90" t="str">
-        <v>Yes - JP Cooper</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>CHOKEHOLD</v>
+        <v>Yes</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-17</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>CHOKEHOLD - Single</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G91" t="str">
-        <v>2:52</v>
+        <v>3:21</v>
       </c>
       <c r="H91" t="str">
-        <v>WesGhost</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L91" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Bad Faith</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-17</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Love Is Not Enough</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H92" t="str">
-        <v>Converge</v>
+        <v>WesGhost</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L92" t="str">
-        <v>Bad Faith - Converge</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Gimme Some Moore</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-17</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G93" t="str">
-        <v>4:00</v>
+        <v>2:48</v>
       </c>
       <c r="H93" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Converge</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L93" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Angel Eyes</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-17</v>
@@ -3947,68 +3947,106 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>God Forgives - Single</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G94" t="str">
-        <v>2:14</v>
+        <v>4:00</v>
       </c>
       <c r="H94" t="str">
-        <v>Guilt Trip</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L94" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
+        <v>Angel Eyes</v>
+      </c>
+      <c r="B95" t="str">
+        <v/>
+      </c>
+      <c r="C95" t="str">
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+      </c>
+      <c r="D95" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v>God Forgives - Single</v>
+      </c>
+      <c r="G95" t="str">
+        <v>2:14</v>
+      </c>
+      <c r="H95" t="str">
+        <v>Guilt Trip</v>
+      </c>
+      <c r="I95" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J95" t="str">
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+      </c>
+      <c r="K95" t="str">
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+      </c>
+      <c r="L95" t="str">
+        <v>Angel Eyes - Guilt Trip</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
         <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
-      <c r="B95" t="str">
-        <v/>
-      </c>
-      <c r="C95" t="str">
+      <c r="B96" t="str">
+        <v/>
+      </c>
+      <c r="C96" t="str">
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
-      <c r="D95" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E95" t="str">
-        <v/>
-      </c>
-      <c r="F95" t="str">
+      <c r="D96" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
         <v>Savage Imperial Death March</v>
       </c>
-      <c r="G95" t="str">
+      <c r="G96" t="str">
         <v>3:17</v>
       </c>
-      <c r="H95" t="str">
+      <c r="H96" t="str">
         <v>Melvins</v>
       </c>
-      <c r="I95" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J95" t="str">
+      <c r="I96" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J96" t="str">
         <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
-      <c r="K95" t="str">
+      <c r="K96" t="str">
         <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
-      <c r="L95" t="str">
+      <c r="L96" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L95"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L96"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/paracosm/1869706756</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/be-her/1869436845</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/other-side/1867923704</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/shadows/1875373696</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E96" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L97"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Paracosm</v>
+        <v>Trimski</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
+        <v>https://music.apple.com/us/song/trimski/1876695030</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-18</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Paracosm</v>
+        <v>Trimski - Single</v>
       </c>
       <c r="G2" t="str">
-        <v>3:23</v>
+        <v>3:02</v>
       </c>
       <c r="H2" t="str">
-        <v>Absolutely</v>
+        <v>NAV</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
+        <v>https://music.apple.com/us/artist/nav/1200089113</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
+        <v>https://music.apple.com/us/album/trimski/1876695024</v>
       </c>
       <c r="L2" t="str">
-        <v>Paracosm - Absolutely</v>
+        <v>Trimski - NAV</v>
       </c>
     </row>
     <row r="3">
@@ -702,13 +702,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Casual Lady</v>
+        <v>Paracosm</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
+        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-18</v>
@@ -717,25 +717,25 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Casual Lady - Single</v>
+        <v>Paracosm</v>
       </c>
       <c r="G9" t="str">
-        <v>3:14</v>
+        <v>3:23</v>
       </c>
       <c r="H9" t="str">
-        <v>flowerovlove</v>
+        <v>Absolutely</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
+        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
+        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
       </c>
       <c r="L9" t="str">
-        <v>Casual Lady - flowerovlove</v>
+        <v>Paracosm - Absolutely</v>
       </c>
     </row>
     <row r="10">
@@ -778,13 +778,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Let Me</v>
+        <v>Casual Lady</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/let-me/1874386210</v>
+        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-18</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>Let Me - Single</v>
+        <v>Casual Lady - Single</v>
       </c>
       <c r="G11" t="str">
-        <v>4:51</v>
+        <v>3:14</v>
       </c>
       <c r="H11" t="str">
-        <v>Victoria Monét</v>
+        <v>flowerovlove</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
+        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/let-me/1874386209</v>
+        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
       </c>
       <c r="L11" t="str">
-        <v>Let Me - Victoria Monét</v>
+        <v>Casual Lady - flowerovlove</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Woman In Love</v>
+        <v>Let Me</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
+        <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-18</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>Woman In Love - Single</v>
+        <v>Let Me - Single</v>
       </c>
       <c r="G12" t="str">
-        <v>2:43</v>
+        <v>4:51</v>
       </c>
       <c r="H12" t="str">
-        <v>Perrie</v>
+        <v>Victoria Monét</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
+        <v>https://music.apple.com/us/album/let-me/1874386209</v>
       </c>
       <c r="L12" t="str">
-        <v>Woman In Love - Perrie</v>
+        <v>Let Me - Victoria Monét</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
+        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-18</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love - Single</v>
       </c>
       <c r="G13" t="str">
-        <v>4:03</v>
+        <v>2:43</v>
       </c>
       <c r="H13" t="str">
-        <v>MUNA</v>
+        <v>Perrie</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
+        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
       </c>
       <c r="L13" t="str">
-        <v>Dancing On The Wall - MUNA</v>
+        <v>Woman In Love - Perrie</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Adrenaline (NO1 Ver.)</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
+        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-18</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Adrenaline (Remix) - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G14" t="str">
-        <v>3:18</v>
+        <v>4:03</v>
       </c>
       <c r="H14" t="str">
-        <v>ATEEZ</v>
+        <v>MUNA</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
+        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
       </c>
       <c r="L14" t="str">
-        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
+        <v>Dancing On The Wall - MUNA</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ICEMAN FREESTYLE</v>
+        <v>Adrenaline (NO1 Ver.)</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
+        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-18</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>ICEMAN FREESTYLE - Single</v>
+        <v>Adrenaline (Remix) - Single</v>
       </c>
       <c r="G15" t="str">
-        <v>3:06</v>
+        <v>3:18</v>
       </c>
       <c r="H15" t="str">
-        <v>Central Cee</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
+        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
       </c>
       <c r="L15" t="str">
-        <v>ICEMAN FREESTYLE - Central Cee</v>
+        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Mírame Baby</v>
+        <v>ICEMAN FREESTYLE</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
+        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-18</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Mírame Baby - Single</v>
+        <v>ICEMAN FREESTYLE - Single</v>
       </c>
       <c r="G16" t="str">
-        <v>3:59</v>
+        <v>3:06</v>
       </c>
       <c r="H16" t="str">
-        <v>Arcángel</v>
+        <v>Central Cee</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
+        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
       </c>
       <c r="L16" t="str">
-        <v>Mírame Baby - Arcángel</v>
+        <v>ICEMAN FREESTYLE - Central Cee</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Lights Burn Dimmer</v>
+        <v>Mírame Baby</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
+        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-18</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Lights Burn Dimmer - Single</v>
+        <v>Mírame Baby - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>4:20</v>
+        <v>3:59</v>
       </c>
       <c r="H17" t="str">
-        <v>Fred again..</v>
+        <v>Arcángel</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
+        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
       </c>
       <c r="L17" t="str">
-        <v>Lights Burn Dimmer - Fred again..</v>
+        <v>Mírame Baby - Arcángel</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Two Hearts</v>
+        <v>Lights Burn Dimmer</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
+        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-18</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Cerulean</v>
+        <v>Lights Burn Dimmer - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>3:52</v>
+        <v>4:20</v>
       </c>
       <c r="H18" t="str">
-        <v>Danny L Harle</v>
+        <v>Fred again..</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
+        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
       </c>
       <c r="L18" t="str">
-        <v>Two Hearts - Danny L Harle</v>
+        <v>Lights Burn Dimmer - Fred again..</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Be By You</v>
+        <v>Two Hearts</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
+        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-18</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>The Way I Am</v>
+        <v>Cerulean</v>
       </c>
       <c r="G19" t="str">
-        <v>3:17</v>
+        <v>3:52</v>
       </c>
       <c r="H19" t="str">
-        <v>Luke Combs</v>
+        <v>Danny L Harle</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
+        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
       </c>
       <c r="L19" t="str">
-        <v>Be By You - Luke Combs</v>
+        <v>Two Hearts - Danny L Harle</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>you and forever</v>
+        <v>Be By You</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
+        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-18</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>everyone for ten minutes</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G20" t="str">
-        <v>3:54</v>
+        <v>3:17</v>
       </c>
       <c r="H20" t="str">
-        <v>Bleachers</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
+        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
       </c>
       <c r="L20" t="str">
-        <v>you and forever - Bleachers</v>
+        <v>Be By You - Luke Combs</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ROOMS</v>
+        <v>you and forever</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/rooms/1874675856</v>
+        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-18</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>ROOMS - Single</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G21" t="str">
-        <v>3:52</v>
+        <v>3:54</v>
       </c>
       <c r="H21" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Bleachers</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/rooms/1874675853</v>
+        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
       </c>
       <c r="L21" t="str">
-        <v>ROOMS - Mike WiLL Made-It</v>
+        <v>you and forever - Bleachers</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>I Just Might (Austin Millz Remix)</v>
+        <v>ROOMS</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
+        <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-18</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>I Just Might (Austin Millz Remix) - Single</v>
+        <v>ROOMS - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>3:16</v>
+        <v>3:52</v>
       </c>
       <c r="H22" t="str">
-        <v>Bruno Mars</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
+        <v>https://music.apple.com/us/album/rooms/1874675853</v>
       </c>
       <c r="L22" t="str">
-        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
+        <v>ROOMS - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>MI$ LLAMADA$</v>
+        <v>I Just Might (Austin Millz Remix)</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
+        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-18</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>DEPR&lt;/3$$ED MFKZ</v>
+        <v>I Just Might (Austin Millz Remix) - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>3:11</v>
+        <v>3:16</v>
       </c>
       <c r="H23" t="str">
-        <v>Junior H</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
+        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
       </c>
       <c r="L23" t="str">
-        <v>MI$ LLAMADA$ - Junior H</v>
+        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Con el Corazón</v>
+        <v>MI$ LLAMADA$</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
+        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-18</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Con el Corazón - Single</v>
+        <v>DEPR&lt;/3$$ED MFKZ</v>
       </c>
       <c r="G24" t="str">
-        <v>3:09</v>
+        <v>3:11</v>
       </c>
       <c r="H24" t="str">
-        <v>Maluma</v>
+        <v>Junior H</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
+        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
       </c>
       <c r="L24" t="str">
-        <v>Con el Corazón - Maluma</v>
+        <v>MI$ LLAMADA$ - Junior H</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Get In Girl</v>
+        <v>Con el Corazón</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
+        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-18</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Toy With Me</v>
+        <v>Con el Corazón - Single</v>
       </c>
       <c r="G25" t="str">
-        <v>3:26</v>
+        <v>3:09</v>
       </c>
       <c r="H25" t="str">
-        <v>Meghan Trainor</v>
+        <v>Maluma</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
+        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
       </c>
       <c r="L25" t="str">
-        <v>Get In Girl - Meghan Trainor</v>
+        <v>Con el Corazón - Maluma</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>London Foolishly</v>
+        <v>Get In Girl</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
+        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-18</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Sunday Best (Deluxe)</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G26" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H26" t="str">
-        <v>Nick Jonas</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
+        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
       </c>
       <c r="L26" t="str">
-        <v>London Foolishly - Nick Jonas</v>
+        <v>Get In Girl - Meghan Trainor</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Thorns</v>
+        <v>London Foolishly</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/thorns/1875330576</v>
+        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-18</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Thorns - Single</v>
+        <v>Sunday Best (Deluxe)</v>
       </c>
       <c r="G27" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H27" t="str">
-        <v>Jelly Roll</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/thorns/1875330145</v>
+        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
       </c>
       <c r="L27" t="str">
-        <v>Thorns - Jelly Roll</v>
+        <v>London Foolishly - Nick Jonas</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Thinkin Bout You</v>
+        <v>Thorns</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
+        <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-18</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Honora</v>
+        <v>Thorns - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>4:10</v>
+        <v>3:10</v>
       </c>
       <c r="H28" t="str">
-        <v>Flea</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
+        <v>https://music.apple.com/us/album/thorns/1875330145</v>
       </c>
       <c r="L28" t="str">
-        <v>Thinkin Bout You - Flea</v>
+        <v>Thorns - Jelly Roll</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>JUICY</v>
+        <v>Thinkin Bout You</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/juicy/1869398762</v>
+        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-18</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>JUICY - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G29" t="str">
-        <v>3:31</v>
+        <v>4:10</v>
       </c>
       <c r="H29" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Flea</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/juicy/1869398760</v>
+        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
       </c>
       <c r="L29" t="str">
-        <v>JUICY - Lenny Tavárez</v>
+        <v>Thinkin Bout You - Flea</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>All They Type</v>
+        <v>JUICY</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
+        <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-18</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>All They Type - Single</v>
+        <v>JUICY - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>2:52</v>
+        <v>3:31</v>
       </c>
       <c r="H30" t="str">
-        <v>Keke Palmer</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
+        <v>https://music.apple.com/us/album/juicy/1869398760</v>
       </c>
       <c r="L30" t="str">
-        <v>All They Type - Keke Palmer</v>
+        <v>JUICY - Lenny Tavárez</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>More Than A Lover</v>
+        <v>All They Type</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
+        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-18</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>More Than A Lover - Single</v>
+        <v>All They Type - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>4:05</v>
+        <v>2:52</v>
       </c>
       <c r="H31" t="str">
-        <v>Mary J. Blige</v>
+        <v>Keke Palmer</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
+        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
       </c>
       <c r="L31" t="str">
-        <v>More Than A Lover - Mary J. Blige</v>
+        <v>All They Type - Keke Palmer</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>City</v>
+        <v>More Than A Lover</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/city/1847721298</v>
+        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-18</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>My Lover</v>
+        <v>More Than A Lover - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>3:16</v>
+        <v>4:05</v>
       </c>
       <c r="H32" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/city/1847721296</v>
+        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
       </c>
       <c r="L32" t="str">
-        <v>City - Claire Rosinkranz</v>
+        <v>More Than A Lover - Mary J. Blige</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Eyes Closed</v>
+        <v>City</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
+        <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-18</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>My Lover</v>
       </c>
       <c r="G33" t="str">
-        <v>2:25</v>
+        <v>3:16</v>
       </c>
       <c r="H33" t="str">
-        <v>Mimi Webb</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
+        <v>https://music.apple.com/us/album/city/1847721296</v>
       </c>
       <c r="L33" t="str">
-        <v>Eyes Closed - Mimi Webb</v>
+        <v>City - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Go For Broke</v>
+        <v>Eyes Closed</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
+        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-18</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Go For Broke - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G34" t="str">
-        <v>2:50</v>
+        <v>2:25</v>
       </c>
       <c r="H34" t="str">
-        <v>Knox</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
+        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
       </c>
       <c r="L34" t="str">
-        <v>Go For Broke - Knox</v>
+        <v>Eyes Closed - Mimi Webb</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>somebody you're supposed to love</v>
+        <v>Go For Broke</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
+        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-18</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>THE ART OF BEING A MESS (DELUXE)</v>
+        <v>Go For Broke - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H35" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Knox</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
+        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
       </c>
       <c r="L35" t="str">
-        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
+        <v>Go For Broke - Knox</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Kentucky Too Long</v>
+        <v>somebody you're supposed to love</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
+        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-18</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Kentucky Too Long - Single</v>
+        <v>THE ART OF BEING A MESS (DELUXE)</v>
       </c>
       <c r="G36" t="str">
-        <v>3:38</v>
+        <v>3:10</v>
       </c>
       <c r="H36" t="str">
-        <v>Charley Crockett</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
+        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
       </c>
       <c r="L36" t="str">
-        <v>Kentucky Too Long - Charley Crockett</v>
+        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Somewhere Down in Georgia</v>
+        <v>Kentucky Too Long</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
+        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-18</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Somewhere Down in Georgia - Single</v>
+        <v>Kentucky Too Long - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H37" t="str">
-        <v>Mon Rovîa</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
+        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
       </c>
       <c r="L37" t="str">
-        <v>Somewhere Down in Georgia - Mon Rovîa</v>
+        <v>Kentucky Too Long - Charley Crockett</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>BANG BANG</v>
+        <v>Somewhere Down in Georgia</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
+        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-18</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>BANG BANG - Single</v>
+        <v>Somewhere Down in Georgia - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>2:58</v>
+        <v>2:57</v>
       </c>
       <c r="H38" t="str">
-        <v>IVE</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
+        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
       </c>
       <c r="L38" t="str">
-        <v>BANG BANG - IVE</v>
+        <v>Somewhere Down in Georgia - Mon Rovîa</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
+        <v>BANG BANG</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
+        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-18</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
+        <v>BANG BANG - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>3:15</v>
+        <v>2:58</v>
       </c>
       <c r="H39" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>IVE</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
+        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
       </c>
       <c r="L39" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
+        <v>BANG BANG - IVE</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
+        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-18</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>5:21</v>
+        <v>3:15</v>
       </c>
       <c r="H40" t="str">
-        <v>Don Broco</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
+        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
       </c>
       <c r="L40" t="str">
-        <v>Nightmare Tripping - Don Broco</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Hive Mind (feat. Denzel Curry)</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
+        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-18</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Single</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="G41" t="str">
-        <v>3:26</v>
+        <v>5:21</v>
       </c>
       <c r="H41" t="str">
-        <v>Knocked Loose</v>
+        <v>Don Broco</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
+        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
+        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
       </c>
       <c r="L41" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
+        <v>Nightmare Tripping - Don Broco</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>for your love</v>
+        <v>Hive Mind (feat. Denzel Curry)</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
+        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-18</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>for your love - Single</v>
+        <v>Hive Mind (feat. Denzel Curry) - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>3:05</v>
+        <v>3:26</v>
       </c>
       <c r="H42" t="str">
-        <v>Cruz Beckham</v>
+        <v>Knocked Loose</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
+        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
       </c>
       <c r="L42" t="str">
-        <v>for your love - Cruz Beckham</v>
+        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Somebody</v>
+        <v>for your love</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873193244</v>
+        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-18</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Somebody - Single</v>
+        <v>for your love - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>3:23</v>
+        <v>3:05</v>
       </c>
       <c r="H43" t="str">
-        <v>Jamie Foxx</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873193243</v>
+        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
       </c>
       <c r="L43" t="str">
-        <v>Somebody - Jamie Foxx</v>
+        <v>for your love - Cruz Beckham</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>BIG FEELING (NO MAKEUP)</v>
+        <v>Somebody</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
+        <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-18</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>BIG FEELING (NO MAKEUP) - Single</v>
+        <v>Somebody - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>1:55</v>
+        <v>3:23</v>
       </c>
       <c r="H44" t="str">
-        <v>BKTHERULA</v>
+        <v>Jamie Foxx</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
+        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
+        <v>https://music.apple.com/us/album/somebody/1873193243</v>
       </c>
       <c r="L44" t="str">
-        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
+        <v>Somebody - Jamie Foxx</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>On and On</v>
+        <v>BIG FEELING (NO MAKEUP)</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
+        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-18</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Work of Heart</v>
+        <v>BIG FEELING (NO MAKEUP) - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>3:43</v>
+        <v>1:55</v>
       </c>
       <c r="H45" t="str">
-        <v>Flatland Cavalry</v>
+        <v>BKTHERULA</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
+        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
       </c>
       <c r="L45" t="str">
-        <v>On and On - Flatland Cavalry</v>
+        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Push My Luck</v>
+        <v>On and On</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
+        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-18</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Push My Luck / All I Ever Need - EP</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G46" t="str">
-        <v>2:44</v>
+        <v>3:43</v>
       </c>
       <c r="H46" t="str">
-        <v>Cold War Kids</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
+        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
       </c>
       <c r="L46" t="str">
-        <v>Push My Luck - Cold War Kids</v>
+        <v>On and On - Flatland Cavalry</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Memphis Players</v>
+        <v>Push My Luck</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
+        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-18</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>AK Cuts: Vol. 2 - EP</v>
+        <v>Push My Luck / All I Ever Need - EP</v>
       </c>
       <c r="G47" t="str">
-        <v>2:46</v>
+        <v>2:44</v>
       </c>
       <c r="H47" t="str">
-        <v>Anish Kumar</v>
+        <v>Cold War Kids</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
+        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
       </c>
       <c r="L47" t="str">
-        <v>Memphis Players - Anish Kumar</v>
+        <v>Push My Luck - Cold War Kids</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Somebody</v>
+        <v>Memphis Players</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873982451</v>
+        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-18</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Blue Sky Mentality (Complete Edition)</v>
+        <v>AK Cuts: Vol. 2 - EP</v>
       </c>
       <c r="G48" t="str">
-        <v>2:49</v>
+        <v>2:46</v>
       </c>
       <c r="H48" t="str">
-        <v>Good Neighbours</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873982325</v>
+        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
       </c>
       <c r="L48" t="str">
-        <v>Somebody - Good Neighbours</v>
+        <v>Memphis Players - Anish Kumar</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>If I Didn't Know You</v>
+        <v>Somebody</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
+        <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-18</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>If I Didn't Know You - Single</v>
+        <v>Blue Sky Mentality (Complete Edition)</v>
       </c>
       <c r="G49" t="str">
-        <v>3:28</v>
+        <v>2:49</v>
       </c>
       <c r="H49" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Good Neighbours</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
+        <v>https://music.apple.com/us/album/somebody/1873982325</v>
       </c>
       <c r="L49" t="str">
-        <v>If I Didn't Know You - The Red Clay Strays</v>
+        <v>Somebody - Good Neighbours</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Seven Seas</v>
+        <v>If I Didn't Know You</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
+        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-18</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Seven Seas - Single</v>
+        <v>If I Didn't Know You - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>3:01</v>
+        <v>3:28</v>
       </c>
       <c r="H50" t="str">
-        <v>Dirty Heads</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
+        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
       </c>
       <c r="L50" t="str">
-        <v>Seven Seas - Dirty Heads</v>
+        <v>If I Didn't Know You - The Red Clay Strays</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>1000 Ways</v>
+        <v>Seven Seas</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
+        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-18</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>A Love For Strangers</v>
+        <v>Seven Seas - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>4:04</v>
+        <v>3:01</v>
       </c>
       <c r="H51" t="str">
-        <v>Chet Faker</v>
+        <v>Dirty Heads</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
+        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
       </c>
       <c r="L51" t="str">
-        <v>1000 Ways - Chet Faker</v>
+        <v>Seven Seas - Dirty Heads</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Beatback</v>
+        <v>1000 Ways</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/beatback/1861895138</v>
+        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-18</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Ö</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G52" t="str">
-        <v>2:19</v>
+        <v>4:04</v>
       </c>
       <c r="H52" t="str">
-        <v>Fcukers</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/beatback/1861895134</v>
+        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
       </c>
       <c r="L52" t="str">
-        <v>Beatback - Fcukers</v>
+        <v>1000 Ways - Chet Faker</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>GANG</v>
+        <v>Beatback</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/gang/1872243101</v>
+        <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-18</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>GANG - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G53" t="str">
-        <v>3:44</v>
+        <v>2:19</v>
       </c>
       <c r="H53" t="str">
-        <v>Tink</v>
+        <v>Fcukers</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/gang/1872243100</v>
+        <v>https://music.apple.com/us/album/beatback/1861895134</v>
       </c>
       <c r="L53" t="str">
-        <v>GANG - Tink</v>
+        <v>Beatback - Fcukers</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>a love song for u</v>
+        <v>GANG</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
+        <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-18</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>a love song for u - EP</v>
+        <v>GANG - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>1:40</v>
+        <v>3:44</v>
       </c>
       <c r="H54" t="str">
-        <v>Eem Triplin</v>
+        <v>Tink</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
+        <v>https://music.apple.com/us/album/gang/1872243100</v>
       </c>
       <c r="L54" t="str">
-        <v>a love song for u - Eem Triplin</v>
+        <v>GANG - Tink</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>See Through</v>
+        <v>a love song for u</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/see-through/1840712229</v>
+        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-18</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>A.R.S.O.N.</v>
+        <v>a love song for u - EP</v>
       </c>
       <c r="G55" t="str">
-        <v>2:38</v>
+        <v>1:40</v>
       </c>
       <c r="H55" t="str">
-        <v>Story of the Year</v>
+        <v>Eem Triplin</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
+        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/see-through/1840712224</v>
+        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
       </c>
       <c r="L55" t="str">
-        <v>See Through - Story of the Year</v>
+        <v>a love song for u - Eem Triplin</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>be the girl!</v>
+        <v>See Through</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
+        <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-18</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>the apple tree under the sea</v>
+        <v>A.R.S.O.N.</v>
       </c>
       <c r="G56" t="str">
-        <v>5:33</v>
+        <v>2:38</v>
       </c>
       <c r="H56" t="str">
-        <v>hemlocke springs</v>
+        <v>Story of the Year</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
+        <v>https://music.apple.com/us/album/see-through/1840712224</v>
       </c>
       <c r="L56" t="str">
-        <v>be the girl! - hemlocke springs</v>
+        <v>See Through - Story of the Year</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>be the girl!</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-18</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G57" t="str">
-        <v>3:33</v>
+        <v>5:33</v>
       </c>
       <c r="H57" t="str">
-        <v>Erin LeCount</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
       </c>
       <c r="L57" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>be the girl! - hemlocke springs</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-18</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:40</v>
+        <v>3:33</v>
       </c>
       <c r="H58" t="str">
-        <v>Kid Sistr</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L58" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ARCADE</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-18</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>ARCADE - Single</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>2:52</v>
+        <v>3:40</v>
       </c>
       <c r="H59" t="str">
-        <v>Deb Never</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L59" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Girls Just Wanna</v>
+        <v>ARCADE</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-18</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Girlhood - EP</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H60" t="str">
-        <v>Morgan St. Jean</v>
+        <v>Deb Never</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L60" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>you special.</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-18</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>you special. - Single</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G61" t="str">
-        <v>2:08</v>
+        <v>2:16</v>
       </c>
       <c r="H61" t="str">
-        <v>YFN Lucci</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L61" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Bass Dhol</v>
+        <v>you special.</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-18</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>3:38</v>
+        <v>2:08</v>
       </c>
       <c r="H62" t="str">
-        <v>Ahadadream</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L62" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-18</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>3:31</v>
+        <v>3:38</v>
       </c>
       <c r="H63" t="str">
-        <v>Charles Kelley</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L63" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>If I See Her Again</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-18</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>2:43</v>
+        <v>3:31</v>
       </c>
       <c r="H64" t="str">
-        <v>Maddox Batson</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L64" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-18</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Under The Sun</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H65" t="str">
-        <v>Sun-El Musician</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L65" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>To B Honest</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-18</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>To Whom This May Concern</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G66" t="str">
-        <v>4:30</v>
+        <v>4:43</v>
       </c>
       <c r="H66" t="str">
-        <v>Jill Scott</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L66" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>lil xan goes to washington</v>
+        <v>To B Honest</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-18</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>the beltway is burning</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G67" t="str">
-        <v>2:41</v>
+        <v>4:30</v>
       </c>
       <c r="H67" t="str">
-        <v>Ekko Astral</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L67" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Koneko</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-18</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Kurage - Single</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G68" t="str">
-        <v>4:08</v>
+        <v>2:41</v>
       </c>
       <c r="H68" t="str">
-        <v>Liana Flores</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L68" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Cupid's Call</v>
+        <v>Koneko</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-18</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>2:58</v>
+        <v>4:08</v>
       </c>
       <c r="H69" t="str">
-        <v>Dizzy Fae</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L69" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Come Back 2 Me</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-18</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>3:13</v>
+        <v>2:58</v>
       </c>
       <c r="H70" t="str">
-        <v>Chloé Caillet</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L70" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Pop Off</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-18</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Pop Off - Single</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:16</v>
+        <v>3:13</v>
       </c>
       <c r="H71" t="str">
-        <v>GRiZ</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L71" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>dreams</v>
+        <v>Pop Off</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-18</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>dreams - Single</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:31</v>
+        <v>3:16</v>
       </c>
       <c r="H72" t="str">
-        <v>Azzecca</v>
+        <v>GRiZ</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L72" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Love Hate Love</v>
+        <v>dreams</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-18</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>2:55</v>
+        <v>3:31</v>
       </c>
       <c r="H73" t="str">
-        <v>Owen Riegling</v>
+        <v>Azzecca</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L73" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Do It All Alone</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-18</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:52</v>
+        <v>2:55</v>
       </c>
       <c r="H74" t="str">
-        <v>Rend Collective</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L74" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>She Makes Me Real</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-18</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Masquerade</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>2:58</v>
+        <v>2:52</v>
       </c>
       <c r="H75" t="str">
-        <v>Cardinals</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L75" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Steady</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-18</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>Masquerade</v>
       </c>
       <c r="G76" t="str">
-        <v>3:26</v>
+        <v>2:58</v>
       </c>
       <c r="H76" t="str">
-        <v>Bella Kay</v>
+        <v>Cardinals</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L76" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>DIRTY TECH</v>
+        <v>Steady</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-18</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>PLAY ME</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:20</v>
+        <v>3:26</v>
       </c>
       <c r="H77" t="str">
-        <v>Kim Gordon</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L77" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Nada Más</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-18</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Nada Más - Single</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G78" t="str">
-        <v>2:19</v>
+        <v>2:20</v>
       </c>
       <c r="H78" t="str">
-        <v>Tombochio</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L78" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Friends Again</v>
+        <v>Nada Más</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-18</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Friends Again - Single</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:38</v>
+        <v>2:19</v>
       </c>
       <c r="H79" t="str">
-        <v>Baby Rose</v>
+        <v>Tombochio</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L79" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>W.T.A.</v>
+        <v>Friends Again</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-18</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>W.T.A. - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:22</v>
+        <v>3:38</v>
       </c>
       <c r="H80" t="str">
-        <v>Isaia Huron</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L80" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>desire.</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-18</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>November Scorpio</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:15</v>
+        <v>3:22</v>
       </c>
       <c r="H81" t="str">
-        <v>Tiana Major9</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L81" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>desire.</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-18</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G82" t="str">
-        <v>3:12</v>
+        <v>3:15</v>
       </c>
       <c r="H82" t="str">
-        <v>August Ponthier</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L82" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Killer Whale</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-18</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Killer Whale - Single</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G83" t="str">
-        <v>4:00</v>
+        <v>3:12</v>
       </c>
       <c r="H83" t="str">
-        <v>Hayden Everett</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L83" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Waits for Me</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-18</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>You’re Free to Go</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>2:46</v>
+        <v>4:00</v>
       </c>
       <c r="H84" t="str">
-        <v>Anjimile</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L84" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Man's World</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-18</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Mud Blood Bone</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G85" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H85" t="str">
-        <v>Cat Clyde</v>
+        <v>Anjimile</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L85" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>In the Middle of It</v>
+        <v>Man's World</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-18</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G86" t="str">
-        <v>3:13</v>
+        <v>2:42</v>
       </c>
       <c r="H86" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L86" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-18</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Fleeting - EP</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>2:51</v>
+        <v>3:13</v>
       </c>
       <c r="H87" t="str">
-        <v>Sarah Kinsley</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L87" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-18</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G88" t="str">
-        <v>5:23</v>
+        <v>2:51</v>
       </c>
       <c r="H88" t="str">
-        <v>BUNT.</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L88" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>I've Never Met Her</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-18</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>3:07</v>
+        <v>5:23</v>
       </c>
       <c r="H89" t="str">
-        <v>Ally Salort</v>
+        <v>BUNT.</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L89" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-18</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>The Elephant</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>3:28</v>
+        <v>3:07</v>
       </c>
       <c r="H90" t="str">
-        <v>Ledbyher</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L90" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Yes</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-18</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Just A Few Folk</v>
+        <v>The Elephant</v>
       </c>
       <c r="G91" t="str">
-        <v>3:21</v>
+        <v>3:28</v>
       </c>
       <c r="H91" t="str">
-        <v>JP Cooper</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L91" t="str">
-        <v>Yes - JP Cooper</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>CHOKEHOLD</v>
+        <v>Yes</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-18</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>CHOKEHOLD - Single</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G92" t="str">
-        <v>2:52</v>
+        <v>3:21</v>
       </c>
       <c r="H92" t="str">
-        <v>WesGhost</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L92" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Bad Faith</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-18</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Love Is Not Enough</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H93" t="str">
-        <v>Converge</v>
+        <v>WesGhost</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L93" t="str">
-        <v>Bad Faith - Converge</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Gimme Some Moore</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-18</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G94" t="str">
-        <v>4:00</v>
+        <v>2:48</v>
       </c>
       <c r="H94" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Converge</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L94" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Angel Eyes</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-18</v>
@@ -3985,68 +3985,106 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>God Forgives - Single</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G95" t="str">
-        <v>2:14</v>
+        <v>4:00</v>
       </c>
       <c r="H95" t="str">
-        <v>Guilt Trip</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L95" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
+        <v>Angel Eyes</v>
+      </c>
+      <c r="B96" t="str">
+        <v/>
+      </c>
+      <c r="C96" t="str">
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+      </c>
+      <c r="D96" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v>God Forgives - Single</v>
+      </c>
+      <c r="G96" t="str">
+        <v>2:14</v>
+      </c>
+      <c r="H96" t="str">
+        <v>Guilt Trip</v>
+      </c>
+      <c r="I96" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J96" t="str">
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+      </c>
+      <c r="K96" t="str">
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+      </c>
+      <c r="L96" t="str">
+        <v>Angel Eyes - Guilt Trip</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
         <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
-      <c r="B96" t="str">
-        <v/>
-      </c>
-      <c r="C96" t="str">
+      <c r="B97" t="str">
+        <v/>
+      </c>
+      <c r="C97" t="str">
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
-      <c r="D96" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="E96" t="str">
-        <v/>
-      </c>
-      <c r="F96" t="str">
+      <c r="D97" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
         <v>Savage Imperial Death March</v>
       </c>
-      <c r="G96" t="str">
+      <c r="G97" t="str">
         <v>3:17</v>
       </c>
-      <c r="H96" t="str">
+      <c r="H97" t="str">
         <v>Melvins</v>
       </c>
-      <c r="I96" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J96" t="str">
+      <c r="I97" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J97" t="str">
         <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
-      <c r="K96" t="str">
+      <c r="K97" t="str">
         <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
-      <c r="L96" t="str">
+      <c r="L97" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L96"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L97"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/trimski/1876695030</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/be-her/1869436845</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/other-side/1867923704</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/shadows/1875373696</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/paracosm/1869706756</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/let-me/1874386210</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E97" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L96"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2526,13 +2526,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>be the girl!</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/be-the-girl/1846462633</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-19</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>the apple tree under the sea</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>5:33</v>
+        <v>3:33</v>
       </c>
       <c r="H57" t="str">
-        <v>hemlocke springs</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/be-the-girl/1846462383</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L57" t="str">
-        <v>be the girl! - hemlocke springs</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-19</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:33</v>
+        <v>3:40</v>
       </c>
       <c r="H58" t="str">
-        <v>Erin LeCount</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L58" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>ARCADE</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-19</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>3:40</v>
+        <v>2:52</v>
       </c>
       <c r="H59" t="str">
-        <v>Kid Sistr</v>
+        <v>Deb Never</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L59" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ARCADE</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-19</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>ARCADE - Single</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G60" t="str">
-        <v>2:52</v>
+        <v>2:16</v>
       </c>
       <c r="H60" t="str">
-        <v>Deb Never</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L60" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Girls Just Wanna</v>
+        <v>you special.</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-19</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Girlhood - EP</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>2:16</v>
+        <v>2:08</v>
       </c>
       <c r="H61" t="str">
-        <v>Morgan St. Jean</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L61" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>you special.</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-19</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>you special. - Single</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>2:08</v>
+        <v>3:38</v>
       </c>
       <c r="H62" t="str">
-        <v>YFN Lucci</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L62" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Bass Dhol</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-19</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>3:38</v>
+        <v>3:31</v>
       </c>
       <c r="H63" t="str">
-        <v>Ahadadream</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L63" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-19</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>3:31</v>
+        <v>2:43</v>
       </c>
       <c r="H64" t="str">
-        <v>Charles Kelley</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L64" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>If I See Her Again</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-19</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G65" t="str">
-        <v>2:43</v>
+        <v>4:43</v>
       </c>
       <c r="H65" t="str">
-        <v>Maddox Batson</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L65" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>To B Honest</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-19</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Under The Sun</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G66" t="str">
-        <v>4:43</v>
+        <v>4:30</v>
       </c>
       <c r="H66" t="str">
-        <v>Sun-El Musician</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L66" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>To B Honest</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-19</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>To Whom This May Concern</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G67" t="str">
-        <v>4:30</v>
+        <v>2:41</v>
       </c>
       <c r="H67" t="str">
-        <v>Jill Scott</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L67" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>lil xan goes to washington</v>
+        <v>Koneko</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-19</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>the beltway is burning</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>2:41</v>
+        <v>4:08</v>
       </c>
       <c r="H68" t="str">
-        <v>Ekko Astral</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L68" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Koneko</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-19</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Kurage - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>4:08</v>
+        <v>2:58</v>
       </c>
       <c r="H69" t="str">
-        <v>Liana Flores</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L69" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Cupid's Call</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-19</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>2:58</v>
+        <v>3:13</v>
       </c>
       <c r="H70" t="str">
-        <v>Dizzy Fae</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L70" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Come Back 2 Me</v>
+        <v>Pop Off</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-19</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:13</v>
+        <v>3:16</v>
       </c>
       <c r="H71" t="str">
-        <v>Chloé Caillet</v>
+        <v>GRiZ</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L71" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Pop Off</v>
+        <v>dreams</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-19</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Pop Off - Single</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:16</v>
+        <v>3:31</v>
       </c>
       <c r="H72" t="str">
-        <v>GRiZ</v>
+        <v>Azzecca</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L72" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>dreams</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-19</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>dreams - Single</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>3:31</v>
+        <v>2:55</v>
       </c>
       <c r="H73" t="str">
-        <v>Azzecca</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L73" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Love Hate Love</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-19</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:55</v>
+        <v>2:52</v>
       </c>
       <c r="H74" t="str">
-        <v>Owen Riegling</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L74" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Do It All Alone</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-19</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Masquerade</v>
       </c>
       <c r="G75" t="str">
-        <v>2:52</v>
+        <v>2:58</v>
       </c>
       <c r="H75" t="str">
-        <v>Rend Collective</v>
+        <v>Cardinals</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L75" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>She Makes Me Real</v>
+        <v>Steady</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-19</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Masquerade</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>2:58</v>
+        <v>3:26</v>
       </c>
       <c r="H76" t="str">
-        <v>Cardinals</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L76" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Steady</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-19</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G77" t="str">
-        <v>3:26</v>
+        <v>2:20</v>
       </c>
       <c r="H77" t="str">
-        <v>Bella Kay</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L77" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>DIRTY TECH</v>
+        <v>Nada Más</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-19</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>PLAY ME</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>2:20</v>
+        <v>2:19</v>
       </c>
       <c r="H78" t="str">
-        <v>Kim Gordon</v>
+        <v>Tombochio</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L78" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Nada Más</v>
+        <v>Friends Again</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-19</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Nada Más - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>2:19</v>
+        <v>3:38</v>
       </c>
       <c r="H79" t="str">
-        <v>Tombochio</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L79" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Friends Again</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-19</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Friends Again - Single</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:38</v>
+        <v>3:22</v>
       </c>
       <c r="H80" t="str">
-        <v>Baby Rose</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L80" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>W.T.A.</v>
+        <v>desire.</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-19</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>W.T.A. - Single</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G81" t="str">
-        <v>3:22</v>
+        <v>3:15</v>
       </c>
       <c r="H81" t="str">
-        <v>Isaia Huron</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L81" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>desire.</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-19</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>November Scorpio</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G82" t="str">
-        <v>3:15</v>
+        <v>3:12</v>
       </c>
       <c r="H82" t="str">
-        <v>Tiana Major9</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L82" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-19</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>3:12</v>
+        <v>4:00</v>
       </c>
       <c r="H83" t="str">
-        <v>August Ponthier</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L83" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Killer Whale</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-19</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Killer Whale - Single</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G84" t="str">
-        <v>4:00</v>
+        <v>2:46</v>
       </c>
       <c r="H84" t="str">
-        <v>Hayden Everett</v>
+        <v>Anjimile</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L84" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Waits for Me</v>
+        <v>Man's World</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-19</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>You’re Free to Go</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G85" t="str">
-        <v>2:46</v>
+        <v>2:42</v>
       </c>
       <c r="H85" t="str">
-        <v>Anjimile</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L85" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Man's World</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-19</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Mud Blood Bone</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>2:42</v>
+        <v>3:13</v>
       </c>
       <c r="H86" t="str">
-        <v>Cat Clyde</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L86" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>In the Middle of It</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-19</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G87" t="str">
-        <v>3:13</v>
+        <v>2:51</v>
       </c>
       <c r="H87" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L87" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-19</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Fleeting - EP</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>2:51</v>
+        <v>5:23</v>
       </c>
       <c r="H88" t="str">
-        <v>Sarah Kinsley</v>
+        <v>BUNT.</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L88" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-19</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>5:23</v>
+        <v>3:07</v>
       </c>
       <c r="H89" t="str">
-        <v>BUNT.</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L89" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>I've Never Met Her</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-19</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>The Elephant</v>
       </c>
       <c r="G90" t="str">
-        <v>3:07</v>
+        <v>3:28</v>
       </c>
       <c r="H90" t="str">
-        <v>Ally Salort</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L90" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>Yes</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-19</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>The Elephant</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G91" t="str">
-        <v>3:28</v>
+        <v>3:21</v>
       </c>
       <c r="H91" t="str">
-        <v>Ledbyher</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L91" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Yes</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-19</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Just A Few Folk</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>3:21</v>
+        <v>2:52</v>
       </c>
       <c r="H92" t="str">
-        <v>JP Cooper</v>
+        <v>WesGhost</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L92" t="str">
-        <v>Yes - JP Cooper</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>CHOKEHOLD</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-19</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>CHOKEHOLD - Single</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G93" t="str">
-        <v>2:52</v>
+        <v>2:48</v>
       </c>
       <c r="H93" t="str">
-        <v>WesGhost</v>
+        <v>Converge</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L93" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Bad Faith</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-19</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Love Is Not Enough</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G94" t="str">
-        <v>2:48</v>
+        <v>4:00</v>
       </c>
       <c r="H94" t="str">
-        <v>Converge</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L94" t="str">
-        <v>Bad Faith - Converge</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Gimme Some Moore</v>
+        <v>Angel Eyes</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-19</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Good God / Baad Man</v>
+        <v>God Forgives - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>4:00</v>
+        <v>2:14</v>
       </c>
       <c r="H95" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Guilt Trip</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
       </c>
       <c r="L95" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
+        <v>Angel Eyes - Guilt Trip</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Angel Eyes</v>
+        <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+        <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-19</v>
@@ -4023,68 +4023,30 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>God Forgives - Single</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G96" t="str">
-        <v>2:14</v>
+        <v>3:17</v>
       </c>
       <c r="H96" t="str">
-        <v>Guilt Trip</v>
+        <v>Melvins</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+        <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
       <c r="L96" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v>Tossing Coins Into The Fountain Of F**k</v>
-      </c>
-      <c r="B97" t="str">
-        <v/>
-      </c>
-      <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
-      </c>
-      <c r="D97" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E97" t="str">
-        <v/>
-      </c>
-      <c r="F97" t="str">
-        <v>Savage Imperial Death March</v>
-      </c>
-      <c r="G97" t="str">
-        <v>3:17</v>
-      </c>
-      <c r="H97" t="str">
-        <v>Melvins</v>
-      </c>
-      <c r="I97" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
-      </c>
-      <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
-      </c>
-      <c r="L97" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L97"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L96"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L97"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2526,13 +2526,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>be the girl!</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/be-the-girl/1877161731</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-19</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G57" t="str">
-        <v>3:33</v>
+        <v>5:33</v>
       </c>
       <c r="H57" t="str">
-        <v>Erin LeCount</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/be-the-girl/1877161526</v>
       </c>
       <c r="L57" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>be the girl! - hemlocke springs</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-19</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:40</v>
+        <v>3:33</v>
       </c>
       <c r="H58" t="str">
-        <v>Kid Sistr</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L58" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ARCADE</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-19</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>ARCADE - Single</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>2:52</v>
+        <v>3:40</v>
       </c>
       <c r="H59" t="str">
-        <v>Deb Never</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L59" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Girls Just Wanna</v>
+        <v>ARCADE</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-19</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Girlhood - EP</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H60" t="str">
-        <v>Morgan St. Jean</v>
+        <v>Deb Never</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L60" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>you special.</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-19</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>you special. - Single</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G61" t="str">
-        <v>2:08</v>
+        <v>2:16</v>
       </c>
       <c r="H61" t="str">
-        <v>YFN Lucci</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L61" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Bass Dhol</v>
+        <v>you special.</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-19</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>3:38</v>
+        <v>2:08</v>
       </c>
       <c r="H62" t="str">
-        <v>Ahadadream</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L62" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-19</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>3:31</v>
+        <v>3:38</v>
       </c>
       <c r="H63" t="str">
-        <v>Charles Kelley</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L63" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>If I See Her Again</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-19</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>2:43</v>
+        <v>3:31</v>
       </c>
       <c r="H64" t="str">
-        <v>Maddox Batson</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L64" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-19</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Under The Sun</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H65" t="str">
-        <v>Sun-El Musician</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L65" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>To B Honest</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-19</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>To Whom This May Concern</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G66" t="str">
-        <v>4:30</v>
+        <v>4:43</v>
       </c>
       <c r="H66" t="str">
-        <v>Jill Scott</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L66" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>lil xan goes to washington</v>
+        <v>To B Honest</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-19</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>the beltway is burning</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G67" t="str">
-        <v>2:41</v>
+        <v>4:30</v>
       </c>
       <c r="H67" t="str">
-        <v>Ekko Astral</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L67" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Koneko</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-19</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Kurage - Single</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G68" t="str">
-        <v>4:08</v>
+        <v>2:41</v>
       </c>
       <c r="H68" t="str">
-        <v>Liana Flores</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L68" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Cupid's Call</v>
+        <v>Koneko</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-19</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>2:58</v>
+        <v>4:08</v>
       </c>
       <c r="H69" t="str">
-        <v>Dizzy Fae</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L69" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Come Back 2 Me</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-19</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>3:13</v>
+        <v>2:58</v>
       </c>
       <c r="H70" t="str">
-        <v>Chloé Caillet</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L70" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Pop Off</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-19</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Pop Off - Single</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:16</v>
+        <v>3:13</v>
       </c>
       <c r="H71" t="str">
-        <v>GRiZ</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L71" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>dreams</v>
+        <v>Pop Off</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-19</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>dreams - Single</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:31</v>
+        <v>3:16</v>
       </c>
       <c r="H72" t="str">
-        <v>Azzecca</v>
+        <v>GRiZ</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L72" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Love Hate Love</v>
+        <v>dreams</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-19</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>2:55</v>
+        <v>3:31</v>
       </c>
       <c r="H73" t="str">
-        <v>Owen Riegling</v>
+        <v>Azzecca</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L73" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Do It All Alone</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-19</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:52</v>
+        <v>2:55</v>
       </c>
       <c r="H74" t="str">
-        <v>Rend Collective</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L74" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>She Makes Me Real</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-19</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Masquerade</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>2:58</v>
+        <v>2:52</v>
       </c>
       <c r="H75" t="str">
-        <v>Cardinals</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L75" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Steady</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-19</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>Masquerade</v>
       </c>
       <c r="G76" t="str">
-        <v>3:26</v>
+        <v>2:58</v>
       </c>
       <c r="H76" t="str">
-        <v>Bella Kay</v>
+        <v>Cardinals</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L76" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>DIRTY TECH</v>
+        <v>Steady</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-19</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>PLAY ME</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:20</v>
+        <v>3:26</v>
       </c>
       <c r="H77" t="str">
-        <v>Kim Gordon</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L77" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Nada Más</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-19</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Nada Más - Single</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G78" t="str">
-        <v>2:19</v>
+        <v>2:20</v>
       </c>
       <c r="H78" t="str">
-        <v>Tombochio</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L78" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Friends Again</v>
+        <v>Nada Más</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-19</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Friends Again - Single</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:38</v>
+        <v>2:19</v>
       </c>
       <c r="H79" t="str">
-        <v>Baby Rose</v>
+        <v>Tombochio</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L79" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>W.T.A.</v>
+        <v>Friends Again</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-19</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>W.T.A. - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:22</v>
+        <v>3:38</v>
       </c>
       <c r="H80" t="str">
-        <v>Isaia Huron</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L80" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>desire.</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-19</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>November Scorpio</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:15</v>
+        <v>3:22</v>
       </c>
       <c r="H81" t="str">
-        <v>Tiana Major9</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L81" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>desire.</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-19</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G82" t="str">
-        <v>3:12</v>
+        <v>3:15</v>
       </c>
       <c r="H82" t="str">
-        <v>August Ponthier</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L82" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Killer Whale</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-19</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Killer Whale - Single</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G83" t="str">
-        <v>4:00</v>
+        <v>3:12</v>
       </c>
       <c r="H83" t="str">
-        <v>Hayden Everett</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L83" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Waits for Me</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-19</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>You’re Free to Go</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>2:46</v>
+        <v>4:00</v>
       </c>
       <c r="H84" t="str">
-        <v>Anjimile</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L84" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Man's World</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-19</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Mud Blood Bone</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G85" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H85" t="str">
-        <v>Cat Clyde</v>
+        <v>Anjimile</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L85" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>In the Middle of It</v>
+        <v>Man's World</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-19</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G86" t="str">
-        <v>3:13</v>
+        <v>2:42</v>
       </c>
       <c r="H86" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L86" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-19</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Fleeting - EP</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>2:51</v>
+        <v>3:13</v>
       </c>
       <c r="H87" t="str">
-        <v>Sarah Kinsley</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L87" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-19</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G88" t="str">
-        <v>5:23</v>
+        <v>2:51</v>
       </c>
       <c r="H88" t="str">
-        <v>BUNT.</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L88" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>I've Never Met Her</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-19</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>3:07</v>
+        <v>5:23</v>
       </c>
       <c r="H89" t="str">
-        <v>Ally Salort</v>
+        <v>BUNT.</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L89" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-19</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>The Elephant</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>3:28</v>
+        <v>3:07</v>
       </c>
       <c r="H90" t="str">
-        <v>Ledbyher</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L90" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Yes</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-19</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Just A Few Folk</v>
+        <v>The Elephant</v>
       </c>
       <c r="G91" t="str">
-        <v>3:21</v>
+        <v>3:28</v>
       </c>
       <c r="H91" t="str">
-        <v>JP Cooper</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L91" t="str">
-        <v>Yes - JP Cooper</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>CHOKEHOLD</v>
+        <v>Yes</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-19</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>CHOKEHOLD - Single</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G92" t="str">
-        <v>2:52</v>
+        <v>3:21</v>
       </c>
       <c r="H92" t="str">
-        <v>WesGhost</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L92" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Bad Faith</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-19</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Love Is Not Enough</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H93" t="str">
-        <v>Converge</v>
+        <v>WesGhost</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L93" t="str">
-        <v>Bad Faith - Converge</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Gimme Some Moore</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-19</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G94" t="str">
-        <v>4:00</v>
+        <v>2:48</v>
       </c>
       <c r="H94" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Converge</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L94" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Angel Eyes</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-19</v>
@@ -3985,68 +3985,106 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>God Forgives - Single</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G95" t="str">
-        <v>2:14</v>
+        <v>4:00</v>
       </c>
       <c r="H95" t="str">
-        <v>Guilt Trip</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L95" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
+        <v>Angel Eyes</v>
+      </c>
+      <c r="B96" t="str">
+        <v/>
+      </c>
+      <c r="C96" t="str">
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+      </c>
+      <c r="D96" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v>God Forgives - Single</v>
+      </c>
+      <c r="G96" t="str">
+        <v>2:14</v>
+      </c>
+      <c r="H96" t="str">
+        <v>Guilt Trip</v>
+      </c>
+      <c r="I96" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J96" t="str">
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+      </c>
+      <c r="K96" t="str">
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+      </c>
+      <c r="L96" t="str">
+        <v>Angel Eyes - Guilt Trip</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
         <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
-      <c r="B96" t="str">
-        <v/>
-      </c>
-      <c r="C96" t="str">
+      <c r="B97" t="str">
+        <v/>
+      </c>
+      <c r="C97" t="str">
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
-      <c r="D96" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E96" t="str">
-        <v/>
-      </c>
-      <c r="F96" t="str">
+      <c r="D97" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
         <v>Savage Imperial Death March</v>
       </c>
-      <c r="G96" t="str">
+      <c r="G97" t="str">
         <v>3:17</v>
       </c>
-      <c r="H96" t="str">
+      <c r="H97" t="str">
         <v>Melvins</v>
       </c>
-      <c r="I96" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J96" t="str">
+      <c r="I97" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J97" t="str">
         <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
-      <c r="K96" t="str">
+      <c r="K97" t="str">
         <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
-      <c r="L96" t="str">
+      <c r="L97" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L96"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L97"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L98"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Trimski</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/trimski/1876695030</v>
+        <v>https://music.apple.com/us/song/your-favorite-toy/1877913734</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-19</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Trimski - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G2" t="str">
-        <v>3:02</v>
+        <v>2:56</v>
       </c>
       <c r="H2" t="str">
-        <v>NAV</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/nav/1200089113</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/trimski/1876695024</v>
+        <v>https://music.apple.com/us/album/your-favorite-toy/1877913489</v>
       </c>
       <c r="L2" t="str">
-        <v>Trimski - NAV</v>
+        <v>Your Favorite Toy - Foo Fighters</v>
       </c>
     </row>
     <row r="3">
@@ -702,13 +702,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Paracosm</v>
+        <v>Trimski</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
+        <v>https://music.apple.com/us/song/trimski/1876695030</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-19</v>
@@ -717,25 +717,25 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Paracosm</v>
+        <v>Trimski - Single</v>
       </c>
       <c r="G9" t="str">
-        <v>3:23</v>
+        <v>3:02</v>
       </c>
       <c r="H9" t="str">
-        <v>Absolutely</v>
+        <v>NAV</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
+        <v>https://music.apple.com/us/artist/nav/1200089113</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
+        <v>https://music.apple.com/us/album/trimski/1876695024</v>
       </c>
       <c r="L9" t="str">
-        <v>Paracosm - Absolutely</v>
+        <v>Trimski - NAV</v>
       </c>
     </row>
     <row r="10">
@@ -778,13 +778,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Casual Lady</v>
+        <v>Paracosm</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
+        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-19</v>
@@ -793,25 +793,25 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>Casual Lady - Single</v>
+        <v>Paracosm</v>
       </c>
       <c r="G11" t="str">
-        <v>3:14</v>
+        <v>3:23</v>
       </c>
       <c r="H11" t="str">
-        <v>flowerovlove</v>
+        <v>Absolutely</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
+        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
+        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
       </c>
       <c r="L11" t="str">
-        <v>Casual Lady - flowerovlove</v>
+        <v>Paracosm - Absolutely</v>
       </c>
     </row>
     <row r="12">
@@ -854,13 +854,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Woman In Love</v>
+        <v>Casual Lady</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
+        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-19</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Woman In Love - Single</v>
+        <v>Casual Lady - Single</v>
       </c>
       <c r="G13" t="str">
-        <v>2:43</v>
+        <v>3:14</v>
       </c>
       <c r="H13" t="str">
-        <v>Perrie</v>
+        <v>flowerovlove</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
+        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
       </c>
       <c r="L13" t="str">
-        <v>Woman In Love - Perrie</v>
+        <v>Casual Lady - flowerovlove</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
+        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-19</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Woman In Love - Single</v>
       </c>
       <c r="G14" t="str">
-        <v>4:03</v>
+        <v>2:43</v>
       </c>
       <c r="H14" t="str">
-        <v>MUNA</v>
+        <v>Perrie</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
+        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
       </c>
       <c r="L14" t="str">
-        <v>Dancing On The Wall - MUNA</v>
+        <v>Woman In Love - Perrie</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Adrenaline (NO1 Ver.)</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
+        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-19</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Adrenaline (Remix) - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G15" t="str">
-        <v>3:18</v>
+        <v>4:03</v>
       </c>
       <c r="H15" t="str">
-        <v>ATEEZ</v>
+        <v>MUNA</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
+        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
       </c>
       <c r="L15" t="str">
-        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
+        <v>Dancing On The Wall - MUNA</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ICEMAN FREESTYLE</v>
+        <v>Adrenaline (NO1 Ver.)</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
+        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-19</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>ICEMAN FREESTYLE - Single</v>
+        <v>Adrenaline (Remix) - Single</v>
       </c>
       <c r="G16" t="str">
-        <v>3:06</v>
+        <v>3:18</v>
       </c>
       <c r="H16" t="str">
-        <v>Central Cee</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
+        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
       </c>
       <c r="L16" t="str">
-        <v>ICEMAN FREESTYLE - Central Cee</v>
+        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Mírame Baby</v>
+        <v>ICEMAN FREESTYLE</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
+        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-19</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Mírame Baby - Single</v>
+        <v>ICEMAN FREESTYLE - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>3:59</v>
+        <v>3:06</v>
       </c>
       <c r="H17" t="str">
-        <v>Arcángel</v>
+        <v>Central Cee</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
+        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
       </c>
       <c r="L17" t="str">
-        <v>Mírame Baby - Arcángel</v>
+        <v>ICEMAN FREESTYLE - Central Cee</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Lights Burn Dimmer</v>
+        <v>Mírame Baby</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
+        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-19</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Lights Burn Dimmer - Single</v>
+        <v>Mírame Baby - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>4:20</v>
+        <v>3:59</v>
       </c>
       <c r="H18" t="str">
-        <v>Fred again..</v>
+        <v>Arcángel</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
+        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
       </c>
       <c r="L18" t="str">
-        <v>Lights Burn Dimmer - Fred again..</v>
+        <v>Mírame Baby - Arcángel</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Two Hearts</v>
+        <v>Lights Burn Dimmer</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
+        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-19</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Cerulean</v>
+        <v>Lights Burn Dimmer - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>3:52</v>
+        <v>4:20</v>
       </c>
       <c r="H19" t="str">
-        <v>Danny L Harle</v>
+        <v>Fred again..</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
+        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
       </c>
       <c r="L19" t="str">
-        <v>Two Hearts - Danny L Harle</v>
+        <v>Lights Burn Dimmer - Fred again..</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Be By You</v>
+        <v>Two Hearts</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
+        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-19</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>The Way I Am</v>
+        <v>Cerulean</v>
       </c>
       <c r="G20" t="str">
-        <v>3:17</v>
+        <v>3:52</v>
       </c>
       <c r="H20" t="str">
-        <v>Luke Combs</v>
+        <v>Danny L Harle</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
+        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
       </c>
       <c r="L20" t="str">
-        <v>Be By You - Luke Combs</v>
+        <v>Two Hearts - Danny L Harle</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>you and forever</v>
+        <v>Be By You</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
+        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-19</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>everyone for ten minutes</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G21" t="str">
-        <v>3:54</v>
+        <v>3:17</v>
       </c>
       <c r="H21" t="str">
-        <v>Bleachers</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
+        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
       </c>
       <c r="L21" t="str">
-        <v>you and forever - Bleachers</v>
+        <v>Be By You - Luke Combs</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ROOMS</v>
+        <v>you and forever</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/rooms/1874675856</v>
+        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-19</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>ROOMS - Single</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G22" t="str">
-        <v>3:52</v>
+        <v>3:54</v>
       </c>
       <c r="H22" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Bleachers</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/rooms/1874675853</v>
+        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
       </c>
       <c r="L22" t="str">
-        <v>ROOMS - Mike WiLL Made-It</v>
+        <v>you and forever - Bleachers</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>I Just Might (Austin Millz Remix)</v>
+        <v>ROOMS</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
+        <v>https://music.apple.com/us/song/rooms/1874675856</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-19</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>I Just Might (Austin Millz Remix) - Single</v>
+        <v>ROOMS - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>3:16</v>
+        <v>3:52</v>
       </c>
       <c r="H23" t="str">
-        <v>Bruno Mars</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
+        <v>https://music.apple.com/us/album/rooms/1874675853</v>
       </c>
       <c r="L23" t="str">
-        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
+        <v>ROOMS - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>MI$ LLAMADA$</v>
+        <v>I Just Might (Austin Millz Remix)</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
+        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-19</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>DEPR&lt;/3$$ED MFKZ</v>
+        <v>I Just Might (Austin Millz Remix) - Single</v>
       </c>
       <c r="G24" t="str">
-        <v>3:11</v>
+        <v>3:16</v>
       </c>
       <c r="H24" t="str">
-        <v>Junior H</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
+        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
       </c>
       <c r="L24" t="str">
-        <v>MI$ LLAMADA$ - Junior H</v>
+        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Con el Corazón</v>
+        <v>MI$ LLAMADA$</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
+        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-19</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Con el Corazón - Single</v>
+        <v>DEPR&lt;/3$$ED MFKZ</v>
       </c>
       <c r="G25" t="str">
-        <v>3:09</v>
+        <v>3:11</v>
       </c>
       <c r="H25" t="str">
-        <v>Maluma</v>
+        <v>Junior H</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
+        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
       </c>
       <c r="L25" t="str">
-        <v>Con el Corazón - Maluma</v>
+        <v>MI$ LLAMADA$ - Junior H</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Get In Girl</v>
+        <v>Con el Corazón</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
+        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-19</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Toy With Me</v>
+        <v>Con el Corazón - Single</v>
       </c>
       <c r="G26" t="str">
-        <v>3:26</v>
+        <v>3:09</v>
       </c>
       <c r="H26" t="str">
-        <v>Meghan Trainor</v>
+        <v>Maluma</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
+        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
       </c>
       <c r="L26" t="str">
-        <v>Get In Girl - Meghan Trainor</v>
+        <v>Con el Corazón - Maluma</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>London Foolishly</v>
+        <v>Get In Girl</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
+        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-19</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Sunday Best (Deluxe)</v>
+        <v>Toy With Me</v>
       </c>
       <c r="G27" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H27" t="str">
-        <v>Nick Jonas</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
+        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
       </c>
       <c r="L27" t="str">
-        <v>London Foolishly - Nick Jonas</v>
+        <v>Get In Girl - Meghan Trainor</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Thorns</v>
+        <v>London Foolishly</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/thorns/1875330576</v>
+        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-19</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Thorns - Single</v>
+        <v>Sunday Best (Deluxe)</v>
       </c>
       <c r="G28" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H28" t="str">
-        <v>Jelly Roll</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/thorns/1875330145</v>
+        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
       </c>
       <c r="L28" t="str">
-        <v>Thorns - Jelly Roll</v>
+        <v>London Foolishly - Nick Jonas</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Thinkin Bout You</v>
+        <v>Thorns</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
+        <v>https://music.apple.com/us/song/thorns/1875330576</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-19</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Honora</v>
+        <v>Thorns - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>4:10</v>
+        <v>3:10</v>
       </c>
       <c r="H29" t="str">
-        <v>Flea</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
+        <v>https://music.apple.com/us/album/thorns/1875330145</v>
       </c>
       <c r="L29" t="str">
-        <v>Thinkin Bout You - Flea</v>
+        <v>Thorns - Jelly Roll</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>JUICY</v>
+        <v>Thinkin Bout You</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/juicy/1869398762</v>
+        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-19</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>JUICY - Single</v>
+        <v>Honora</v>
       </c>
       <c r="G30" t="str">
-        <v>3:31</v>
+        <v>4:10</v>
       </c>
       <c r="H30" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Flea</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/juicy/1869398760</v>
+        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
       </c>
       <c r="L30" t="str">
-        <v>JUICY - Lenny Tavárez</v>
+        <v>Thinkin Bout You - Flea</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>All They Type</v>
+        <v>JUICY</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
+        <v>https://music.apple.com/us/song/juicy/1869398762</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-19</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>All They Type - Single</v>
+        <v>JUICY - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>2:52</v>
+        <v>3:31</v>
       </c>
       <c r="H31" t="str">
-        <v>Keke Palmer</v>
+        <v>Lenny Tavárez</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
+        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
+        <v>https://music.apple.com/us/album/juicy/1869398760</v>
       </c>
       <c r="L31" t="str">
-        <v>All They Type - Keke Palmer</v>
+        <v>JUICY - Lenny Tavárez</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>More Than A Lover</v>
+        <v>All They Type</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
+        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-19</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>More Than A Lover - Single</v>
+        <v>All They Type - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>4:05</v>
+        <v>2:52</v>
       </c>
       <c r="H32" t="str">
-        <v>Mary J. Blige</v>
+        <v>Keke Palmer</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
+        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
       </c>
       <c r="L32" t="str">
-        <v>More Than A Lover - Mary J. Blige</v>
+        <v>All They Type - Keke Palmer</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>City</v>
+        <v>More Than A Lover</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/city/1847721298</v>
+        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-19</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>My Lover</v>
+        <v>More Than A Lover - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>3:16</v>
+        <v>4:05</v>
       </c>
       <c r="H33" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/city/1847721296</v>
+        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
       </c>
       <c r="L33" t="str">
-        <v>City - Claire Rosinkranz</v>
+        <v>More Than A Lover - Mary J. Blige</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Eyes Closed</v>
+        <v>City</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
+        <v>https://music.apple.com/us/song/city/1847721298</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-19</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>My Lover</v>
       </c>
       <c r="G34" t="str">
-        <v>2:25</v>
+        <v>3:16</v>
       </c>
       <c r="H34" t="str">
-        <v>Mimi Webb</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
+        <v>https://music.apple.com/us/album/city/1847721296</v>
       </c>
       <c r="L34" t="str">
-        <v>Eyes Closed - Mimi Webb</v>
+        <v>City - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Go For Broke</v>
+        <v>Eyes Closed</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
+        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-19</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Go For Broke - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G35" t="str">
-        <v>2:50</v>
+        <v>2:25</v>
       </c>
       <c r="H35" t="str">
-        <v>Knox</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
+        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
       </c>
       <c r="L35" t="str">
-        <v>Go For Broke - Knox</v>
+        <v>Eyes Closed - Mimi Webb</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>somebody you're supposed to love</v>
+        <v>Go For Broke</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
+        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-19</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>THE ART OF BEING A MESS (DELUXE)</v>
+        <v>Go For Broke - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H36" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Knox</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/knox/1547519433</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
+        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
       </c>
       <c r="L36" t="str">
-        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
+        <v>Go For Broke - Knox</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Kentucky Too Long</v>
+        <v>somebody you're supposed to love</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
+        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-19</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Kentucky Too Long - Single</v>
+        <v>THE ART OF BEING A MESS (DELUXE)</v>
       </c>
       <c r="G37" t="str">
-        <v>3:38</v>
+        <v>3:10</v>
       </c>
       <c r="H37" t="str">
-        <v>Charley Crockett</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
+        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
       </c>
       <c r="L37" t="str">
-        <v>Kentucky Too Long - Charley Crockett</v>
+        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Somewhere Down in Georgia</v>
+        <v>Kentucky Too Long</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
+        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-19</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Somewhere Down in Georgia - Single</v>
+        <v>Kentucky Too Long - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H38" t="str">
-        <v>Mon Rovîa</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
+        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
       </c>
       <c r="L38" t="str">
-        <v>Somewhere Down in Georgia - Mon Rovîa</v>
+        <v>Kentucky Too Long - Charley Crockett</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>BANG BANG</v>
+        <v>Somewhere Down in Georgia</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
+        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-19</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>BANG BANG - Single</v>
+        <v>Somewhere Down in Georgia - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>2:58</v>
+        <v>2:57</v>
       </c>
       <c r="H39" t="str">
-        <v>IVE</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
+        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
       </c>
       <c r="L39" t="str">
-        <v>BANG BANG - IVE</v>
+        <v>Somewhere Down in Georgia - Mon Rovîa</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
+        <v>BANG BANG</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
+        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-19</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
+        <v>BANG BANG - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>3:15</v>
+        <v>2:58</v>
       </c>
       <c r="H40" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>IVE</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
+        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
       </c>
       <c r="L40" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
+        <v>BANG BANG - IVE</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
+        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-19</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Nightmare Tripping</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>5:21</v>
+        <v>3:15</v>
       </c>
       <c r="H41" t="str">
-        <v>Don Broco</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
+        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
       </c>
       <c r="L41" t="str">
-        <v>Nightmare Tripping - Don Broco</v>
+        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Hive Mind (feat. Denzel Curry)</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
+        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-19</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Single</v>
+        <v>Nightmare Tripping</v>
       </c>
       <c r="G42" t="str">
-        <v>3:26</v>
+        <v>5:21</v>
       </c>
       <c r="H42" t="str">
-        <v>Knocked Loose</v>
+        <v>Don Broco</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
+        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
+        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
       </c>
       <c r="L42" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
+        <v>Nightmare Tripping - Don Broco</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>for your love</v>
+        <v>Hive Mind (feat. Denzel Curry)</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
+        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-19</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>for your love - Single</v>
+        <v>Hive Mind (feat. Denzel Curry) - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>3:05</v>
+        <v>3:26</v>
       </c>
       <c r="H43" t="str">
-        <v>Cruz Beckham</v>
+        <v>Knocked Loose</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
+        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
       </c>
       <c r="L43" t="str">
-        <v>for your love - Cruz Beckham</v>
+        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Somebody</v>
+        <v>for your love</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873193244</v>
+        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-19</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Somebody - Single</v>
+        <v>for your love - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>3:23</v>
+        <v>3:05</v>
       </c>
       <c r="H44" t="str">
-        <v>Jamie Foxx</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873193243</v>
+        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
       </c>
       <c r="L44" t="str">
-        <v>Somebody - Jamie Foxx</v>
+        <v>for your love - Cruz Beckham</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>BIG FEELING (NO MAKEUP)</v>
+        <v>Somebody</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
+        <v>https://music.apple.com/us/song/somebody/1873193244</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-19</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>BIG FEELING (NO MAKEUP) - Single</v>
+        <v>Somebody - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>1:55</v>
+        <v>3:23</v>
       </c>
       <c r="H45" t="str">
-        <v>BKTHERULA</v>
+        <v>Jamie Foxx</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
+        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
+        <v>https://music.apple.com/us/album/somebody/1873193243</v>
       </c>
       <c r="L45" t="str">
-        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
+        <v>Somebody - Jamie Foxx</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>On and On</v>
+        <v>BIG FEELING (NO MAKEUP)</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
+        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-19</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Work of Heart</v>
+        <v>BIG FEELING (NO MAKEUP) - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>3:43</v>
+        <v>1:55</v>
       </c>
       <c r="H46" t="str">
-        <v>Flatland Cavalry</v>
+        <v>BKTHERULA</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
+        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
       </c>
       <c r="L46" t="str">
-        <v>On and On - Flatland Cavalry</v>
+        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Push My Luck</v>
+        <v>On and On</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
+        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-19</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Push My Luck / All I Ever Need - EP</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G47" t="str">
-        <v>2:44</v>
+        <v>3:43</v>
       </c>
       <c r="H47" t="str">
-        <v>Cold War Kids</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
+        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
       </c>
       <c r="L47" t="str">
-        <v>Push My Luck - Cold War Kids</v>
+        <v>On and On - Flatland Cavalry</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Memphis Players</v>
+        <v>Push My Luck</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
+        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-19</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>AK Cuts: Vol. 2 - EP</v>
+        <v>Push My Luck / All I Ever Need - EP</v>
       </c>
       <c r="G48" t="str">
-        <v>2:46</v>
+        <v>2:44</v>
       </c>
       <c r="H48" t="str">
-        <v>Anish Kumar</v>
+        <v>Cold War Kids</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
+        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
       </c>
       <c r="L48" t="str">
-        <v>Memphis Players - Anish Kumar</v>
+        <v>Push My Luck - Cold War Kids</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Somebody</v>
+        <v>Memphis Players</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873982451</v>
+        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-19</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Blue Sky Mentality (Complete Edition)</v>
+        <v>AK Cuts: Vol. 2 - EP</v>
       </c>
       <c r="G49" t="str">
-        <v>2:49</v>
+        <v>2:46</v>
       </c>
       <c r="H49" t="str">
-        <v>Good Neighbours</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873982325</v>
+        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
       </c>
       <c r="L49" t="str">
-        <v>Somebody - Good Neighbours</v>
+        <v>Memphis Players - Anish Kumar</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>If I Didn't Know You</v>
+        <v>Somebody</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
+        <v>https://music.apple.com/us/song/somebody/1873982451</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-19</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>If I Didn't Know You - Single</v>
+        <v>Blue Sky Mentality (Complete Edition)</v>
       </c>
       <c r="G50" t="str">
-        <v>3:28</v>
+        <v>2:49</v>
       </c>
       <c r="H50" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Good Neighbours</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
+        <v>https://music.apple.com/us/album/somebody/1873982325</v>
       </c>
       <c r="L50" t="str">
-        <v>If I Didn't Know You - The Red Clay Strays</v>
+        <v>Somebody - Good Neighbours</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Seven Seas</v>
+        <v>If I Didn't Know You</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
+        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-19</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Seven Seas - Single</v>
+        <v>If I Didn't Know You - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>3:01</v>
+        <v>3:28</v>
       </c>
       <c r="H51" t="str">
-        <v>Dirty Heads</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
+        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
       </c>
       <c r="L51" t="str">
-        <v>Seven Seas - Dirty Heads</v>
+        <v>If I Didn't Know You - The Red Clay Strays</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>1000 Ways</v>
+        <v>Seven Seas</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
+        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-19</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>A Love For Strangers</v>
+        <v>Seven Seas - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>4:04</v>
+        <v>3:01</v>
       </c>
       <c r="H52" t="str">
-        <v>Chet Faker</v>
+        <v>Dirty Heads</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
+        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
       </c>
       <c r="L52" t="str">
-        <v>1000 Ways - Chet Faker</v>
+        <v>Seven Seas - Dirty Heads</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Beatback</v>
+        <v>1000 Ways</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/beatback/1861895138</v>
+        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-19</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Ö</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G53" t="str">
-        <v>2:19</v>
+        <v>4:04</v>
       </c>
       <c r="H53" t="str">
-        <v>Fcukers</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/beatback/1861895134</v>
+        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
       </c>
       <c r="L53" t="str">
-        <v>Beatback - Fcukers</v>
+        <v>1000 Ways - Chet Faker</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>GANG</v>
+        <v>Beatback</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/gang/1872243101</v>
+        <v>https://music.apple.com/us/song/beatback/1861895138</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-19</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>GANG - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G54" t="str">
-        <v>3:44</v>
+        <v>2:19</v>
       </c>
       <c r="H54" t="str">
-        <v>Tink</v>
+        <v>Fcukers</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/gang/1872243100</v>
+        <v>https://music.apple.com/us/album/beatback/1861895134</v>
       </c>
       <c r="L54" t="str">
-        <v>GANG - Tink</v>
+        <v>Beatback - Fcukers</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>a love song for u</v>
+        <v>GANG</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
+        <v>https://music.apple.com/us/song/gang/1872243101</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-19</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>a love song for u - EP</v>
+        <v>GANG - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>1:40</v>
+        <v>3:44</v>
       </c>
       <c r="H55" t="str">
-        <v>Eem Triplin</v>
+        <v>Tink</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
+        <v>https://music.apple.com/us/album/gang/1872243100</v>
       </c>
       <c r="L55" t="str">
-        <v>a love song for u - Eem Triplin</v>
+        <v>GANG - Tink</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>See Through</v>
+        <v>a love song for u</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/see-through/1840712229</v>
+        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-19</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>A.R.S.O.N.</v>
+        <v>a love song for u - EP</v>
       </c>
       <c r="G56" t="str">
-        <v>2:38</v>
+        <v>1:40</v>
       </c>
       <c r="H56" t="str">
-        <v>Story of the Year</v>
+        <v>Eem Triplin</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
+        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/see-through/1840712224</v>
+        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
       </c>
       <c r="L56" t="str">
-        <v>See Through - Story of the Year</v>
+        <v>a love song for u - Eem Triplin</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>be the girl!</v>
+        <v>See Through</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/be-the-girl/1877161731</v>
+        <v>https://music.apple.com/us/song/see-through/1840712229</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-19</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>the apple tree under the sea</v>
+        <v>A.R.S.O.N.</v>
       </c>
       <c r="G57" t="str">
-        <v>5:33</v>
+        <v>2:38</v>
       </c>
       <c r="H57" t="str">
-        <v>hemlocke springs</v>
+        <v>Story of the Year</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/be-the-girl/1877161526</v>
+        <v>https://music.apple.com/us/album/see-through/1840712224</v>
       </c>
       <c r="L57" t="str">
-        <v>be the girl! - hemlocke springs</v>
+        <v>See Through - Story of the Year</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>be the girl!</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/be-the-girl/1877161731</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-19</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G58" t="str">
-        <v>3:33</v>
+        <v>5:33</v>
       </c>
       <c r="H58" t="str">
-        <v>Erin LeCount</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/be-the-girl/1877161526</v>
       </c>
       <c r="L58" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>be the girl! - hemlocke springs</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>DON’T YOU SEE ME TRYING?</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-19</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>DON’T YOU SEE ME TRYING? - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>3:40</v>
+        <v>3:33</v>
       </c>
       <c r="H59" t="str">
-        <v>Kid Sistr</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
       </c>
       <c r="L59" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ARCADE</v>
+        <v>American Teenage Prophecy</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-19</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>ARCADE - Single</v>
+        <v>American Teenage Prophecy - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>2:52</v>
+        <v>3:40</v>
       </c>
       <c r="H60" t="str">
-        <v>Deb Never</v>
+        <v>Kid Sistr</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
       </c>
       <c r="L60" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>American Teenage Prophecy - Kid Sistr</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Girls Just Wanna</v>
+        <v>ARCADE</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/arcade/1870715147</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-19</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Girlhood - EP</v>
+        <v>ARCADE - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>2:16</v>
+        <v>2:52</v>
       </c>
       <c r="H61" t="str">
-        <v>Morgan St. Jean</v>
+        <v>Deb Never</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/arcade/1870715146</v>
       </c>
       <c r="L61" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>ARCADE - Deb Never</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>you special.</v>
+        <v>Girls Just Wanna</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-19</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>you special. - Single</v>
+        <v>Girlhood - EP</v>
       </c>
       <c r="G62" t="str">
-        <v>2:08</v>
+        <v>2:16</v>
       </c>
       <c r="H62" t="str">
-        <v>YFN Lucci</v>
+        <v>Morgan St. Jean</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
       </c>
       <c r="L62" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Girls Just Wanna - Morgan St. Jean</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Bass Dhol</v>
+        <v>you special.</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/you-special/1875125174</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-19</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>you special. - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>3:38</v>
+        <v>2:08</v>
       </c>
       <c r="H63" t="str">
-        <v>Ahadadream</v>
+        <v>YFN Lucci</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/you-special/1875125170</v>
       </c>
       <c r="L63" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>you special. - YFN Lucci</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>Bass Dhol</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-19</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>Bass Dhol - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>3:31</v>
+        <v>3:38</v>
       </c>
       <c r="H64" t="str">
-        <v>Charles Kelley</v>
+        <v>Ahadadream</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
       </c>
       <c r="L64" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>Bass Dhol - Ahadadream</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>If I See Her Again</v>
+        <v>Can't Be Alone Tonight</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-19</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Can't Be Alone Tonight - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>2:43</v>
+        <v>3:31</v>
       </c>
       <c r="H65" t="str">
-        <v>Maddox Batson</v>
+        <v>Charles Kelley</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
       </c>
       <c r="L65" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>Can't Be Alone Tonight - Charles Kelley</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>If I See Her Again</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-19</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Under The Sun</v>
+        <v>If I See Her Again - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>4:43</v>
+        <v>2:43</v>
       </c>
       <c r="H66" t="str">
-        <v>Sun-El Musician</v>
+        <v>Maddox Batson</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
       </c>
       <c r="L66" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>If I See Her Again - Maddox Batson</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>To B Honest</v>
+        <v>I’ll Be There (For You)</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-19</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>To Whom This May Concern</v>
+        <v>Under The Sun</v>
       </c>
       <c r="G67" t="str">
-        <v>4:30</v>
+        <v>4:43</v>
       </c>
       <c r="H67" t="str">
-        <v>Jill Scott</v>
+        <v>Sun-El Musician</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
       </c>
       <c r="L67" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>I’ll Be There (For You) - Sun-El Musician</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>lil xan goes to washington</v>
+        <v>To B Honest</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-19</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>the beltway is burning</v>
+        <v>To Whom This May Concern</v>
       </c>
       <c r="G68" t="str">
-        <v>2:41</v>
+        <v>4:30</v>
       </c>
       <c r="H68" t="str">
-        <v>Ekko Astral</v>
+        <v>Jill Scott</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
       </c>
       <c r="L68" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>To B Honest - Jill Scott</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Koneko</v>
+        <v>lil xan goes to washington</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-19</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Kurage - Single</v>
+        <v>the beltway is burning</v>
       </c>
       <c r="G69" t="str">
-        <v>4:08</v>
+        <v>2:41</v>
       </c>
       <c r="H69" t="str">
-        <v>Liana Flores</v>
+        <v>Ekko Astral</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
       </c>
       <c r="L69" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>lil xan goes to washington - Ekko Astral</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Cupid's Call</v>
+        <v>Koneko</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/koneko/1867318937</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-19</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Kurage - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>2:58</v>
+        <v>4:08</v>
       </c>
       <c r="H70" t="str">
-        <v>Dizzy Fae</v>
+        <v>Liana Flores</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/koneko/1867318935</v>
       </c>
       <c r="L70" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Koneko - Liana Flores</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Come Back 2 Me</v>
+        <v>Cupid's Call</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-19</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>Cupid's Call - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:13</v>
+        <v>2:58</v>
       </c>
       <c r="H71" t="str">
-        <v>Chloé Caillet</v>
+        <v>Dizzy Fae</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
       </c>
       <c r="L71" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>Cupid's Call - Dizzy Fae</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Pop Off</v>
+        <v>Come Back 2 Me</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-19</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Pop Off - Single</v>
+        <v>Come Back 2 Me - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:16</v>
+        <v>3:13</v>
       </c>
       <c r="H72" t="str">
-        <v>GRiZ</v>
+        <v>Chloé Caillet</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
       </c>
       <c r="L72" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>Come Back 2 Me - Chloé Caillet</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>dreams</v>
+        <v>Pop Off</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-19</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>dreams - Single</v>
+        <v>Pop Off - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>3:31</v>
+        <v>3:16</v>
       </c>
       <c r="H73" t="str">
-        <v>Azzecca</v>
+        <v>GRiZ</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
       </c>
       <c r="L73" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Pop Off - GRiZ</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Love Hate Love</v>
+        <v>dreams</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/dreams/1871138304</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-19</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>dreams - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:55</v>
+        <v>3:31</v>
       </c>
       <c r="H74" t="str">
-        <v>Owen Riegling</v>
+        <v>Azzecca</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/dreams/1871138302</v>
       </c>
       <c r="L74" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>dreams - Azzecca</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Do It All Alone</v>
+        <v>Love Hate Love</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-19</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Love Hate Love - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>2:52</v>
+        <v>2:55</v>
       </c>
       <c r="H75" t="str">
-        <v>Rend Collective</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
       </c>
       <c r="L75" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Love Hate Love - Owen Riegling</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>She Makes Me Real</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-19</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Masquerade</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>2:58</v>
+        <v>2:52</v>
       </c>
       <c r="H76" t="str">
-        <v>Cardinals</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
       </c>
       <c r="L76" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Steady</v>
+        <v>She Makes Me Real</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-19</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>Masquerade</v>
       </c>
       <c r="G77" t="str">
-        <v>3:26</v>
+        <v>2:58</v>
       </c>
       <c r="H77" t="str">
-        <v>Bella Kay</v>
+        <v>Cardinals</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
       </c>
       <c r="L77" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>She Makes Me Real - Cardinals</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>DIRTY TECH</v>
+        <v>Steady</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/steady/1874718519</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-19</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>PLAY ME</v>
+        <v>a couple minutes out - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>2:20</v>
+        <v>3:26</v>
       </c>
       <c r="H78" t="str">
-        <v>Kim Gordon</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/steady/1874718231</v>
       </c>
       <c r="L78" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>Steady - Bella Kay</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Nada Más</v>
+        <v>DIRTY TECH</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-19</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Nada Más - Single</v>
+        <v>PLAY ME</v>
       </c>
       <c r="G79" t="str">
-        <v>2:19</v>
+        <v>2:20</v>
       </c>
       <c r="H79" t="str">
-        <v>Tombochio</v>
+        <v>Kim Gordon</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
       </c>
       <c r="L79" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>DIRTY TECH - Kim Gordon</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Friends Again</v>
+        <v>Nada Más</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-19</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Friends Again - Single</v>
+        <v>Nada Más - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:38</v>
+        <v>2:19</v>
       </c>
       <c r="H80" t="str">
-        <v>Baby Rose</v>
+        <v>Tombochio</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
       </c>
       <c r="L80" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>Nada Más - Tombochio</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>W.T.A.</v>
+        <v>Friends Again</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-19</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>W.T.A. - Single</v>
+        <v>Friends Again - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:22</v>
+        <v>3:38</v>
       </c>
       <c r="H81" t="str">
-        <v>Isaia Huron</v>
+        <v>Baby Rose</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
       </c>
       <c r="L81" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>Friends Again - Baby Rose</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>desire.</v>
+        <v>W.T.A.</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-19</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>November Scorpio</v>
+        <v>W.T.A. - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:15</v>
+        <v>3:22</v>
       </c>
       <c r="H82" t="str">
-        <v>Tiana Major9</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
       </c>
       <c r="L82" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>W.T.A. - Isaia Huron</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>desire.</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/desire/1846171015</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-19</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>November Scorpio</v>
       </c>
       <c r="G83" t="str">
-        <v>3:12</v>
+        <v>3:15</v>
       </c>
       <c r="H83" t="str">
-        <v>August Ponthier</v>
+        <v>Tiana Major9</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/desire/1846170591</v>
       </c>
       <c r="L83" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>desire. - Tiana Major9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Killer Whale</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-19</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Killer Whale - Single</v>
+        <v>Everywhere Isn't Texas</v>
       </c>
       <c r="G84" t="str">
-        <v>4:00</v>
+        <v>3:12</v>
       </c>
       <c r="H84" t="str">
-        <v>Hayden Everett</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
       </c>
       <c r="L84" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Everywhere Isn't Texas - August Ponthier</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Waits for Me</v>
+        <v>Killer Whale</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-19</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>You’re Free to Go</v>
+        <v>Killer Whale - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>2:46</v>
+        <v>4:00</v>
       </c>
       <c r="H85" t="str">
-        <v>Anjimile</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
       </c>
       <c r="L85" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Killer Whale - Hayden Everett</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Man's World</v>
+        <v>Waits for Me</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-19</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Mud Blood Bone</v>
+        <v>You’re Free to Go</v>
       </c>
       <c r="G86" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H86" t="str">
-        <v>Cat Clyde</v>
+        <v>Anjimile</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
       </c>
       <c r="L86" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>Waits for Me - Anjimile</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>In the Middle of It</v>
+        <v>Man's World</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-19</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>Mud Blood Bone</v>
       </c>
       <c r="G87" t="str">
-        <v>3:13</v>
+        <v>2:42</v>
       </c>
       <c r="H87" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Cat Clyde</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
       </c>
       <c r="L87" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>Man's World - Cat Clyde</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>In the Middle of It</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-19</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Fleeting - EP</v>
+        <v>In the Middle of It - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>2:51</v>
+        <v>3:13</v>
       </c>
       <c r="H88" t="str">
-        <v>Sarah Kinsley</v>
+        <v>Hiss Golden Messenger</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
       </c>
       <c r="L88" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>In the Middle of It - Hiss Golden Messenger</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>Truth Of Pursuit</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-19</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>Fleeting - EP</v>
       </c>
       <c r="G89" t="str">
-        <v>5:23</v>
+        <v>2:51</v>
       </c>
       <c r="H89" t="str">
-        <v>BUNT.</v>
+        <v>Sarah Kinsley</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
       </c>
       <c r="L89" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>Truth Of Pursuit - Sarah Kinsley</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>I've Never Met Her</v>
+        <v>What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-19</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>What If You Fly (Sweet Disposition) - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>3:07</v>
+        <v>5:23</v>
       </c>
       <c r="H90" t="str">
-        <v>Ally Salort</v>
+        <v>BUNT.</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
       </c>
       <c r="L90" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>I've Never Met Her</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-19</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>The Elephant</v>
+        <v>I've Never Met Her - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>3:28</v>
+        <v>3:07</v>
       </c>
       <c r="H91" t="str">
-        <v>Ledbyher</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
       </c>
       <c r="L91" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
+        <v>I've Never Met Her - Ally Salort</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Yes</v>
+        <v>BACKWARDS, INTO U</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
+        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-19</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Just A Few Folk</v>
+        <v>The Elephant</v>
       </c>
       <c r="G92" t="str">
-        <v>3:21</v>
+        <v>3:28</v>
       </c>
       <c r="H92" t="str">
-        <v>JP Cooper</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
+        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
       </c>
       <c r="L92" t="str">
-        <v>Yes - JP Cooper</v>
+        <v>BACKWARDS, INTO U - Ledbyher</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>CHOKEHOLD</v>
+        <v>Yes</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
+        <v>https://music.apple.com/us/song/yes/1849157719</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-19</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>CHOKEHOLD - Single</v>
+        <v>Just A Few Folk</v>
       </c>
       <c r="G93" t="str">
-        <v>2:52</v>
+        <v>3:21</v>
       </c>
       <c r="H93" t="str">
-        <v>WesGhost</v>
+        <v>JP Cooper</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
+        <v>https://music.apple.com/us/album/yes/1849157442</v>
       </c>
       <c r="L93" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
+        <v>Yes - JP Cooper</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Bad Faith</v>
+        <v>CHOKEHOLD</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
+        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-19</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Love Is Not Enough</v>
+        <v>CHOKEHOLD - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H94" t="str">
-        <v>Converge</v>
+        <v>WesGhost</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
+        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
       </c>
       <c r="L94" t="str">
-        <v>Bad Faith - Converge</v>
+        <v>CHOKEHOLD - WesGhost</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Gimme Some Moore</v>
+        <v>Bad Faith</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
+        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-19</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Love Is Not Enough</v>
       </c>
       <c r="G95" t="str">
-        <v>4:00</v>
+        <v>2:48</v>
       </c>
       <c r="H95" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Converge</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
+        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
       </c>
       <c r="L95" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
+        <v>Bad Faith - Converge</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Angel Eyes</v>
+        <v>Gimme Some Moore</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-19</v>
@@ -4023,68 +4023,106 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>God Forgives - Single</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G96" t="str">
-        <v>2:14</v>
+        <v>4:00</v>
       </c>
       <c r="H96" t="str">
-        <v>Guilt Trip</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
       </c>
       <c r="L96" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
+        <v>Gimme Some Moore - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
+        <v>Angel Eyes</v>
+      </c>
+      <c r="B97" t="str">
+        <v/>
+      </c>
+      <c r="C97" t="str">
+        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
+      </c>
+      <c r="D97" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v>God Forgives - Single</v>
+      </c>
+      <c r="G97" t="str">
+        <v>2:14</v>
+      </c>
+      <c r="H97" t="str">
+        <v>Guilt Trip</v>
+      </c>
+      <c r="I97" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J97" t="str">
+        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
+      </c>
+      <c r="K97" t="str">
+        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
+      </c>
+      <c r="L97" t="str">
+        <v>Angel Eyes - Guilt Trip</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
         <v>Tossing Coins Into The Fountain Of F**k</v>
       </c>
-      <c r="B97" t="str">
-        <v/>
-      </c>
-      <c r="C97" t="str">
+      <c r="B98" t="str">
+        <v/>
+      </c>
+      <c r="C98" t="str">
         <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
       </c>
-      <c r="D97" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E97" t="str">
-        <v/>
-      </c>
-      <c r="F97" t="str">
+      <c r="D98" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
         <v>Savage Imperial Death March</v>
       </c>
-      <c r="G97" t="str">
+      <c r="G98" t="str">
         <v>3:17</v>
       </c>
-      <c r="H97" t="str">
+      <c r="H98" t="str">
         <v>Melvins</v>
       </c>
-      <c r="I97" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J97" t="str">
+      <c r="I98" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J98" t="str">
         <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
-      <c r="K97" t="str">
+      <c r="K98" t="str">
         <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
       </c>
-      <c r="L97" t="str">
+      <c r="L98" t="str">
         <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L97"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L98"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L98"/>
+  <dimension ref="A1:L94"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,78 +436,78 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Badlands</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/your-favorite-toy/1877913734</v>
+        <v>https://music.apple.com/us/song/badlands/1848218132</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Prizefighter</v>
       </c>
       <c r="G2" t="str">
-        <v>2:56</v>
+        <v>2:58</v>
       </c>
       <c r="H2" t="str">
-        <v>Foo Fighters</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/your-favorite-toy/1877913489</v>
+        <v>https://music.apple.com/us/album/badlands/1848218113</v>
       </c>
       <c r="L2" t="str">
-        <v>Your Favorite Toy - Foo Fighters</v>
+        <v>Badlands - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Always Everywhere</v>
+        <v>Opalite (Chris Lake Remix)</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://music.apple.com/us/song/always-everywhere/1852566433</v>
+        <v>https://music.apple.com/us/song/opalite-chris-lake-remix/1878187199</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>Wuthering Heights</v>
+        <v>Opalite (Chris Lake Remix) - Single</v>
       </c>
       <c r="G3" t="str">
-        <v>3:03</v>
+        <v>3:48</v>
       </c>
       <c r="H3" t="str">
-        <v>Charli xcx</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K3" t="str">
-        <v>https://music.apple.com/us/album/always-everywhere/1852566184</v>
+        <v>https://music.apple.com/us/album/opalite-chris-lake-remix/1878187190</v>
       </c>
       <c r="L3" t="str">
-        <v>Always Everywhere - Charli xcx</v>
+        <v>Opalite (Chris Lake Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="4">
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -550,1750 +550,1750 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Be Her</v>
+        <v>ROSITA</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/be-her/1869436845</v>
+        <v>https://music.apple.com/us/song/rosita/1877264687</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>Dandelion</v>
+        <v>ROSITA - Single</v>
       </c>
       <c r="G5" t="str">
-        <v>3:37</v>
+        <v>4:05</v>
       </c>
       <c r="H5" t="str">
-        <v>Ella Langley</v>
+        <v>Tainy</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/tainy/193167653</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/be-her/1869436835</v>
+        <v>https://music.apple.com/us/album/rosita/1877264686</v>
       </c>
       <c r="L5" t="str">
-        <v>Be Her - Ella Langley</v>
+        <v>ROSITA - Tainy</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>other side.</v>
+        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd)</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/other-side/1867923704</v>
+        <v>https://music.apple.com/us/song/good-flirts-feat-kendrick-lamar-momo-boyd/1878400231</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>Icon</v>
+        <v>Ca$ino</v>
       </c>
       <c r="G6" t="str">
-        <v>3:15</v>
+        <v>3:52</v>
       </c>
       <c r="H6" t="str">
-        <v>Brent Faiyaz</v>
+        <v>Baby Keem</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/baby-keem/1413572916</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/other-side/1867923697</v>
+        <v>https://music.apple.com/us/album/good-flirts-feat-kendrick-lamar-momo-boyd/1878399948</v>
       </c>
       <c r="L6" t="str">
-        <v>other side. - Brent Faiyaz</v>
+        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd) - Baby Keem</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SHADOWS</v>
+        <v>Save The Day (From "Hoppers")</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/shadows/1875373696</v>
+        <v>https://music.apple.com/us/song/save-the-day-from-hoppers/1877213780</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>SHADOWS - Single</v>
+        <v>Save The Day (From "Hoppers") - Single</v>
       </c>
       <c r="G7" t="str">
-        <v>3:22</v>
+        <v>2:52</v>
       </c>
       <c r="H7" t="str">
-        <v>John Summit</v>
+        <v>SZA</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/sza/605800394</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/shadows/1875373695</v>
+        <v>https://music.apple.com/us/album/save-the-day-from-hoppers/1877213779</v>
       </c>
       <c r="L7" t="str">
-        <v>SHADOWS - John Summit</v>
+        <v>Save The Day (From "Hoppers") - SZA</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Mention Me (From The Movie "GOAT")</v>
+        <v>Medicine</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/mention-me-from-the-movie-goat/1870623628</v>
+        <v>https://music.apple.com/us/song/medicine/1851297056</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G8" t="str">
-        <v>3:00</v>
+        <v>3:11</v>
       </c>
       <c r="H8" t="str">
-        <v>CORTIS</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/mention-me-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/medicine/1851296746</v>
       </c>
       <c r="L8" t="str">
-        <v>Mention Me (From The Movie "GOAT") - CORTIS</v>
+        <v>Medicine - Megan Moroney</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Trimski</v>
+        <v>Weather For Tennis</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/trimski/1876695030</v>
+        <v>https://music.apple.com/us/song/weather-for-tennis/1854567104</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Trimski - Single</v>
+        <v>luck... or something</v>
       </c>
       <c r="G9" t="str">
-        <v>3:02</v>
+        <v>3:16</v>
       </c>
       <c r="H9" t="str">
-        <v>NAV</v>
+        <v>Hilary Duff</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/nav/1200089113</v>
+        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/trimski/1876695024</v>
+        <v>https://music.apple.com/us/album/weather-for-tennis/1854567102</v>
       </c>
       <c r="L9" t="str">
-        <v>Trimski - NAV</v>
+        <v>Weather For Tennis - Hilary Duff</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>I Had a Dream She Took My Hand</v>
+        <v>ear to the cocoon</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream-she-took-my-hand/1862353791</v>
+        <v>https://music.apple.com/us/song/ear-to-the-cocoon/1872767745</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>Trying Times</v>
+        <v>petal rock black</v>
       </c>
       <c r="G10" t="str">
-        <v>3:40</v>
+        <v>4:18</v>
       </c>
       <c r="H10" t="str">
-        <v>James Blake</v>
+        <v>WILLOW</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream-she-took-my-hand/1862353780</v>
+        <v>https://music.apple.com/us/album/ear-to-the-cocoon/1872767488</v>
       </c>
       <c r="L10" t="str">
-        <v>I Had a Dream She Took My Hand - James Blake</v>
+        <v>ear to the cocoon - WILLOW</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Paracosm</v>
+        <v>Drag Path</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
+        <v>https://music.apple.com/us/song/drag-path/1876977596</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>Paracosm</v>
+        <v>Drag Path - Single</v>
       </c>
       <c r="G11" t="str">
-        <v>3:23</v>
+        <v>3:44</v>
       </c>
       <c r="H11" t="str">
-        <v>Absolutely</v>
+        <v>twenty one pilots</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
+        <v>https://music.apple.com/us/artist/twenty-one-pilots/349736311</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
+        <v>https://music.apple.com/us/album/drag-path/1876977594</v>
       </c>
       <c r="L11" t="str">
-        <v>Paracosm - Absolutely</v>
+        <v>Drag Path - twenty one pilots</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Let Me</v>
+        <v>Song Of The Future</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/let-me/1874386210</v>
+        <v>https://music.apple.com/us/song/song-of-the-future/1875348244</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>Let Me - Single</v>
+        <v>Days Of Ash - EP</v>
       </c>
       <c r="G12" t="str">
-        <v>4:51</v>
+        <v>3:55</v>
       </c>
       <c r="H12" t="str">
-        <v>Victoria Monét</v>
+        <v>U2</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/victoria-mon%C3%A9t/540070252</v>
+        <v>https://music.apple.com/us/artist/u2/78500</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/let-me/1874386209</v>
+        <v>https://music.apple.com/us/album/song-of-the-future/1875348241</v>
       </c>
       <c r="L12" t="str">
-        <v>Let Me - Victoria Monét</v>
+        <v>Song Of The Future - U2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Casual Lady</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
+        <v>https://music.apple.com/us/song/your-favorite-toy/1877913734</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Casual Lady - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G13" t="str">
-        <v>3:14</v>
+        <v>2:56</v>
       </c>
       <c r="H13" t="str">
-        <v>flowerovlove</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
+        <v>https://music.apple.com/us/album/your-favorite-toy/1877913489</v>
       </c>
       <c r="L13" t="str">
-        <v>Casual Lady - flowerovlove</v>
+        <v>Your Favorite Toy - Foo Fighters</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Woman In Love</v>
+        <v>Trimski</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/woman-in-love/1872963291</v>
+        <v>https://music.apple.com/us/song/trimski/1876695030</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Woman In Love - Single</v>
+        <v>Trimski - Single</v>
       </c>
       <c r="G14" t="str">
-        <v>2:43</v>
+        <v>3:02</v>
       </c>
       <c r="H14" t="str">
-        <v>Perrie</v>
+        <v>NAV</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/perrie/1729865272</v>
+        <v>https://music.apple.com/us/artist/nav/1200089113</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/woman-in-love/1872963288</v>
+        <v>https://music.apple.com/us/album/trimski/1876695024</v>
       </c>
       <c r="L14" t="str">
-        <v>Woman In Love - Perrie</v>
+        <v>Trimski - NAV</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Paracosm</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/dancing-on-the-wall/1870702698</v>
+        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Paracosm</v>
       </c>
       <c r="G15" t="str">
-        <v>4:03</v>
+        <v>3:23</v>
       </c>
       <c r="H15" t="str">
-        <v>MUNA</v>
+        <v>Absolutely</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/dancing-on-the-wall/1870702692</v>
+        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
       </c>
       <c r="L15" t="str">
-        <v>Dancing On The Wall - MUNA</v>
+        <v>Paracosm - Absolutely</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Adrenaline (NO1 Ver.)</v>
+        <v>Casual Lady</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/adrenaline-no1-ver/1873860001</v>
+        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Adrenaline (Remix) - Single</v>
+        <v>Casual Lady - Single</v>
       </c>
       <c r="G16" t="str">
-        <v>3:18</v>
+        <v>3:14</v>
       </c>
       <c r="H16" t="str">
-        <v>ATEEZ</v>
+        <v>flowerovlove</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/adrenaline-no1-ver/1873859999</v>
+        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
       </c>
       <c r="L16" t="str">
-        <v>Adrenaline (NO1 Ver.) - ATEEZ</v>
+        <v>Casual Lady - flowerovlove</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ICEMAN FREESTYLE</v>
+        <v>Begging for Change</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/iceman-freestyle/1876663952</v>
+        <v>https://music.apple.com/us/song/begging-for-change/1870313832</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>ICEMAN FREESTYLE - Single</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G17" t="str">
-        <v>3:06</v>
+        <v>4:20</v>
       </c>
       <c r="H17" t="str">
-        <v>Central Cee</v>
+        <v>Pulp</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/central-cee/1085149646</v>
+        <v>https://music.apple.com/us/artist/pulp/312518</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/iceman-freestyle/1876663951</v>
+        <v>https://music.apple.com/us/album/begging-for-change/1870313498</v>
       </c>
       <c r="L17" t="str">
-        <v>ICEMAN FREESTYLE - Central Cee</v>
+        <v>Begging for Change - Pulp</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Mírame Baby</v>
+        <v>My Maker</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/m%C3%ADrame-baby/1876677814</v>
+        <v>https://music.apple.com/us/song/my-maker/1862845748</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Mírame Baby - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G18" t="str">
-        <v>3:59</v>
+        <v>4:19</v>
       </c>
       <c r="H18" t="str">
-        <v>Arcángel</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/m%C3%ADrame-baby/1876677811</v>
+        <v>https://music.apple.com/us/album/my-maker/1862845733</v>
       </c>
       <c r="L18" t="str">
-        <v>Mírame Baby - Arcángel</v>
+        <v>My Maker - Snail Mail</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Lights Burn Dimmer</v>
+        <v>Opalite (BUNT. Remix)</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/lights-burn-dimmer/1874902790</v>
+        <v>https://music.apple.com/us/song/opalite-bunt-remix/1878183696</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Lights Burn Dimmer - Single</v>
+        <v>Opalite (BUNT. Remix) - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>4:20</v>
+        <v>3:32</v>
       </c>
       <c r="H19" t="str">
-        <v>Fred again..</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/lights-burn-dimmer/1874902788</v>
+        <v>https://music.apple.com/us/album/opalite-bunt-remix/1878183335</v>
       </c>
       <c r="L19" t="str">
-        <v>Lights Burn Dimmer - Fred again..</v>
+        <v>Opalite (BUNT. Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Two Hearts</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)")</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/two-hearts/1847663423</v>
+        <v>https://music.apple.com/us/song/such-great-heights-from-tell-me-lies-season-3/1872222695</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Cerulean</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>3:52</v>
+        <v>4:27</v>
       </c>
       <c r="H20" t="str">
-        <v>Danny L Harle</v>
+        <v>CHVRCHES</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/two-hearts/1847662970</v>
+        <v>https://music.apple.com/us/album/such-great-heights-from-tell-me-lies-season-3/1872222683</v>
       </c>
       <c r="L20" t="str">
-        <v>Two Hearts - Danny L Harle</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Be By You</v>
+        <v>She Knows Too Much</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/be-by-you/1862634805</v>
+        <v>https://music.apple.com/us/song/she-knows-too-much/1861531670</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>The Way I Am</v>
+        <v>Distracted</v>
       </c>
       <c r="G21" t="str">
-        <v>3:17</v>
+        <v>3:33</v>
       </c>
       <c r="H21" t="str">
-        <v>Luke Combs</v>
+        <v>Thundercat</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/be-by-you/1862634688</v>
+        <v>https://music.apple.com/us/album/she-knows-too-much/1861531667</v>
       </c>
       <c r="L21" t="str">
-        <v>Be By You - Luke Combs</v>
+        <v>She Knows Too Much - Thundercat</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>you and forever</v>
+        <v>Tea Time</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/you-and-forever/1872842319</v>
+        <v>https://music.apple.com/us/song/tea-time/1877002914</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Tea Time - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>3:54</v>
+        <v>2:25</v>
       </c>
       <c r="H22" t="str">
-        <v>Bleachers</v>
+        <v>Yung Miami</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/yung-miami/1476226954</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/you-and-forever/1872842313</v>
+        <v>https://music.apple.com/us/album/tea-time/1877002906</v>
       </c>
       <c r="L22" t="str">
-        <v>you and forever - Bleachers</v>
+        <v>Tea Time - Yung Miami</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ROOMS</v>
+        <v>full moon. (fall in tokyo) [bonus track]</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/rooms/1874675856</v>
+        <v>https://music.apple.com/us/song/full-moon-fall-in-tokyo-bonus-track/1877180113</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>ROOMS - Single</v>
+        <v>Icon (Director's Cut)</v>
       </c>
       <c r="G23" t="str">
-        <v>3:52</v>
+        <v>3:12</v>
       </c>
       <c r="H23" t="str">
-        <v>Mike WiLL Made-It</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/rooms/1874675853</v>
+        <v>https://music.apple.com/us/album/full-moon-fall-in-tokyo-bonus-track/1877179580</v>
       </c>
       <c r="L23" t="str">
-        <v>ROOMS - Mike WiLL Made-It</v>
+        <v>full moon. (fall in tokyo) [bonus track] - Brent Faiyaz</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>I Just Might (Austin Millz Remix)</v>
+        <v>Save My Love</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/i-just-might-austin-millz-remix/1876674174</v>
+        <v>https://music.apple.com/us/song/save-my-love/1876235280</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>I Just Might (Austin Millz Remix) - Single</v>
+        <v>Save My Love - Single</v>
       </c>
       <c r="G24" t="str">
-        <v>3:16</v>
+        <v>3:30</v>
       </c>
       <c r="H24" t="str">
-        <v>Bruno Mars</v>
+        <v>Kygo</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/i-just-might-austin-millz-remix/1876674173</v>
+        <v>https://music.apple.com/us/album/save-my-love/1876235273</v>
       </c>
       <c r="L24" t="str">
-        <v>I Just Might (Austin Millz Remix) - Bruno Mars</v>
+        <v>Save My Love - Kygo</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>MI$ LLAMADA$</v>
+        <v>FOREVER TU GANTEL</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/mi%24-llamada%24/1876715327</v>
+        <v>https://music.apple.com/us/song/forever-tu-gantel/1877482427</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>DEPR&lt;/3$$ED MFKZ</v>
+        <v>POR SI MAÑANA NO ESTOY</v>
       </c>
       <c r="G25" t="str">
-        <v>3:11</v>
+        <v>3:46</v>
       </c>
       <c r="H25" t="str">
-        <v>Junior H</v>
+        <v>Omar Courtz</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/junior-h/1442059565</v>
+        <v>https://music.apple.com/us/artist/omar-courtz/1370744631</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/mi%24-llamada%24/1876715320</v>
+        <v>https://music.apple.com/us/album/forever-tu-gantel/1877481995</v>
       </c>
       <c r="L25" t="str">
-        <v>MI$ LLAMADA$ - Junior H</v>
+        <v>FOREVER TU GANTEL - Omar Courtz</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Con el Corazón</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/con-el-coraz%C3%B3n/1876364732</v>
+        <v>https://music.apple.com/us/song/suburban-requiem/1874720791</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Con el Corazón - Single</v>
+        <v>Idols (Complete)</v>
       </c>
       <c r="G26" t="str">
-        <v>3:09</v>
+        <v>4:39</v>
       </c>
       <c r="H26" t="str">
-        <v>Maluma</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/yungblud/213048599</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/con-el-coraz%C3%B3n/1876364727</v>
+        <v>https://music.apple.com/us/album/suburban-requiem/1874720357</v>
       </c>
       <c r="L26" t="str">
-        <v>Con el Corazón - Maluma</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Get In Girl</v>
+        <v>Good Grief</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/get-in-girl/1852006223</v>
+        <v>https://music.apple.com/us/song/good-grief/1869516030</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Toy With Me</v>
+        <v>(((((ultraSOUND)))))+</v>
       </c>
       <c r="G27" t="str">
-        <v>3:26</v>
+        <v>4:21</v>
       </c>
       <c r="H27" t="str">
-        <v>Meghan Trainor</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/meghan-trainor/348580754</v>
+        <v>https://music.apple.com/us/artist/the-neighbourhood/219350813</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/get-in-girl/1852006222</v>
+        <v>https://music.apple.com/us/album/good-grief/1869516027</v>
       </c>
       <c r="L27" t="str">
-        <v>Get In Girl - Meghan Trainor</v>
+        <v>Good Grief - The Neighbourhood</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>London Foolishly</v>
+        <v>Freak On</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/london-foolishly/1873094039</v>
+        <v>https://music.apple.com/us/song/freak-on/1874265564</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Sunday Best (Deluxe)</v>
+        <v>Freak On - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>3:21</v>
+        <v>2:49</v>
       </c>
       <c r="H28" t="str">
-        <v>Nick Jonas</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/london-foolishly/1873093472</v>
+        <v>https://music.apple.com/us/album/freak-on/1874265561</v>
       </c>
       <c r="L28" t="str">
-        <v>London Foolishly - Nick Jonas</v>
+        <v>Freak On - Steve Aoki</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Thorns</v>
+        <v>Science (feat. Stevie Appleton) [Radio Edit]</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/thorns/1875330576</v>
+        <v>https://music.apple.com/us/song/science-feat-stevie-appleton-radio-edit/1871036143</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Thorns - Single</v>
+        <v>Science (feat. Stevie Appleton) - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>3:10</v>
+        <v>3:32</v>
       </c>
       <c r="H29" t="str">
-        <v>Jelly Roll</v>
+        <v>deadmau5</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/thorns/1875330145</v>
+        <v>https://music.apple.com/us/album/science-feat-stevie-appleton-radio-edit/1871036141</v>
       </c>
       <c r="L29" t="str">
-        <v>Thorns - Jelly Roll</v>
+        <v>Science (feat. Stevie Appleton) [Radio Edit] - deadmau5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Thinkin Bout You</v>
+        <v>Opalite (Skream Remix)</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/thinkin-bout-you/1861644320</v>
+        <v>https://music.apple.com/us/song/opalite-skream-remix/1878173708</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Honora</v>
+        <v>Opalite (Skream Remix) - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>4:10</v>
+        <v>3:55</v>
       </c>
       <c r="H30" t="str">
-        <v>Flea</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/thinkin-bout-you/1861644307</v>
+        <v>https://music.apple.com/us/album/opalite-skream-remix/1878173707</v>
       </c>
       <c r="L30" t="str">
-        <v>Thinkin Bout You - Flea</v>
+        <v>Opalite (Skream Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>JUICY</v>
+        <v>More Than A Lover</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/juicy/1869398762</v>
+        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>JUICY - Single</v>
+        <v>More Than A Lover - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>3:31</v>
+        <v>4:05</v>
       </c>
       <c r="H31" t="str">
-        <v>Lenny Tavárez</v>
+        <v>Mary J. Blige</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/lenny-tav%C3%A1rez/950466227</v>
+        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/juicy/1869398760</v>
+        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
       </c>
       <c r="L31" t="str">
-        <v>JUICY - Lenny Tavárez</v>
+        <v>More Than A Lover - Mary J. Blige</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>All They Type</v>
+        <v>Yellow Eyes</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/all-they-type/1874473046</v>
+        <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>All They Type - Single</v>
+        <v>Jean</v>
       </c>
       <c r="G32" t="str">
-        <v>2:52</v>
+        <v>2:42</v>
       </c>
       <c r="H32" t="str">
-        <v>Keke Palmer</v>
+        <v>Yebba</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/keke-palmer/136765925</v>
+        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/all-they-type/1874473045</v>
+        <v>https://music.apple.com/us/album/yellow-eyes/1877157664</v>
       </c>
       <c r="L32" t="str">
-        <v>All They Type - Keke Palmer</v>
+        <v>Yellow Eyes - Yebba</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>More Than A Lover</v>
+        <v>Word On The Street</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
+        <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>More Than A Lover - Single</v>
+        <v>Word On The Street - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>4:05</v>
+        <v>2:56</v>
       </c>
       <c r="H33" t="str">
-        <v>Mary J. Blige</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
+        <v>https://music.apple.com/us/album/word-on-the-street/1876607713</v>
       </c>
       <c r="L33" t="str">
-        <v>More Than A Lover - Mary J. Blige</v>
+        <v>Word On The Street - Luke Bryan</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>City</v>
+        <v>only the best</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/city/1847721298</v>
+        <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>My Lover</v>
+        <v>only the best - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>3:16</v>
+        <v>3:22</v>
       </c>
       <c r="H34" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/claire-rosinkranz/1483262366</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/city/1847721296</v>
+        <v>https://music.apple.com/us/album/only-the-best/1876048174</v>
       </c>
       <c r="L34" t="str">
-        <v>City - Claire Rosinkranz</v>
+        <v>only the best - horsegiirL</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Eyes Closed</v>
+        <v>miss u 2 (with Leon Thomas)</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/eyes-closed/1870981489</v>
+        <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G35" t="str">
-        <v>2:25</v>
+        <v>2:28</v>
       </c>
       <c r="H35" t="str">
-        <v>Mimi Webb</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/eyes-closed/1870981483</v>
+        <v>https://music.apple.com/us/album/miss-u-2-with-leon-thomas/1878416755</v>
       </c>
       <c r="L35" t="str">
-        <v>Eyes Closed - Mimi Webb</v>
+        <v>miss u 2 (with Leon Thomas) - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Go For Broke</v>
+        <v>ILRB (feat. Babyface Ray)</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/go-for-broke/1874444640</v>
+        <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Go For Broke - Single</v>
+        <v>Da Realest</v>
       </c>
       <c r="G36" t="str">
-        <v>2:50</v>
+        <v>1:51</v>
       </c>
       <c r="H36" t="str">
-        <v>Knox</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/knox/1547519433</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/go-for-broke/1874444096</v>
+        <v>https://music.apple.com/us/album/ilrb-feat-babyface-ray/1860991661</v>
       </c>
       <c r="L36" t="str">
-        <v>Go For Broke - Knox</v>
+        <v>ILRB (feat. Babyface Ray) - Babyfxce E</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>somebody you're supposed to love</v>
+        <v>Fine Shit</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/somebody-youre-supposed-to-love/1874356533</v>
+        <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>THE ART OF BEING A MESS (DELUXE)</v>
+        <v>Fine Shit - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>3:10</v>
+        <v>1:53</v>
       </c>
       <c r="H37" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Real Boston Richey</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/lauren-spencer-smith/1462708784</v>
+        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/somebody-youre-supposed-to-love/1874356359</v>
+        <v>https://music.apple.com/us/album/fine-shit/1878172115</v>
       </c>
       <c r="L37" t="str">
-        <v>somebody you're supposed to love - Lauren Spencer Smith</v>
+        <v>Fine Shit - Real Boston Richey</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Kentucky Too Long</v>
+        <v>What's Your Name</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/kentucky-too-long/1873097340</v>
+        <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Kentucky Too Long - Single</v>
+        <v>What's Your Name - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>3:38</v>
+        <v>2:20</v>
       </c>
       <c r="H38" t="str">
-        <v>Charley Crockett</v>
+        <v>Soulidified</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/soulidified/1824036220</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/kentucky-too-long/1873097339</v>
+        <v>https://music.apple.com/us/album/whats-your-name/1878121935</v>
       </c>
       <c r="L38" t="str">
-        <v>Kentucky Too Long - Charley Crockett</v>
+        <v>What's Your Name - Soulidified</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Somewhere Down in Georgia</v>
+        <v>Ends In Y</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/somewhere-down-in-georgia/1871309595</v>
+        <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Somewhere Down in Georgia - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G39" t="str">
-        <v>2:57</v>
+        <v>2:53</v>
       </c>
       <c r="H39" t="str">
-        <v>Mon Rovîa</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/somewhere-down-in-georgia/1871309593</v>
+        <v>https://music.apple.com/us/album/ends-in-y/1870981483</v>
       </c>
       <c r="L39" t="str">
-        <v>Somewhere Down in Georgia - Mon Rovîa</v>
+        <v>Ends In Y - Mimi Webb</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>BANG BANG</v>
+        <v>Bully</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/bang-bang/1872628039</v>
+        <v>https://music.apple.com/us/song/bully/1874401861</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>BANG BANG - Single</v>
+        <v>Bully - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>2:58</v>
+        <v>3:05</v>
       </c>
       <c r="H40" t="str">
-        <v>IVE</v>
+        <v>Iris Copperman</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/bang-bang/1872627662</v>
+        <v>https://music.apple.com/us/album/bully/1874401857</v>
       </c>
       <c r="L40" t="str">
-        <v>BANG BANG - IVE</v>
+        <v>Bully - Iris Copperman</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA</v>
+        <v>MC24 (1:4)</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302091</v>
+        <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - Single</v>
+        <v>MC24 &amp; SIN24 - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>3:15</v>
+        <v>3:16</v>
       </c>
       <c r="H41" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/charles-leclerc/1687977492</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/hasta-jes%C3%BAs-tuvo-un-mal-d%C3%ADa/1876302088</v>
+        <v>https://music.apple.com/us/album/mc24-1-4/1793396725</v>
       </c>
       <c r="L41" t="str">
-        <v>HASTA JESÚS TUVO UN MAL DÍA - CA7RIEL &amp; Paco Amoroso</v>
+        <v>MC24 (1:4) - Charles Leclerc</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Nightmare Tripping</v>
+        <v>ZERO</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/nightmare-tripping/1870746330</v>
+        <v>https://music.apple.com/us/song/zero/1874607340</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Nightmare Tripping</v>
+        <v>ZERO - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>5:21</v>
+        <v>2:20</v>
       </c>
       <c r="H42" t="str">
-        <v>Don Broco</v>
+        <v>REHMA</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/don-broco/307317604</v>
+        <v>https://music.apple.com/us/artist/rehma/1112461361</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/nightmare-tripping/1870746243</v>
+        <v>https://music.apple.com/us/album/zero/1874607338</v>
       </c>
       <c r="L42" t="str">
-        <v>Nightmare Tripping - Don Broco</v>
+        <v>ZERO - REHMA</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Hive Mind (feat. Denzel Curry)</v>
+        <v>Ride</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/hive-mind-feat-denzel-curry/1874420207</v>
+        <v>https://music.apple.com/us/song/ride/1869414360</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Single</v>
+        <v>Superbloom</v>
       </c>
       <c r="G43" t="str">
-        <v>3:26</v>
+        <v>4:39</v>
       </c>
       <c r="H43" t="str">
-        <v>Knocked Loose</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/knocked-loose/862677537</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/hive-mind-feat-denzel-curry/1874420203</v>
+        <v>https://music.apple.com/us/album/ride/1869414259</v>
       </c>
       <c r="L43" t="str">
-        <v>Hive Mind (feat. Denzel Curry) - Knocked Loose</v>
+        <v>Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>for your love</v>
+        <v>Arkansas Mud</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/for-your-love/1873085601</v>
+        <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>for your love - Single</v>
+        <v>Arkansas Mud - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>3:05</v>
+        <v>4:18</v>
       </c>
       <c r="H44" t="str">
-        <v>Cruz Beckham</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/for-your-love/1873085599</v>
+        <v>https://music.apple.com/us/album/arkansas-mud/1874413516</v>
       </c>
       <c r="L44" t="str">
-        <v>for your love - Cruz Beckham</v>
+        <v>Arkansas Mud - Ashley McBryde</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Somebody</v>
+        <v>Don't Leave</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873193244</v>
+        <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Somebody - Single</v>
+        <v>Don't Leave - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>3:23</v>
+        <v>2:10</v>
       </c>
       <c r="H45" t="str">
-        <v>Jamie Foxx</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/jamie-foxx/5171355</v>
+        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873193243</v>
+        <v>https://music.apple.com/us/album/dont-leave/1872418571</v>
       </c>
       <c r="L45" t="str">
-        <v>Somebody - Jamie Foxx</v>
+        <v>Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>BIG FEELING (NO MAKEUP)</v>
+        <v>FLAMED UP</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/big-feeling-no-makeup/1875437501</v>
+        <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>BIG FEELING (NO MAKEUP) - Single</v>
+        <v>FLAMED UP - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>1:55</v>
+        <v>2:31</v>
       </c>
       <c r="H46" t="str">
-        <v>BKTHERULA</v>
+        <v>JayDon</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/bktherula/1493904309</v>
+        <v>https://music.apple.com/us/artist/jaydon/1773146127</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/big-feeling-no-makeup/1875437500</v>
+        <v>https://music.apple.com/us/album/flamed-up/1876888777</v>
       </c>
       <c r="L46" t="str">
-        <v>BIG FEELING (NO MAKEUP) - BKTHERULA</v>
+        <v>FLAMED UP - JayDon</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>On and On</v>
+        <v>3am in Paris</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/on-and-on/1869618278</v>
+        <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Work of Heart</v>
+        <v>3am in Paris - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>3:43</v>
+        <v>2:49</v>
       </c>
       <c r="H47" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/on-and-on/1869617637</v>
+        <v>https://music.apple.com/us/album/3am-in-paris/1838055453</v>
       </c>
       <c r="L47" t="str">
-        <v>On and On - Flatland Cavalry</v>
+        <v>3am in Paris - Anais Cardot</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Push My Luck</v>
+        <v>I Got Saved (feat. Chris Brown) [Live]</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/push-my-luck/1868821460</v>
+        <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Push My Luck / All I Ever Need - EP</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G48" t="str">
-        <v>2:44</v>
+        <v>5:13</v>
       </c>
       <c r="H48" t="str">
-        <v>Cold War Kids</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/cold-war-kids/196319371</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/push-my-luck/1868821453</v>
+        <v>https://music.apple.com/us/album/i-got-saved-feat-chris-brown-live/1870678481</v>
       </c>
       <c r="L48" t="str">
-        <v>Push My Luck - Cold War Kids</v>
+        <v>I Got Saved (feat. Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Memphis Players</v>
+        <v>Opalite (Ely Oaks Remix)</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/memphis-players/1852533135</v>
+        <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>AK Cuts: Vol. 2 - EP</v>
+        <v>Opalite (Ely Oaks Remix) - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>2:46</v>
+        <v>3:26</v>
       </c>
       <c r="H49" t="str">
-        <v>Anish Kumar</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/memphis-players/1852533132</v>
+        <v>https://music.apple.com/us/album/opalite-ely-oaks-remix/1878155587</v>
       </c>
       <c r="L49" t="str">
-        <v>Memphis Players - Anish Kumar</v>
+        <v>Opalite (Ely Oaks Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Somebody</v>
+        <v>Old Man</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/somebody/1873982451</v>
+        <v>https://music.apple.com/us/song/old-man/1872189176</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Blue Sky Mentality (Complete Edition)</v>
+        <v>Old Man - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>2:49</v>
+        <v>4:05</v>
       </c>
       <c r="H50" t="str">
-        <v>Good Neighbours</v>
+        <v>Trousdale</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/good-neighbours/1726004707</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/somebody/1873982325</v>
+        <v>https://music.apple.com/us/album/old-man/1872189159</v>
       </c>
       <c r="L50" t="str">
-        <v>Somebody - Good Neighbours</v>
+        <v>Old Man - Trousdale</v>
       </c>
     </row>
     <row r="51">
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2336,1793 +2336,1641 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Seven Seas</v>
+        <v>Of Joy (feat. ARY)</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/seven-seas/1868461350</v>
+        <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Seven Seas - Single</v>
+        <v>Of Joy (feat. ARY) - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>3:01</v>
+        <v>3:19</v>
       </c>
       <c r="H52" t="str">
-        <v>Dirty Heads</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/dirty-heads/287941061</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/seven-seas/1868461349</v>
+        <v>https://music.apple.com/us/album/of-joy-feat-ary/1870539616</v>
       </c>
       <c r="L52" t="str">
-        <v>Seven Seas - Dirty Heads</v>
+        <v>Of Joy (feat. ARY) - DJ Seinfeld</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>1000 Ways</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg)</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/1000-ways/1846189474</v>
+        <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>A Love For Strangers</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G53" t="str">
-        <v>4:04</v>
+        <v>2:56</v>
       </c>
       <c r="H53" t="str">
-        <v>Chet Faker</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/1000-ways/1846189472</v>
+        <v>https://music.apple.com/us/album/the-scythe-feat-tiacorine-a%24ap-ferg/1868519270</v>
       </c>
       <c r="L53" t="str">
-        <v>1000 Ways - Chet Faker</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg) - Denzel Curry</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Beatback</v>
+        <v>Refuge</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/beatback/1861895138</v>
+        <v>https://music.apple.com/us/song/refuge/1867616924</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Ö</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G54" t="str">
-        <v>2:19</v>
+        <v>3:38</v>
       </c>
       <c r="H54" t="str">
-        <v>Fcukers</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/beatback/1861895134</v>
+        <v>https://music.apple.com/us/album/refuge/1867616617</v>
       </c>
       <c r="L54" t="str">
-        <v>Beatback - Fcukers</v>
+        <v>Refuge - Dermot Kennedy</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>GANG</v>
+        <v>Goodbye Goodmorning</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/gang/1872243101</v>
+        <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>GANG - Single</v>
+        <v>My Ego Told Me To</v>
       </c>
       <c r="G55" t="str">
-        <v>3:44</v>
+        <v>3:24</v>
       </c>
       <c r="H55" t="str">
-        <v>Tink</v>
+        <v>Leigh-Anne</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/gang/1872243100</v>
+        <v>https://music.apple.com/us/album/goodbye-goodmorning/1844865923</v>
       </c>
       <c r="L55" t="str">
-        <v>GANG - Tink</v>
+        <v>Goodbye Goodmorning - Leigh-Anne</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>a love song for u</v>
+        <v>Smoke Screen</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/a-love-song-for-u/1874696799</v>
+        <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>a love song for u - EP</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G56" t="str">
-        <v>1:40</v>
+        <v>2:51</v>
       </c>
       <c r="H56" t="str">
-        <v>Eem Triplin</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/eem-triplin/1348832122</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/a-love-song-for-u/1874696798</v>
+        <v>https://music.apple.com/us/album/smoke-screen/1851033857</v>
       </c>
       <c r="L56" t="str">
-        <v>a love song for u - Eem Triplin</v>
+        <v>Smoke Screen - Sweet Pill</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>See Through</v>
+        <v>Twisting The Knife (feat. Mckenna Grace)</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/see-through/1840712229</v>
+        <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>A.R.S.O.N.</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>2:38</v>
+        <v>3:21</v>
       </c>
       <c r="H57" t="str">
-        <v>Story of the Year</v>
+        <v>ICE NINE KILLS</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/story-of-the-year/2417172</v>
+        <v>https://music.apple.com/us/artist/ice-nine-kills/204318665</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/see-through/1840712224</v>
+        <v>https://music.apple.com/us/album/twisting-the-knife-feat-mckenna-grace/1871023713</v>
       </c>
       <c r="L57" t="str">
-        <v>See Through - Story of the Year</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - ICE NINE KILLS</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>be the girl!</v>
+        <v>Angel Wings</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/be-the-girl/1877161731</v>
+        <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>the apple tree under the sea</v>
+        <v>Angel Wings - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>5:33</v>
+        <v>3:52</v>
       </c>
       <c r="H58" t="str">
-        <v>hemlocke springs</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/be-the-girl/1877161526</v>
+        <v>https://music.apple.com/us/album/angel-wings/1876325893</v>
       </c>
       <c r="L58" t="str">
-        <v>be the girl! - hemlocke springs</v>
+        <v>Angel Wings - PRESIDENT</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>DON’T YOU SEE ME TRYING?</v>
+        <v>Roamer</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/dont-you-see-me-trying/1870646587</v>
+        <v>https://music.apple.com/us/song/roamer/1852775825</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Single</v>
+        <v>AngieAngieAngie</v>
       </c>
       <c r="G59" t="str">
-        <v>3:33</v>
+        <v>2:19</v>
       </c>
       <c r="H59" t="str">
-        <v>Erin LeCount</v>
+        <v>spill tab</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/spill-tab/1440467280</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/dont-you-see-me-trying/1870646585</v>
+        <v>https://music.apple.com/us/album/roamer/1852775506</v>
       </c>
       <c r="L59" t="str">
-        <v>DON’T YOU SEE ME TRYING? - Erin LeCount</v>
+        <v>Roamer - spill tab</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>American Teenage Prophecy</v>
+        <v>These Nights</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/american-teenage-prophecy/1871282503</v>
+        <v>https://music.apple.com/us/song/these-nights/1870989892</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>American Teenage Prophecy - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G60" t="str">
-        <v>3:40</v>
+        <v>4:39</v>
       </c>
       <c r="H60" t="str">
-        <v>Kid Sistr</v>
+        <v>Cannons</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/kid-sistr/1506324271</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/american-teenage-prophecy/1871282501</v>
+        <v>https://music.apple.com/us/album/these-nights/1870989672</v>
       </c>
       <c r="L60" t="str">
-        <v>American Teenage Prophecy - Kid Sistr</v>
+        <v>These Nights - Cannons</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ARCADE</v>
+        <v>Locked and Loaded</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/arcade/1870715147</v>
+        <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>ARCADE - Single</v>
+        <v>Locked and Loaded - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>2:52</v>
+        <v>2:55</v>
       </c>
       <c r="H61" t="str">
-        <v>Deb Never</v>
+        <v>The Cab</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/the-cab/135077748</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/arcade/1870715146</v>
+        <v>https://music.apple.com/us/album/locked-and-loaded/1876992433</v>
       </c>
       <c r="L61" t="str">
-        <v>ARCADE - Deb Never</v>
+        <v>Locked and Loaded - The Cab</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Girls Just Wanna</v>
+        <v>Safe And Sound</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/girls-just-wanna/1860974799</v>
+        <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Girlhood - EP</v>
+        <v>EI8HT</v>
       </c>
       <c r="G62" t="str">
-        <v>2:16</v>
+        <v>3:21</v>
       </c>
       <c r="H62" t="str">
-        <v>Morgan St. Jean</v>
+        <v>Shinedown</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/morgan-st-jean/1097954066</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/girls-just-wanna/1860974208</v>
+        <v>https://music.apple.com/us/album/safe-and-sound/1877229738</v>
       </c>
       <c r="L62" t="str">
-        <v>Girls Just Wanna - Morgan St. Jean</v>
+        <v>Safe And Sound - Shinedown</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>you special.</v>
+        <v>Flinch</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/you-special/1875125174</v>
+        <v>https://music.apple.com/us/song/flinch/1863072401</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>you special. - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G63" t="str">
-        <v>2:08</v>
+        <v>2:15</v>
       </c>
       <c r="H63" t="str">
-        <v>YFN Lucci</v>
+        <v>alexsucks</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/yfn-lucci/957498371</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/you-special/1875125170</v>
+        <v>https://music.apple.com/us/album/flinch/1863072393</v>
       </c>
       <c r="L63" t="str">
-        <v>you special. - YFN Lucci</v>
+        <v>Flinch - alexsucks</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Bass Dhol</v>
+        <v>Fall Up</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/bass-dhol/1868374433</v>
+        <v>https://music.apple.com/us/song/fall-up/1874959467</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Bass Dhol - Single</v>
+        <v>Fall Up - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>3:38</v>
+        <v>3:10</v>
       </c>
       <c r="H64" t="str">
-        <v>Ahadadream</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/ahadadream/661082529</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/bass-dhol/1868374424</v>
+        <v>https://music.apple.com/us/album/fall-up/1874959466</v>
       </c>
       <c r="L64" t="str">
-        <v>Bass Dhol - Ahadadream</v>
+        <v>Fall Up - VOILÀ</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Can't Be Alone Tonight</v>
+        <v>No Typo</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/cant-be-alone-tonight/1871970526</v>
+        <v>https://music.apple.com/us/song/no-typo/1872454952</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Can't Be Alone Tonight - Single</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G65" t="str">
-        <v>3:31</v>
+        <v>1:43</v>
       </c>
       <c r="H65" t="str">
-        <v>Charles Kelley</v>
+        <v>Nasty C</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/charles-kelley/156719136</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/cant-be-alone-tonight/1871970523</v>
+        <v>https://music.apple.com/us/album/no-typo/1872454582</v>
       </c>
       <c r="L65" t="str">
-        <v>Can't Be Alone Tonight - Charles Kelley</v>
+        <v>No Typo - Nasty C</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>If I See Her Again</v>
+        <v>Desiree</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/if-i-see-her-again/1871575409</v>
+        <v>https://music.apple.com/us/song/desiree/1852556464</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>If I See Her Again - Single</v>
+        <v>Wings of Desire</v>
       </c>
       <c r="G66" t="str">
-        <v>2:43</v>
+        <v>3:46</v>
       </c>
       <c r="H66" t="str">
-        <v>Maddox Batson</v>
+        <v>Hemi Hemingway</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/maddox-batson/1719310687</v>
+        <v>https://music.apple.com/us/artist/hemi-hemingway/1560734927</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/if-i-see-her-again/1871575408</v>
+        <v>https://music.apple.com/us/album/desiree/1852556460</v>
       </c>
       <c r="L66" t="str">
-        <v>If I See Her Again - Maddox Batson</v>
+        <v>Desiree - Hemi Hemingway</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>I’ll Be There (For You)</v>
+        <v>Goliath (feat. Katie Jacoby)</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/ill-be-there-for-you/1857048303</v>
+        <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Under The Sun</v>
+        <v>Goliath</v>
       </c>
       <c r="G67" t="str">
-        <v>4:43</v>
+        <v>5:04</v>
       </c>
       <c r="H67" t="str">
-        <v>Sun-El Musician</v>
+        <v>Exodus</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/sun-el-musician/1240936356</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/ill-be-there-for-you/1857048126</v>
+        <v>https://music.apple.com/us/album/goliath-feat-katie-jacoby/1862225385</v>
       </c>
       <c r="L67" t="str">
-        <v>I’ll Be There (For You) - Sun-El Musician</v>
+        <v>Goliath (feat. Katie Jacoby) - Exodus</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>To B Honest</v>
+        <v>Nomad</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/to-b-honest/1861386324</v>
+        <v>https://music.apple.com/us/song/nomad/1843578167</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>To Whom This May Concern</v>
+        <v>Loss</v>
       </c>
       <c r="G68" t="str">
-        <v>4:30</v>
+        <v>5:30</v>
       </c>
       <c r="H68" t="str">
-        <v>Jill Scott</v>
+        <v>Gaerea</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/jill-scott/14867</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/to-b-honest/1861385995</v>
+        <v>https://music.apple.com/us/album/nomad/1843578156</v>
       </c>
       <c r="L68" t="str">
-        <v>To B Honest - Jill Scott</v>
+        <v>Nomad - Gaerea</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>lil xan goes to washington</v>
+        <v>Empty Words</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/lil-xan-goes-to-washington/1842982366</v>
+        <v>https://music.apple.com/us/song/empty-words/1876625198</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>the beltway is burning</v>
+        <v>Empty Words - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>2:41</v>
+        <v>2:32</v>
       </c>
       <c r="H69" t="str">
-        <v>Ekko Astral</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/ekko-astral/1618850644</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/lil-xan-goes-to-washington/1842982354</v>
+        <v>https://music.apple.com/us/album/empty-words/1876625197</v>
       </c>
       <c r="L69" t="str">
-        <v>lil xan goes to washington - Ekko Astral</v>
+        <v>Empty Words - Corey Kent</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Koneko</v>
+        <v>Didn't Forget</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/koneko/1867318937</v>
+        <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Kurage - Single</v>
+        <v>Didn't Forget - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>4:08</v>
+        <v>3:48</v>
       </c>
       <c r="H70" t="str">
-        <v>Liana Flores</v>
+        <v>Waylon Wyatt</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/liana-flores/1393850429</v>
+        <v>https://music.apple.com/us/artist/waylon-wyatt/1713519329</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/koneko/1867318935</v>
+        <v>https://music.apple.com/us/album/didnt-forget/1876997982</v>
       </c>
       <c r="L70" t="str">
-        <v>Koneko - Liana Flores</v>
+        <v>Didn't Forget - Waylon Wyatt</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Cupid's Call</v>
+        <v>Euphoria</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/cupids-call/1872179949</v>
+        <v>https://music.apple.com/us/song/euphoria/1874295624</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Cupid's Call - Single</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>2:58</v>
+        <v>2:14</v>
       </c>
       <c r="H71" t="str">
-        <v>Dizzy Fae</v>
+        <v>Bluff City</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/dizzy-fae/1113842926</v>
+        <v>https://music.apple.com/us/artist/bluff-city/1491129891</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/cupids-call/1872179942</v>
+        <v>https://music.apple.com/us/album/euphoria/1874295623</v>
       </c>
       <c r="L71" t="str">
-        <v>Cupid's Call - Dizzy Fae</v>
+        <v>Euphoria - Bluff City</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Come Back 2 Me</v>
+        <v>hopeless romantic</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/come-back-2-me/1860381601</v>
+        <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Come Back 2 Me - Single</v>
+        <v>hopeless romantic - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:13</v>
+        <v>3:03</v>
       </c>
       <c r="H72" t="str">
-        <v>Chloé Caillet</v>
+        <v>kwn</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/chlo%C3%A9-caillet/1256658136</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/come-back-2-me/1860381445</v>
+        <v>https://music.apple.com/us/album/hopeless-romantic/1877131450</v>
       </c>
       <c r="L72" t="str">
-        <v>Come Back 2 Me - Chloé Caillet</v>
+        <v>hopeless romantic - kwn</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Pop Off</v>
+        <v>Stay Close</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/pop-off/1872187055</v>
+        <v>https://music.apple.com/us/song/stay-close/1871555365</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Pop Off - Single</v>
+        <v>Stay Close - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>3:16</v>
+        <v>2:58</v>
       </c>
       <c r="H73" t="str">
-        <v>GRiZ</v>
+        <v>Evelyn Cormier</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/evelyn-cormier/1222282253</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/pop-off/1872187054</v>
+        <v>https://music.apple.com/us/album/stay-close/1871555119</v>
       </c>
       <c r="L73" t="str">
-        <v>Pop Off - GRiZ</v>
+        <v>Stay Close - Evelyn Cormier</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>dreams</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/dreams/1871138304</v>
+        <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>dreams - Single</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="G74" t="str">
-        <v>3:31</v>
+        <v>2:54</v>
       </c>
       <c r="H74" t="str">
-        <v>Azzecca</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/azzecca/1627777746</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/dreams/1871138302</v>
+        <v>https://music.apple.com/us/album/metamorphosis/1870994803</v>
       </c>
       <c r="L74" t="str">
-        <v>dreams - Azzecca</v>
+        <v>Metamorphosis - lydi lynn</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Love Hate Love</v>
+        <v>peace at last</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/love-hate-love/1871329794</v>
+        <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Love Hate Love - Single</v>
+        <v>peace at last - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>2:55</v>
+        <v>2:34</v>
       </c>
       <c r="H75" t="str">
-        <v>Owen Riegling</v>
+        <v>Aaron Cole</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/love-hate-love/1871329793</v>
+        <v>https://music.apple.com/us/album/peace-at-last/1870895278</v>
       </c>
       <c r="L75" t="str">
-        <v>Love Hate Love - Owen Riegling</v>
+        <v>peace at last - Aaron Cole</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Do It All Alone</v>
+        <v>Aguántame</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1871330760</v>
+        <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Aguántame - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>2:52</v>
+        <v>2:08</v>
       </c>
       <c r="H76" t="str">
-        <v>Rend Collective</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1871330759</v>
+        <v>https://music.apple.com/us/album/agu%C3%A1ntame/1873075917</v>
       </c>
       <c r="L76" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Aguántame - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>She Makes Me Real</v>
+        <v>Para No Hacernos Daño</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/she-makes-me-real/1838995902</v>
+        <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Masquerade</v>
+        <v>Para No Hacernos Daño - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:58</v>
+        <v>2:40</v>
       </c>
       <c r="H77" t="str">
-        <v>Cardinals</v>
+        <v>Codiciado</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/cardinals/1651654416</v>
+        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/she-makes-me-real/1838995891</v>
+        <v>https://music.apple.com/us/album/para-no-hacernos-da%C3%B1o/1872743927</v>
       </c>
       <c r="L77" t="str">
-        <v>She Makes Me Real - Cardinals</v>
+        <v>Para No Hacernos Daño - Codiciado</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Steady</v>
+        <v>NADA PERSONAL</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/steady/1874718519</v>
+        <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>a couple minutes out - Single</v>
+        <v>NADA PERSONAL - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:26</v>
+        <v>3:11</v>
       </c>
       <c r="H78" t="str">
-        <v>Bella Kay</v>
+        <v>La Joaqui</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/la-joaqui/1222726669</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/steady/1874718231</v>
+        <v>https://music.apple.com/us/album/nada-personal/1875350196</v>
       </c>
       <c r="L78" t="str">
-        <v>Steady - Bella Kay</v>
+        <v>NADA PERSONAL - La Joaqui</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>DIRTY TECH</v>
+        <v>V3n3n0</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/dirty-tech/1859967737</v>
+        <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>PLAY ME</v>
+        <v>V3n3n0 - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>2:20</v>
+        <v>2:32</v>
       </c>
       <c r="H79" t="str">
-        <v>Kim Gordon</v>
+        <v>Esty</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/kim-gordon/27266002</v>
+        <v>https://music.apple.com/us/artist/esty/255471858</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/dirty-tech/1859967390</v>
+        <v>https://music.apple.com/us/album/v3n3n0/1874454944</v>
       </c>
       <c r="L79" t="str">
-        <v>DIRTY TECH - Kim Gordon</v>
+        <v>V3n3n0 - Esty</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Nada Más</v>
+        <v>Moth In The Headlights</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/nada-m%C3%A1s/1875335005</v>
+        <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Nada Más - Single</v>
+        <v>Inanimate Objects of the 21st Century</v>
       </c>
       <c r="G80" t="str">
-        <v>2:19</v>
+        <v>4:23</v>
       </c>
       <c r="H80" t="str">
-        <v>Tombochio</v>
+        <v>The Pale White</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/tombochio/1570164065</v>
+        <v>https://music.apple.com/us/artist/the-pale-white/1127116907</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/nada-m%C3%A1s/1875335003</v>
+        <v>https://music.apple.com/us/album/moth-in-the-headlights/1870538540</v>
       </c>
       <c r="L80" t="str">
-        <v>Nada Más - Tombochio</v>
+        <v>Moth In The Headlights - The Pale White</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Friends Again</v>
+        <v>lately in the void</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/friends-again/1871211171</v>
+        <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Friends Again - Single</v>
+        <v>lately in the void - EP</v>
       </c>
       <c r="G81" t="str">
-        <v>3:38</v>
+        <v>3:41</v>
       </c>
       <c r="H81" t="str">
-        <v>Baby Rose</v>
+        <v>bad tuner</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/baby-rose/582355843</v>
+        <v>https://music.apple.com/us/artist/bad-tuner/1051446214</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/friends-again/1871211170</v>
+        <v>https://music.apple.com/us/album/lately-in-the-void/1847993191</v>
       </c>
       <c r="L81" t="str">
-        <v>Friends Again - Baby Rose</v>
+        <v>lately in the void - bad tuner</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>W.T.A.</v>
+        <v>When I Fall in Love</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/w-t-a/1874385898</v>
+        <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>W.T.A. - Single</v>
+        <v>Nightjar</v>
       </c>
       <c r="G82" t="str">
-        <v>3:22</v>
+        <v>4:45</v>
       </c>
       <c r="H82" t="str">
-        <v>Isaia Huron</v>
+        <v>David Gray</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/david-gray/316381</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/w-t-a/1874385895</v>
+        <v>https://music.apple.com/us/album/when-i-fall-in-love/1860381106</v>
       </c>
       <c r="L82" t="str">
-        <v>W.T.A. - Isaia Huron</v>
+        <v>When I Fall in Love - David Gray</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>desire.</v>
+        <v>Repeat Offender</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/desire/1846171015</v>
+        <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>November Scorpio</v>
+        <v>Repeat Offender - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>3:15</v>
+        <v>2:33</v>
       </c>
       <c r="H83" t="str">
-        <v>Tiana Major9</v>
+        <v>yeemz</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/tiana-major9/1210840772</v>
+        <v>https://music.apple.com/us/artist/yeemz/1561474492</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/desire/1846170591</v>
+        <v>https://music.apple.com/us/album/repeat-offender/1873099828</v>
       </c>
       <c r="L83" t="str">
-        <v>desire. - Tiana Major9</v>
+        <v>Repeat Offender - yeemz</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>Class Reunion</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/everywhere-isnt-texas/1846001266</v>
+        <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Everywhere Isn't Texas</v>
+        <v>We Swallowed The Sky</v>
       </c>
       <c r="G84" t="str">
-        <v>3:12</v>
+        <v>4:11</v>
       </c>
       <c r="H84" t="str">
-        <v>August Ponthier</v>
+        <v>Beatrix</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/august-ponthier/1856731175</v>
+        <v>https://music.apple.com/us/artist/beatrix/1732651124</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/everywhere-isnt-texas/1846001261</v>
+        <v>https://music.apple.com/us/album/class-reunion/1876698281</v>
       </c>
       <c r="L84" t="str">
-        <v>Everywhere Isn't Texas - August Ponthier</v>
+        <v>Class Reunion - Beatrix</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Killer Whale</v>
+        <v>Promise Me</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/killer-whale/1872124744</v>
+        <v>https://music.apple.com/us/song/promise-me/1848977981</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Killer Whale - Single</v>
+        <v>Instant Comfort</v>
       </c>
       <c r="G85" t="str">
-        <v>4:00</v>
+        <v>5:34</v>
       </c>
       <c r="H85" t="str">
-        <v>Hayden Everett</v>
+        <v>Lucid Express</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/lucid-express/1560683497</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/killer-whale/1872124743</v>
+        <v>https://music.apple.com/us/album/promise-me/1848977978</v>
       </c>
       <c r="L85" t="str">
-        <v>Killer Whale - Hayden Everett</v>
+        <v>Promise Me - Lucid Express</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Waits for Me</v>
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions)</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/waits-for-me/1860276549</v>
+        <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>You’re Free to Go</v>
+        <v>Awe Mah (feat. Shakes &amp; Les, MK Productions &amp; Funky Qla) - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>2:46</v>
+        <v>3:33</v>
       </c>
       <c r="H86" t="str">
-        <v>Anjimile</v>
+        <v>Zee Nxumalo</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/anjimile/786333277</v>
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/waits-for-me/1860276153</v>
+        <v>https://music.apple.com/us/album/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873675</v>
       </c>
       <c r="L86" t="str">
-        <v>Waits for Me - Anjimile</v>
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions) - Zee Nxumalo</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Man's World</v>
+        <v>Hit and Run (feat. AZ Chike)</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/mans-world/1861998024</v>
+        <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Mud Blood Bone</v>
+        <v>Hit and Run (feat. AZ Chike) - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>2:42</v>
+        <v>3:19</v>
       </c>
       <c r="H87" t="str">
-        <v>Cat Clyde</v>
+        <v>Ray Vaughn</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/cat-clyde/1001664473</v>
+        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/mans-world/1861997858</v>
+        <v>https://music.apple.com/us/album/hit-and-run-feat-az-chike/1877912892</v>
       </c>
       <c r="L87" t="str">
-        <v>Man's World - Cat Clyde</v>
+        <v>Hit and Run (feat. AZ Chike) - Ray Vaughn</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>In the Middle of It</v>
+        <v>So Good</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/in-the-middle-of-it/1860939767</v>
+        <v>https://music.apple.com/us/song/so-good/1874733689</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>In the Middle of It - Single</v>
+        <v>So Good - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:13</v>
+        <v>2:47</v>
       </c>
       <c r="H88" t="str">
-        <v>Hiss Golden Messenger</v>
+        <v>Ari Abdul</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/hiss-golden-messenger/320910472</v>
+        <v>https://music.apple.com/us/artist/ari-abdul/1606828852</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/in-the-middle-of-it/1860939764</v>
+        <v>https://music.apple.com/us/album/so-good/1874733688</v>
       </c>
       <c r="L88" t="str">
-        <v>In the Middle of It - Hiss Golden Messenger</v>
+        <v>So Good - Ari Abdul</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Truth Of Pursuit</v>
+        <v>YDH</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/truth-of-pursuit/1860734195</v>
+        <v>https://music.apple.com/us/song/ydh/1874940744</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Fleeting - EP</v>
+        <v>YDH - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>2:51</v>
+        <v>3:17</v>
       </c>
       <c r="H89" t="str">
-        <v>Sarah Kinsley</v>
+        <v>Chloe Qisha</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/sarah-kinsley/1436737349</v>
+        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/truth-of-pursuit/1860733977</v>
+        <v>https://music.apple.com/us/album/ydh/1874940739</v>
       </c>
       <c r="L89" t="str">
-        <v>Truth Of Pursuit - Sarah Kinsley</v>
+        <v>YDH - Chloe Qisha</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>What If You Fly (Sweet Disposition)</v>
+        <v>Eucalyptus</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/what-if-you-fly-sweet-disposition/1876421017</v>
+        <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>What If You Fly (Sweet Disposition) - Single</v>
+        <v>Porcelain</v>
       </c>
       <c r="G90" t="str">
-        <v>5:23</v>
+        <v>3:00</v>
       </c>
       <c r="H90" t="str">
-        <v>BUNT.</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/what-if-you-fly-sweet-disposition/1876421016</v>
+        <v>https://music.apple.com/us/album/eucalyptus/1861380240</v>
       </c>
       <c r="L90" t="str">
-        <v>What If You Fly (Sweet Disposition) - BUNT.</v>
+        <v>Eucalyptus - Peach PRC</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>I've Never Met Her</v>
+        <v>Pearls In The Trap</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/ive-never-met-her/1874385820</v>
+        <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>I've Never Met Her - Single</v>
+        <v>Pearls In The Trap - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>3:07</v>
+        <v>1:38</v>
       </c>
       <c r="H91" t="str">
-        <v>Ally Salort</v>
+        <v>carolesdaughter</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/ally-salort/1622933985</v>
+        <v>https://music.apple.com/us/artist/carolesdaughter/1502564996</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/ive-never-met-her/1874385599</v>
+        <v>https://music.apple.com/us/album/pearls-in-the-trap/1877892476</v>
       </c>
       <c r="L91" t="str">
-        <v>I've Never Met Her - Ally Salort</v>
+        <v>Pearls In The Trap - carolesdaughter</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>BACKWARDS, INTO U</v>
+        <v>The Fever Mask</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/backwards-into-u/1871425369</v>
+        <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>The Elephant</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G92" t="str">
-        <v>3:28</v>
+        <v>3:12</v>
       </c>
       <c r="H92" t="str">
-        <v>Ledbyher</v>
+        <v>At The Gates</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/backwards-into-u/1871425115</v>
+        <v>https://music.apple.com/us/album/the-fever-mask/1873364809</v>
       </c>
       <c r="L92" t="str">
-        <v>BACKWARDS, INTO U - Ledbyher</v>
+        <v>The Fever Mask - At The Gates</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Yes</v>
+        <v>The Air's on Fire</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/yes/1849157719</v>
+        <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Just A Few Folk</v>
+        <v>Location Lost</v>
       </c>
       <c r="G93" t="str">
-        <v>3:21</v>
+        <v>5:15</v>
       </c>
       <c r="H93" t="str">
-        <v>JP Cooper</v>
+        <v>Failure</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/jp-cooper/576710545</v>
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/yes/1849157442</v>
+        <v>https://music.apple.com/us/album/the-airs-on-fire/1867015665</v>
       </c>
       <c r="L93" t="str">
-        <v>Yes - JP Cooper</v>
+        <v>The Air's on Fire - Failure</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>CHOKEHOLD</v>
+        <v>To The Last Breath</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/chokehold/1874372640</v>
+        <v>https://music.apple.com/us/song/to-the-last-breath/1874618974</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>CHOKEHOLD - Single</v>
+        <v>To The Last Breath - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>2:52</v>
+        <v>4:57</v>
       </c>
       <c r="H94" t="str">
-        <v>WesGhost</v>
+        <v>Arch Enemy</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/wesghost/1676527385</v>
+        <v>https://music.apple.com/us/artist/arch-enemy/18098340</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/chokehold/1874372639</v>
+        <v>https://music.apple.com/us/album/to-the-last-breath/1874618973</v>
       </c>
       <c r="L94" t="str">
-        <v>CHOKEHOLD - WesGhost</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v>Bad Faith</v>
-      </c>
-      <c r="B95" t="str">
-        <v/>
-      </c>
-      <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/bad-faith/1848413295</v>
-      </c>
-      <c r="D95" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E95" t="str">
-        <v/>
-      </c>
-      <c r="F95" t="str">
-        <v>Love Is Not Enough</v>
-      </c>
-      <c r="G95" t="str">
-        <v>2:48</v>
-      </c>
-      <c r="H95" t="str">
-        <v>Converge</v>
-      </c>
-      <c r="I95" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
-      </c>
-      <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/bad-faith/1848413292</v>
-      </c>
-      <c r="L95" t="str">
-        <v>Bad Faith - Converge</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v>Gimme Some Moore</v>
-      </c>
-      <c r="B96" t="str">
-        <v/>
-      </c>
-      <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/gimme-some-moore/1869085900</v>
-      </c>
-      <c r="D96" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E96" t="str">
-        <v/>
-      </c>
-      <c r="F96" t="str">
-        <v>Good God / Baad Man</v>
-      </c>
-      <c r="G96" t="str">
-        <v>4:00</v>
-      </c>
-      <c r="H96" t="str">
-        <v>Corrosion of Conformity</v>
-      </c>
-      <c r="I96" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
-      </c>
-      <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/gimme-some-moore/1869085524</v>
-      </c>
-      <c r="L96" t="str">
-        <v>Gimme Some Moore - Corrosion of Conformity</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v>Angel Eyes</v>
-      </c>
-      <c r="B97" t="str">
-        <v/>
-      </c>
-      <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/angel-eyes/1873059540</v>
-      </c>
-      <c r="D97" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E97" t="str">
-        <v/>
-      </c>
-      <c r="F97" t="str">
-        <v>God Forgives - Single</v>
-      </c>
-      <c r="G97" t="str">
-        <v>2:14</v>
-      </c>
-      <c r="H97" t="str">
-        <v>Guilt Trip</v>
-      </c>
-      <c r="I97" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/guilt-trip/1463581100</v>
-      </c>
-      <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/angel-eyes/1873059365</v>
-      </c>
-      <c r="L97" t="str">
-        <v>Angel Eyes - Guilt Trip</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v>Tossing Coins Into The Fountain Of F**k</v>
-      </c>
-      <c r="B98" t="str">
-        <v/>
-      </c>
-      <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/tossing-coins-into-the-fountain-of-f-k/1866957687</v>
-      </c>
-      <c r="D98" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E98" t="str">
-        <v/>
-      </c>
-      <c r="F98" t="str">
-        <v>Savage Imperial Death March</v>
-      </c>
-      <c r="G98" t="str">
-        <v>3:17</v>
-      </c>
-      <c r="H98" t="str">
-        <v>Melvins</v>
-      </c>
-      <c r="I98" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
-      </c>
-      <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/tossing-coins-into-the-fountain-of-f-k/1866957685</v>
-      </c>
-      <c r="L98" t="str">
-        <v>Tossing Coins Into The Fountain Of F**k - Melvins</v>
+        <v>To The Last Breath - Arch Enemy</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L94"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L96"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1538,13 +1538,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>More Than A Lover</v>
+        <v>Yellow Eyes</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/more-than-a-lover/1876711633</v>
+        <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-20</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>More Than A Lover - Single</v>
+        <v>Jean</v>
       </c>
       <c r="G31" t="str">
-        <v>4:05</v>
+        <v>2:42</v>
       </c>
       <c r="H31" t="str">
-        <v>Mary J. Blige</v>
+        <v>Yebba</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/mary-j-blige/1392280</v>
+        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/more-than-a-lover/1876711631</v>
+        <v>https://music.apple.com/us/album/yellow-eyes/1877157664</v>
       </c>
       <c r="L31" t="str">
-        <v>More Than A Lover - Mary J. Blige</v>
+        <v>Yellow Eyes - Yebba</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Yellow Eyes</v>
+        <v>Word On The Street</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
+        <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-20</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Jean</v>
+        <v>Word On The Street - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>2:42</v>
+        <v>2:56</v>
       </c>
       <c r="H32" t="str">
-        <v>Yebba</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/yellow-eyes/1877157664</v>
+        <v>https://music.apple.com/us/album/word-on-the-street/1876607713</v>
       </c>
       <c r="L32" t="str">
-        <v>Yellow Eyes - Yebba</v>
+        <v>Word On The Street - Luke Bryan</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Word On The Street</v>
+        <v>only the best</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
+        <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-20</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Word On The Street - Single</v>
+        <v>only the best - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>2:56</v>
+        <v>3:22</v>
       </c>
       <c r="H33" t="str">
-        <v>Luke Bryan</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/word-on-the-street/1876607713</v>
+        <v>https://music.apple.com/us/album/only-the-best/1876048174</v>
       </c>
       <c r="L33" t="str">
-        <v>Word On The Street - Luke Bryan</v>
+        <v>only the best - horsegiirL</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>only the best</v>
+        <v>Beautiful Places</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
+        <v>https://music.apple.com/us/song/beautiful-places/1876326643</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-20</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>only the best - Single</v>
+        <v>Beautiful Places - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>3:22</v>
+        <v>2:59</v>
       </c>
       <c r="H34" t="str">
-        <v>horsegiirL</v>
+        <v>Tiësto</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/ti%C3%ABsto/4091218</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/only-the-best/1876048174</v>
+        <v>https://music.apple.com/us/album/beautiful-places/1876326642</v>
       </c>
       <c r="L34" t="str">
-        <v>only the best - horsegiirL</v>
+        <v>Beautiful Places - Tiësto</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>miss u 2 (with Leon Thomas)</v>
+        <v>STAMPEDE</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
+        <v>https://music.apple.com/us/song/stampede/1868995802</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-20</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>girl music vol. 1 - EP</v>
+        <v>STAMPEDE - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>2:28</v>
+        <v>3:09</v>
       </c>
       <c r="H35" t="str">
-        <v>Ty Dolla $ign</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/miss-u-2-with-leon-thomas/1878416755</v>
+        <v>https://music.apple.com/us/album/stampede/1868995797</v>
       </c>
       <c r="L35" t="str">
-        <v>miss u 2 (with Leon Thomas) - Ty Dolla $ign</v>
+        <v>STAMPEDE - Genesis Owusu</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ILRB (feat. Babyface Ray)</v>
+        <v>Infinite Beach</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
+        <v>https://music.apple.com/us/song/infinite-beach/1858554535</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-20</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Da Realest</v>
+        <v>Mārara</v>
       </c>
       <c r="G36" t="str">
-        <v>1:51</v>
+        <v>3:10</v>
       </c>
       <c r="H36" t="str">
-        <v>Babyfxce E</v>
+        <v>15 15</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/ilrb-feat-babyface-ray/1860991661</v>
+        <v>https://music.apple.com/us/album/infinite-beach/1858554036</v>
       </c>
       <c r="L36" t="str">
-        <v>ILRB (feat. Babyface Ray) - Babyfxce E</v>
+        <v>Infinite Beach - 15 15</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Fine Shit</v>
+        <v>Championship Ring</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
+        <v>https://music.apple.com/us/song/championship-ring/1875186768</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-20</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Fine Shit - Single</v>
+        <v>I Want Blood</v>
       </c>
       <c r="G37" t="str">
-        <v>1:53</v>
+        <v>3:41</v>
       </c>
       <c r="H37" t="str">
-        <v>Real Boston Richey</v>
+        <v>SleazyWorld Go</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
+        <v>https://music.apple.com/us/artist/sleazyworld-go/1503917115</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/fine-shit/1878172115</v>
+        <v>https://music.apple.com/us/album/championship-ring/1875186762</v>
       </c>
       <c r="L37" t="str">
-        <v>Fine Shit - Real Boston Richey</v>
+        <v>Championship Ring - SleazyWorld Go</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>What's Your Name</v>
+        <v>miss u 2 (with Leon Thomas)</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
+        <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-20</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>What's Your Name - Single</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G38" t="str">
-        <v>2:20</v>
+        <v>2:28</v>
       </c>
       <c r="H38" t="str">
-        <v>Soulidified</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/soulidified/1824036220</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/whats-your-name/1878121935</v>
+        <v>https://music.apple.com/us/album/miss-u-2-with-leon-thomas/1878416755</v>
       </c>
       <c r="L38" t="str">
-        <v>What's Your Name - Soulidified</v>
+        <v>miss u 2 (with Leon Thomas) - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Ends In Y</v>
+        <v>ILRB (feat. Babyface Ray)</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
+        <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-20</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>Da Realest</v>
       </c>
       <c r="G39" t="str">
-        <v>2:53</v>
+        <v>1:51</v>
       </c>
       <c r="H39" t="str">
-        <v>Mimi Webb</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/ends-in-y/1870981483</v>
+        <v>https://music.apple.com/us/album/ilrb-feat-babyface-ray/1860991661</v>
       </c>
       <c r="L39" t="str">
-        <v>Ends In Y - Mimi Webb</v>
+        <v>ILRB (feat. Babyface Ray) - Babyfxce E</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Bully</v>
+        <v>Fine Shit</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/bully/1874401861</v>
+        <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-20</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Bully - Single</v>
+        <v>Fine Shit - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>3:05</v>
+        <v>1:53</v>
       </c>
       <c r="H40" t="str">
-        <v>Iris Copperman</v>
+        <v>Real Boston Richey</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
+        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/bully/1874401857</v>
+        <v>https://music.apple.com/us/album/fine-shit/1878172115</v>
       </c>
       <c r="L40" t="str">
-        <v>Bully - Iris Copperman</v>
+        <v>Fine Shit - Real Boston Richey</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>MC24 (1:4)</v>
+        <v>What's Your Name</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
+        <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-20</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>MC24 &amp; SIN24 - Single</v>
+        <v>What's Your Name - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>3:16</v>
+        <v>2:20</v>
       </c>
       <c r="H41" t="str">
-        <v>Charles Leclerc</v>
+        <v>Soulidified</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/charles-leclerc/1687977492</v>
+        <v>https://music.apple.com/us/artist/soulidified/1824036220</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/mc24-1-4/1793396725</v>
+        <v>https://music.apple.com/us/album/whats-your-name/1878121935</v>
       </c>
       <c r="L41" t="str">
-        <v>MC24 (1:4) - Charles Leclerc</v>
+        <v>What's Your Name - Soulidified</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ZERO</v>
+        <v>Ends In Y</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/zero/1874607340</v>
+        <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-20</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>ZERO - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G42" t="str">
-        <v>2:20</v>
+        <v>2:53</v>
       </c>
       <c r="H42" t="str">
-        <v>REHMA</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/rehma/1112461361</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/zero/1874607338</v>
+        <v>https://music.apple.com/us/album/ends-in-y/1870981483</v>
       </c>
       <c r="L42" t="str">
-        <v>ZERO - REHMA</v>
+        <v>Ends In Y - Mimi Webb</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Ride</v>
+        <v>Bully</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/ride/1869414360</v>
+        <v>https://music.apple.com/us/song/bully/1874401861</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-20</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Superbloom</v>
+        <v>Bully - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>4:39</v>
+        <v>3:05</v>
       </c>
       <c r="H43" t="str">
-        <v>Jessie Ware</v>
+        <v>Iris Copperman</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/ride/1869414259</v>
+        <v>https://music.apple.com/us/album/bully/1874401857</v>
       </c>
       <c r="L43" t="str">
-        <v>Ride - Jessie Ware</v>
+        <v>Bully - Iris Copperman</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Arkansas Mud</v>
+        <v>MC24 (1:4)</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
+        <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-20</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Arkansas Mud - Single</v>
+        <v>MC24 &amp; SIN24 - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>4:18</v>
+        <v>3:16</v>
       </c>
       <c r="H44" t="str">
-        <v>Ashley McBryde</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/charles-leclerc/1687977492</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/arkansas-mud/1874413516</v>
+        <v>https://music.apple.com/us/album/mc24-1-4/1793396725</v>
       </c>
       <c r="L44" t="str">
-        <v>Arkansas Mud - Ashley McBryde</v>
+        <v>MC24 (1:4) - Charles Leclerc</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Don't Leave</v>
+        <v>Ride</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
+        <v>https://music.apple.com/us/song/ride/1869414360</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-20</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Don't Leave - Single</v>
+        <v>Superbloom</v>
       </c>
       <c r="G45" t="str">
-        <v>2:10</v>
+        <v>4:39</v>
       </c>
       <c r="H45" t="str">
-        <v>Jorja Smith</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/dont-leave/1872418571</v>
+        <v>https://music.apple.com/us/album/ride/1869414259</v>
       </c>
       <c r="L45" t="str">
-        <v>Don't Leave - Jorja Smith</v>
+        <v>Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>FLAMED UP</v>
+        <v>Arkansas Mud</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
+        <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-20</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>FLAMED UP - Single</v>
+        <v>Arkansas Mud - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>2:31</v>
+        <v>4:18</v>
       </c>
       <c r="H46" t="str">
-        <v>JayDon</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/jaydon/1773146127</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/flamed-up/1876888777</v>
+        <v>https://music.apple.com/us/album/arkansas-mud/1874413516</v>
       </c>
       <c r="L46" t="str">
-        <v>FLAMED UP - JayDon</v>
+        <v>Arkansas Mud - Ashley McBryde</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>3am in Paris</v>
+        <v>Don't Leave</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
+        <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-20</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>3am in Paris - Single</v>
+        <v>Don't Leave - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>2:49</v>
+        <v>2:10</v>
       </c>
       <c r="H47" t="str">
-        <v>Anais Cardot</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/3am-in-paris/1838055453</v>
+        <v>https://music.apple.com/us/album/dont-leave/1872418571</v>
       </c>
       <c r="L47" t="str">
-        <v>3am in Paris - Anais Cardot</v>
+        <v>Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>I Got Saved (feat. Chris Brown) [Live]</v>
+        <v>FLAMED UP</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
+        <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-20</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>FLAMED UP - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>5:13</v>
+        <v>2:31</v>
       </c>
       <c r="H48" t="str">
-        <v>Elevation Worship</v>
+        <v>JayDon</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/jaydon/1773146127</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/i-got-saved-feat-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/flamed-up/1876888777</v>
       </c>
       <c r="L48" t="str">
-        <v>I Got Saved (feat. Chris Brown) [Live] - Elevation Worship</v>
+        <v>FLAMED UP - JayDon</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Opalite (Ely Oaks Remix)</v>
+        <v>3am in Paris</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
+        <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-20</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Opalite (Ely Oaks Remix) - Single</v>
+        <v>3am in Paris - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>3:26</v>
+        <v>2:49</v>
       </c>
       <c r="H49" t="str">
-        <v>Taylor Swift</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/opalite-ely-oaks-remix/1878155587</v>
+        <v>https://music.apple.com/us/album/3am-in-paris/1838055453</v>
       </c>
       <c r="L49" t="str">
-        <v>Opalite (Ely Oaks Remix) - Taylor Swift</v>
+        <v>3am in Paris - Anais Cardot</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Old Man</v>
+        <v>I Got Saved (feat. Chris Brown) [Live]</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/old-man/1872189176</v>
+        <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-20</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Old Man - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G50" t="str">
-        <v>4:05</v>
+        <v>5:13</v>
       </c>
       <c r="H50" t="str">
-        <v>Trousdale</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/old-man/1872189159</v>
+        <v>https://music.apple.com/us/album/i-got-saved-feat-chris-brown-live/1870678481</v>
       </c>
       <c r="L50" t="str">
-        <v>Old Man - Trousdale</v>
+        <v>I Got Saved (feat. Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>If I Didn't Know You</v>
+        <v>Migajero</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/if-i-didnt-know-you/1875965776</v>
+        <v>https://music.apple.com/us/song/migajero/1873051149</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-20</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>If I Didn't Know You - Single</v>
+        <v>Migajero - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>3:28</v>
+        <v>3:18</v>
       </c>
       <c r="H51" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Grupo Marca Registrada</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/grupo-marca-registrada/1051127522</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/if-i-didnt-know-you/1875965774</v>
+        <v>https://music.apple.com/us/album/migajero/1873051145</v>
       </c>
       <c r="L51" t="str">
-        <v>If I Didn't Know You - The Red Clay Strays</v>
+        <v>Migajero - Grupo Marca Registrada</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Of Joy (feat. ARY)</v>
+        <v>Opalite (Ely Oaks Remix)</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
+        <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-20</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Of Joy (feat. ARY) - Single</v>
+        <v>Opalite (Ely Oaks Remix) - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>3:19</v>
+        <v>3:26</v>
       </c>
       <c r="H52" t="str">
-        <v>DJ Seinfeld</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/of-joy-feat-ary/1870539616</v>
+        <v>https://music.apple.com/us/album/opalite-ely-oaks-remix/1878155587</v>
       </c>
       <c r="L52" t="str">
-        <v>Of Joy (feat. ARY) - DJ Seinfeld</v>
+        <v>Opalite (Ely Oaks Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg)</v>
+        <v>Old Man</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
+        <v>https://music.apple.com/us/song/old-man/1872189176</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-20</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>Old Man - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>2:56</v>
+        <v>4:05</v>
       </c>
       <c r="H53" t="str">
-        <v>Denzel Curry</v>
+        <v>Trousdale</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/the-scythe-feat-tiacorine-a%24ap-ferg/1868519270</v>
+        <v>https://music.apple.com/us/album/old-man/1872189159</v>
       </c>
       <c r="L53" t="str">
-        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg) - Denzel Curry</v>
+        <v>Old Man - Trousdale</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Refuge</v>
+        <v>Of Joy (feat. ARY)</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/refuge/1867616924</v>
+        <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-20</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Of Joy (feat. ARY) - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>3:38</v>
+        <v>3:19</v>
       </c>
       <c r="H54" t="str">
-        <v>Dermot Kennedy</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/refuge/1867616617</v>
+        <v>https://music.apple.com/us/album/of-joy-feat-ary/1870539616</v>
       </c>
       <c r="L54" t="str">
-        <v>Refuge - Dermot Kennedy</v>
+        <v>Of Joy (feat. ARY) - DJ Seinfeld</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Goodbye Goodmorning</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg)</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
+        <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-20</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>My Ego Told Me To</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G55" t="str">
-        <v>3:24</v>
+        <v>2:56</v>
       </c>
       <c r="H55" t="str">
-        <v>Leigh-Anne</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/goodbye-goodmorning/1844865923</v>
+        <v>https://music.apple.com/us/album/the-scythe-feat-tiacorine-a%24ap-ferg/1868519270</v>
       </c>
       <c r="L55" t="str">
-        <v>Goodbye Goodmorning - Leigh-Anne</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg) - Denzel Curry</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Smoke Screen</v>
+        <v>Refuge</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
+        <v>https://music.apple.com/us/song/refuge/1867616924</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-20</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Still There’s a Glow</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G56" t="str">
-        <v>2:51</v>
+        <v>3:38</v>
       </c>
       <c r="H56" t="str">
-        <v>Sweet Pill</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/smoke-screen/1851033857</v>
+        <v>https://music.apple.com/us/album/refuge/1867616617</v>
       </c>
       <c r="L56" t="str">
-        <v>Smoke Screen - Sweet Pill</v>
+        <v>Refuge - Dermot Kennedy</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace)</v>
+        <v>Goodbye Goodmorning</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
+        <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-20</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace) - Single</v>
+        <v>My Ego Told Me To</v>
       </c>
       <c r="G57" t="str">
-        <v>3:21</v>
+        <v>3:24</v>
       </c>
       <c r="H57" t="str">
-        <v>ICE NINE KILLS</v>
+        <v>Leigh-Anne</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/ice-nine-kills/204318665</v>
+        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/twisting-the-knife-feat-mckenna-grace/1871023713</v>
+        <v>https://music.apple.com/us/album/goodbye-goodmorning/1844865923</v>
       </c>
       <c r="L57" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace) - ICE NINE KILLS</v>
+        <v>Goodbye Goodmorning - Leigh-Anne</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Angel Wings</v>
+        <v>Smoke Screen</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
+        <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-20</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Angel Wings - Single</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G58" t="str">
-        <v>3:52</v>
+        <v>2:51</v>
       </c>
       <c r="H58" t="str">
-        <v>PRESIDENT</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/angel-wings/1876325893</v>
+        <v>https://music.apple.com/us/album/smoke-screen/1851033857</v>
       </c>
       <c r="L58" t="str">
-        <v>Angel Wings - PRESIDENT</v>
+        <v>Smoke Screen - Sweet Pill</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Roamer</v>
+        <v>Twisting The Knife (feat. Mckenna Grace)</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/roamer/1852775825</v>
+        <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-20</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>AngieAngieAngie</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>2:19</v>
+        <v>3:21</v>
       </c>
       <c r="H59" t="str">
-        <v>spill tab</v>
+        <v>ICE NINE KILLS</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/spill-tab/1440467280</v>
+        <v>https://music.apple.com/us/artist/ice-nine-kills/204318665</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/roamer/1852775506</v>
+        <v>https://music.apple.com/us/album/twisting-the-knife-feat-mckenna-grace/1871023713</v>
       </c>
       <c r="L59" t="str">
-        <v>Roamer - spill tab</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - ICE NINE KILLS</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>These Nights</v>
+        <v>Angel Wings</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/these-nights/1870989892</v>
+        <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-20</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Everything Glows</v>
+        <v>Angel Wings - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>4:39</v>
+        <v>3:52</v>
       </c>
       <c r="H60" t="str">
-        <v>Cannons</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/these-nights/1870989672</v>
+        <v>https://music.apple.com/us/album/angel-wings/1876325893</v>
       </c>
       <c r="L60" t="str">
-        <v>These Nights - Cannons</v>
+        <v>Angel Wings - PRESIDENT</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Locked and Loaded</v>
+        <v>Roamer</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
+        <v>https://music.apple.com/us/song/roamer/1852775825</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-20</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Locked and Loaded - Single</v>
+        <v>AngieAngieAngie</v>
       </c>
       <c r="G61" t="str">
-        <v>2:55</v>
+        <v>2:19</v>
       </c>
       <c r="H61" t="str">
-        <v>The Cab</v>
+        <v>spill tab</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/the-cab/135077748</v>
+        <v>https://music.apple.com/us/artist/spill-tab/1440467280</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/locked-and-loaded/1876992433</v>
+        <v>https://music.apple.com/us/album/roamer/1852775506</v>
       </c>
       <c r="L61" t="str">
-        <v>Locked and Loaded - The Cab</v>
+        <v>Roamer - spill tab</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Safe And Sound</v>
+        <v>These Nights</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
+        <v>https://music.apple.com/us/song/these-nights/1870989892</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-20</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>EI8HT</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G62" t="str">
-        <v>3:21</v>
+        <v>4:39</v>
       </c>
       <c r="H62" t="str">
-        <v>Shinedown</v>
+        <v>Cannons</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/safe-and-sound/1877229738</v>
+        <v>https://music.apple.com/us/album/these-nights/1870989672</v>
       </c>
       <c r="L62" t="str">
-        <v>Safe And Sound - Shinedown</v>
+        <v>These Nights - Cannons</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Flinch</v>
+        <v>Locked and Loaded</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/flinch/1863072401</v>
+        <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-20</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Autopilot</v>
+        <v>Locked and Loaded - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>2:15</v>
+        <v>2:55</v>
       </c>
       <c r="H63" t="str">
-        <v>alexsucks</v>
+        <v>The Cab</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/the-cab/135077748</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/flinch/1863072393</v>
+        <v>https://music.apple.com/us/album/locked-and-loaded/1876992433</v>
       </c>
       <c r="L63" t="str">
-        <v>Flinch - alexsucks</v>
+        <v>Locked and Loaded - The Cab</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Fall Up</v>
+        <v>Safe And Sound</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/fall-up/1874959467</v>
+        <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-20</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Fall Up - Single</v>
+        <v>EI8HT</v>
       </c>
       <c r="G64" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H64" t="str">
-        <v>VOILÀ</v>
+        <v>Shinedown</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/fall-up/1874959466</v>
+        <v>https://music.apple.com/us/album/safe-and-sound/1877229738</v>
       </c>
       <c r="L64" t="str">
-        <v>Fall Up - VOILÀ</v>
+        <v>Safe And Sound - Shinedown</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>No Typo</v>
+        <v>Flinch</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/no-typo/1872454952</v>
+        <v>https://music.apple.com/us/song/flinch/1863072401</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-20</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Free (Deluxe)</v>
+        <v>Autopilot</v>
       </c>
       <c r="G65" t="str">
-        <v>1:43</v>
+        <v>2:15</v>
       </c>
       <c r="H65" t="str">
-        <v>Nasty C</v>
+        <v>alexsucks</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/no-typo/1872454582</v>
+        <v>https://music.apple.com/us/album/flinch/1863072393</v>
       </c>
       <c r="L65" t="str">
-        <v>No Typo - Nasty C</v>
+        <v>Flinch - alexsucks</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Desiree</v>
+        <v>Fall Up</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/desiree/1852556464</v>
+        <v>https://music.apple.com/us/song/fall-up/1874959467</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-20</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Wings of Desire</v>
+        <v>Fall Up - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>3:46</v>
+        <v>3:10</v>
       </c>
       <c r="H66" t="str">
-        <v>Hemi Hemingway</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/hemi-hemingway/1560734927</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/desiree/1852556460</v>
+        <v>https://music.apple.com/us/album/fall-up/1874959466</v>
       </c>
       <c r="L66" t="str">
-        <v>Desiree - Hemi Hemingway</v>
+        <v>Fall Up - VOILÀ</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Goliath (feat. Katie Jacoby)</v>
+        <v>No Typo</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
+        <v>https://music.apple.com/us/song/no-typo/1872454952</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-20</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Goliath</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G67" t="str">
-        <v>5:04</v>
+        <v>1:43</v>
       </c>
       <c r="H67" t="str">
-        <v>Exodus</v>
+        <v>Nasty C</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/goliath-feat-katie-jacoby/1862225385</v>
+        <v>https://music.apple.com/us/album/no-typo/1872454582</v>
       </c>
       <c r="L67" t="str">
-        <v>Goliath (feat. Katie Jacoby) - Exodus</v>
+        <v>No Typo - Nasty C</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Nomad</v>
+        <v>Desiree</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/nomad/1843578167</v>
+        <v>https://music.apple.com/us/song/desiree/1852556464</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-20</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Loss</v>
+        <v>Wings of Desire</v>
       </c>
       <c r="G68" t="str">
-        <v>5:30</v>
+        <v>3:46</v>
       </c>
       <c r="H68" t="str">
-        <v>Gaerea</v>
+        <v>Hemi Hemingway</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/hemi-hemingway/1560734927</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/nomad/1843578156</v>
+        <v>https://music.apple.com/us/album/desiree/1852556460</v>
       </c>
       <c r="L68" t="str">
-        <v>Nomad - Gaerea</v>
+        <v>Desiree - Hemi Hemingway</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Empty Words</v>
+        <v>Goliath (feat. Katie Jacoby)</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/empty-words/1876625198</v>
+        <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-20</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Empty Words - Single</v>
+        <v>Goliath</v>
       </c>
       <c r="G69" t="str">
-        <v>2:32</v>
+        <v>5:04</v>
       </c>
       <c r="H69" t="str">
-        <v>Corey Kent</v>
+        <v>Exodus</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/empty-words/1876625197</v>
+        <v>https://music.apple.com/us/album/goliath-feat-katie-jacoby/1862225385</v>
       </c>
       <c r="L69" t="str">
-        <v>Empty Words - Corey Kent</v>
+        <v>Goliath (feat. Katie Jacoby) - Exodus</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Didn't Forget</v>
+        <v>Nomad</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
+        <v>https://music.apple.com/us/song/nomad/1843578167</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-20</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Didn't Forget - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G70" t="str">
-        <v>3:48</v>
+        <v>5:30</v>
       </c>
       <c r="H70" t="str">
-        <v>Waylon Wyatt</v>
+        <v>Gaerea</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/waylon-wyatt/1713519329</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/didnt-forget/1876997982</v>
+        <v>https://music.apple.com/us/album/nomad/1843578156</v>
       </c>
       <c r="L70" t="str">
-        <v>Didn't Forget - Waylon Wyatt</v>
+        <v>Nomad - Gaerea</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Euphoria</v>
+        <v>Empty Words</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1874295624</v>
+        <v>https://music.apple.com/us/song/empty-words/1876625198</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-20</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Euphoria - Single</v>
+        <v>Empty Words - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>2:14</v>
+        <v>2:32</v>
       </c>
       <c r="H71" t="str">
-        <v>Bluff City</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/bluff-city/1491129891</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1874295623</v>
+        <v>https://music.apple.com/us/album/empty-words/1876625197</v>
       </c>
       <c r="L71" t="str">
-        <v>Euphoria - Bluff City</v>
+        <v>Empty Words - Corey Kent</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>hopeless romantic</v>
+        <v>Didn't Forget</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
+        <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-20</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>hopeless romantic - Single</v>
+        <v>Didn't Forget - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:03</v>
+        <v>3:48</v>
       </c>
       <c r="H72" t="str">
-        <v>kwn</v>
+        <v>Waylon Wyatt</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/waylon-wyatt/1713519329</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/hopeless-romantic/1877131450</v>
+        <v>https://music.apple.com/us/album/didnt-forget/1876997982</v>
       </c>
       <c r="L72" t="str">
-        <v>hopeless romantic - kwn</v>
+        <v>Didn't Forget - Waylon Wyatt</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Stay Close</v>
+        <v>Euphoria</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/stay-close/1871555365</v>
+        <v>https://music.apple.com/us/song/euphoria/1874295624</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-20</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Stay Close - Single</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>2:58</v>
+        <v>2:14</v>
       </c>
       <c r="H73" t="str">
-        <v>Evelyn Cormier</v>
+        <v>Bluff City</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/evelyn-cormier/1222282253</v>
+        <v>https://music.apple.com/us/artist/bluff-city/1491129891</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/stay-close/1871555119</v>
+        <v>https://music.apple.com/us/album/euphoria/1874295623</v>
       </c>
       <c r="L73" t="str">
-        <v>Stay Close - Evelyn Cormier</v>
+        <v>Euphoria - Bluff City</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Metamorphosis</v>
+        <v>hopeless romantic</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
+        <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-20</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Metamorphosis</v>
+        <v>hopeless romantic - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:54</v>
+        <v>3:03</v>
       </c>
       <c r="H74" t="str">
-        <v>lydi lynn</v>
+        <v>kwn</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/metamorphosis/1870994803</v>
+        <v>https://music.apple.com/us/album/hopeless-romantic/1877131450</v>
       </c>
       <c r="L74" t="str">
-        <v>Metamorphosis - lydi lynn</v>
+        <v>hopeless romantic - kwn</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>peace at last</v>
+        <v>Stay Close</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
+        <v>https://music.apple.com/us/song/stay-close/1871555365</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-20</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>peace at last - Single</v>
+        <v>Stay Close - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>2:34</v>
+        <v>2:58</v>
       </c>
       <c r="H75" t="str">
-        <v>Aaron Cole</v>
+        <v>Evelyn Cormier</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
+        <v>https://music.apple.com/us/artist/evelyn-cormier/1222282253</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/peace-at-last/1870895278</v>
+        <v>https://music.apple.com/us/album/stay-close/1871555119</v>
       </c>
       <c r="L75" t="str">
-        <v>peace at last - Aaron Cole</v>
+        <v>Stay Close - Evelyn Cormier</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Aguántame</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
+        <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-20</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Aguántame - Single</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="G76" t="str">
-        <v>2:08</v>
+        <v>2:54</v>
       </c>
       <c r="H76" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/agu%C3%A1ntame/1873075917</v>
+        <v>https://music.apple.com/us/album/metamorphosis/1870994803</v>
       </c>
       <c r="L76" t="str">
-        <v>Aguántame - Banda MS de Sergio Lizárraga</v>
+        <v>Metamorphosis - lydi lynn</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Para No Hacernos Daño</v>
+        <v>peace at last</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
+        <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-20</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Para No Hacernos Daño - Single</v>
+        <v>peace at last - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:40</v>
+        <v>2:34</v>
       </c>
       <c r="H77" t="str">
-        <v>Codiciado</v>
+        <v>Aaron Cole</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
+        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/para-no-hacernos-da%C3%B1o/1872743927</v>
+        <v>https://music.apple.com/us/album/peace-at-last/1870895278</v>
       </c>
       <c r="L77" t="str">
-        <v>Para No Hacernos Daño - Codiciado</v>
+        <v>peace at last - Aaron Cole</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>NADA PERSONAL</v>
+        <v>Aguántame</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
+        <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-20</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>NADA PERSONAL - Single</v>
+        <v>Aguántame - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:11</v>
+        <v>2:08</v>
       </c>
       <c r="H78" t="str">
-        <v>La Joaqui</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/la-joaqui/1222726669</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/nada-personal/1875350196</v>
+        <v>https://music.apple.com/us/album/agu%C3%A1ntame/1873075917</v>
       </c>
       <c r="L78" t="str">
-        <v>NADA PERSONAL - La Joaqui</v>
+        <v>Aguántame - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>V3n3n0</v>
+        <v>Para No Hacernos Daño</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
+        <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-20</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>V3n3n0 - Single</v>
+        <v>Para No Hacernos Daño - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>2:32</v>
+        <v>2:40</v>
       </c>
       <c r="H79" t="str">
-        <v>Esty</v>
+        <v>Codiciado</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/esty/255471858</v>
+        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/v3n3n0/1874454944</v>
+        <v>https://music.apple.com/us/album/para-no-hacernos-da%C3%B1o/1872743927</v>
       </c>
       <c r="L79" t="str">
-        <v>V3n3n0 - Esty</v>
+        <v>Para No Hacernos Daño - Codiciado</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Moth In The Headlights</v>
+        <v>NADA PERSONAL</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
+        <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-20</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Inanimate Objects of the 21st Century</v>
+        <v>NADA PERSONAL - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>4:23</v>
+        <v>3:11</v>
       </c>
       <c r="H80" t="str">
-        <v>The Pale White</v>
+        <v>La Joaqui</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/the-pale-white/1127116907</v>
+        <v>https://music.apple.com/us/artist/la-joaqui/1222726669</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/moth-in-the-headlights/1870538540</v>
+        <v>https://music.apple.com/us/album/nada-personal/1875350196</v>
       </c>
       <c r="L80" t="str">
-        <v>Moth In The Headlights - The Pale White</v>
+        <v>NADA PERSONAL - La Joaqui</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>lately in the void</v>
+        <v>V3n3n0</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
+        <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-20</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>lately in the void - EP</v>
+        <v>V3n3n0 - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:41</v>
+        <v>2:32</v>
       </c>
       <c r="H81" t="str">
-        <v>bad tuner</v>
+        <v>Esty</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/bad-tuner/1051446214</v>
+        <v>https://music.apple.com/us/artist/esty/255471858</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/lately-in-the-void/1847993191</v>
+        <v>https://music.apple.com/us/album/v3n3n0/1874454944</v>
       </c>
       <c r="L81" t="str">
-        <v>lately in the void - bad tuner</v>
+        <v>V3n3n0 - Esty</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>When I Fall in Love</v>
+        <v>Moth In The Headlights</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
+        <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-20</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Nightjar</v>
+        <v>Inanimate Objects of the 21st Century</v>
       </c>
       <c r="G82" t="str">
-        <v>4:45</v>
+        <v>4:23</v>
       </c>
       <c r="H82" t="str">
-        <v>David Gray</v>
+        <v>The Pale White</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/david-gray/316381</v>
+        <v>https://music.apple.com/us/artist/the-pale-white/1127116907</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/when-i-fall-in-love/1860381106</v>
+        <v>https://music.apple.com/us/album/moth-in-the-headlights/1870538540</v>
       </c>
       <c r="L82" t="str">
-        <v>When I Fall in Love - David Gray</v>
+        <v>Moth In The Headlights - The Pale White</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Repeat Offender</v>
+        <v>lately in the void</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
+        <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-20</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Repeat Offender - Single</v>
+        <v>lately in the void - EP</v>
       </c>
       <c r="G83" t="str">
-        <v>2:33</v>
+        <v>3:41</v>
       </c>
       <c r="H83" t="str">
-        <v>yeemz</v>
+        <v>bad tuner</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/yeemz/1561474492</v>
+        <v>https://music.apple.com/us/artist/bad-tuner/1051446214</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/repeat-offender/1873099828</v>
+        <v>https://music.apple.com/us/album/lately-in-the-void/1847993191</v>
       </c>
       <c r="L83" t="str">
-        <v>Repeat Offender - yeemz</v>
+        <v>lately in the void - bad tuner</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Class Reunion</v>
+        <v>When I Fall in Love</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
+        <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-20</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>We Swallowed The Sky</v>
+        <v>Nightjar</v>
       </c>
       <c r="G84" t="str">
-        <v>4:11</v>
+        <v>4:45</v>
       </c>
       <c r="H84" t="str">
-        <v>Beatrix</v>
+        <v>David Gray</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/beatrix/1732651124</v>
+        <v>https://music.apple.com/us/artist/david-gray/316381</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/class-reunion/1876698281</v>
+        <v>https://music.apple.com/us/album/when-i-fall-in-love/1860381106</v>
       </c>
       <c r="L84" t="str">
-        <v>Class Reunion - Beatrix</v>
+        <v>When I Fall in Love - David Gray</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Promise Me</v>
+        <v>Repeat Offender</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/promise-me/1848977981</v>
+        <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-20</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Instant Comfort</v>
+        <v>Repeat Offender - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>5:34</v>
+        <v>2:33</v>
       </c>
       <c r="H85" t="str">
-        <v>Lucid Express</v>
+        <v>yeemz</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/lucid-express/1560683497</v>
+        <v>https://music.apple.com/us/artist/yeemz/1561474492</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/promise-me/1848977978</v>
+        <v>https://music.apple.com/us/album/repeat-offender/1873099828</v>
       </c>
       <c r="L85" t="str">
-        <v>Promise Me - Lucid Express</v>
+        <v>Repeat Offender - yeemz</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions)</v>
+        <v>Class Reunion</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
+        <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-20</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Awe Mah (feat. Shakes &amp; Les, MK Productions &amp; Funky Qla) - Single</v>
+        <v>We Swallowed The Sky</v>
       </c>
       <c r="G86" t="str">
-        <v>3:33</v>
+        <v>4:11</v>
       </c>
       <c r="H86" t="str">
-        <v>Zee Nxumalo</v>
+        <v>Beatrix</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
+        <v>https://music.apple.com/us/artist/beatrix/1732651124</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873675</v>
+        <v>https://music.apple.com/us/album/class-reunion/1876698281</v>
       </c>
       <c r="L86" t="str">
-        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions) - Zee Nxumalo</v>
+        <v>Class Reunion - Beatrix</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Hit and Run (feat. AZ Chike)</v>
+        <v>Promise Me</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
+        <v>https://music.apple.com/us/song/promise-me/1848977981</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-20</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Hit and Run (feat. AZ Chike) - Single</v>
+        <v>Instant Comfort</v>
       </c>
       <c r="G87" t="str">
-        <v>3:19</v>
+        <v>5:34</v>
       </c>
       <c r="H87" t="str">
-        <v>Ray Vaughn</v>
+        <v>Lucid Express</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
+        <v>https://music.apple.com/us/artist/lucid-express/1560683497</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/hit-and-run-feat-az-chike/1877912892</v>
+        <v>https://music.apple.com/us/album/promise-me/1848977978</v>
       </c>
       <c r="L87" t="str">
-        <v>Hit and Run (feat. AZ Chike) - Ray Vaughn</v>
+        <v>Promise Me - Lucid Express</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>So Good</v>
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions)</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/so-good/1874733689</v>
+        <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-20</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>So Good - Single</v>
+        <v>Awe Mah (feat. Shakes &amp; Les, MK Productions &amp; Funky Qla) - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>2:47</v>
+        <v>3:33</v>
       </c>
       <c r="H88" t="str">
-        <v>Ari Abdul</v>
+        <v>Zee Nxumalo</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/ari-abdul/1606828852</v>
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/so-good/1874733688</v>
+        <v>https://music.apple.com/us/album/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873675</v>
       </c>
       <c r="L88" t="str">
-        <v>So Good - Ari Abdul</v>
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions) - Zee Nxumalo</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>YDH</v>
+        <v>Hit and Run (feat. AZ Chike)</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/ydh/1874940744</v>
+        <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-20</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>YDH - Single</v>
+        <v>Hit and Run (feat. AZ Chike) - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>3:17</v>
+        <v>3:19</v>
       </c>
       <c r="H89" t="str">
-        <v>Chloe Qisha</v>
+        <v>Ray Vaughn</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
+        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/ydh/1874940739</v>
+        <v>https://music.apple.com/us/album/hit-and-run-feat-az-chike/1877912892</v>
       </c>
       <c r="L89" t="str">
-        <v>YDH - Chloe Qisha</v>
+        <v>Hit and Run (feat. AZ Chike) - Ray Vaughn</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Eucalyptus</v>
+        <v>So Good</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
+        <v>https://music.apple.com/us/song/so-good/1874733689</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-20</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Porcelain</v>
+        <v>So Good - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>3:00</v>
+        <v>2:47</v>
       </c>
       <c r="H90" t="str">
-        <v>Peach PRC</v>
+        <v>Ari Abdul</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
+        <v>https://music.apple.com/us/artist/ari-abdul/1606828852</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/eucalyptus/1861380240</v>
+        <v>https://music.apple.com/us/album/so-good/1874733688</v>
       </c>
       <c r="L90" t="str">
-        <v>Eucalyptus - Peach PRC</v>
+        <v>So Good - Ari Abdul</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Pearls In The Trap</v>
+        <v>YDH</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
+        <v>https://music.apple.com/us/song/ydh/1874940744</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-20</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Pearls In The Trap - Single</v>
+        <v>YDH - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>1:38</v>
+        <v>3:17</v>
       </c>
       <c r="H91" t="str">
-        <v>carolesdaughter</v>
+        <v>Chloe Qisha</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/carolesdaughter/1502564996</v>
+        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/pearls-in-the-trap/1877892476</v>
+        <v>https://music.apple.com/us/album/ydh/1874940739</v>
       </c>
       <c r="L91" t="str">
-        <v>Pearls In The Trap - carolesdaughter</v>
+        <v>YDH - Chloe Qisha</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>The Fever Mask</v>
+        <v>Eucalyptus</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
+        <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-20</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>Porcelain</v>
       </c>
       <c r="G92" t="str">
-        <v>3:12</v>
+        <v>3:00</v>
       </c>
       <c r="H92" t="str">
-        <v>At The Gates</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/the-fever-mask/1873364809</v>
+        <v>https://music.apple.com/us/album/eucalyptus/1861380240</v>
       </c>
       <c r="L92" t="str">
-        <v>The Fever Mask - At The Gates</v>
+        <v>Eucalyptus - Peach PRC</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>The Air's on Fire</v>
+        <v>Pearls In The Trap</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
+        <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-20</v>
@@ -3909,68 +3909,144 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Location Lost</v>
+        <v>Pearls In The Trap - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>5:15</v>
+        <v>1:38</v>
       </c>
       <c r="H93" t="str">
-        <v>Failure</v>
+        <v>carolesdaughter</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/failure/1646309</v>
+        <v>https://music.apple.com/us/artist/carolesdaughter/1502564996</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/the-airs-on-fire/1867015665</v>
+        <v>https://music.apple.com/us/album/pearls-in-the-trap/1877892476</v>
       </c>
       <c r="L93" t="str">
-        <v>The Air's on Fire - Failure</v>
+        <v>Pearls In The Trap - carolesdaughter</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
+        <v>The Fever Mask</v>
+      </c>
+      <c r="B94" t="str">
+        <v/>
+      </c>
+      <c r="C94" t="str">
+        <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
+      </c>
+      <c r="D94" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v>The Ghost of a Future Dead</v>
+      </c>
+      <c r="G94" t="str">
+        <v>3:12</v>
+      </c>
+      <c r="H94" t="str">
+        <v>At The Gates</v>
+      </c>
+      <c r="I94" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J94" t="str">
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+      </c>
+      <c r="K94" t="str">
+        <v>https://music.apple.com/us/album/the-fever-mask/1873364809</v>
+      </c>
+      <c r="L94" t="str">
+        <v>The Fever Mask - At The Gates</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>The Air's on Fire</v>
+      </c>
+      <c r="B95" t="str">
+        <v/>
+      </c>
+      <c r="C95" t="str">
+        <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
+      </c>
+      <c r="D95" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v>Location Lost</v>
+      </c>
+      <c r="G95" t="str">
+        <v>5:15</v>
+      </c>
+      <c r="H95" t="str">
+        <v>Failure</v>
+      </c>
+      <c r="I95" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J95" t="str">
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
+      </c>
+      <c r="K95" t="str">
+        <v>https://music.apple.com/us/album/the-airs-on-fire/1867015665</v>
+      </c>
+      <c r="L95" t="str">
+        <v>The Air's on Fire - Failure</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
         <v>To The Last Breath</v>
       </c>
-      <c r="B94" t="str">
-        <v/>
-      </c>
-      <c r="C94" t="str">
+      <c r="B96" t="str">
+        <v/>
+      </c>
+      <c r="C96" t="str">
         <v>https://music.apple.com/us/song/to-the-last-breath/1874618974</v>
       </c>
-      <c r="D94" t="str">
-        <v>2026-02-20</v>
-      </c>
-      <c r="E94" t="str">
-        <v/>
-      </c>
-      <c r="F94" t="str">
+      <c r="D96" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
         <v>To The Last Breath - Single</v>
       </c>
-      <c r="G94" t="str">
+      <c r="G96" t="str">
         <v>4:57</v>
       </c>
-      <c r="H94" t="str">
+      <c r="H96" t="str">
         <v>Arch Enemy</v>
       </c>
-      <c r="I94" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J94" t="str">
+      <c r="I96" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J96" t="str">
         <v>https://music.apple.com/us/artist/arch-enemy/18098340</v>
       </c>
-      <c r="K94" t="str">
+      <c r="K96" t="str">
         <v>https://music.apple.com/us/album/to-the-last-breath/1874618973</v>
       </c>
-      <c r="L94" t="str">
+      <c r="L96" t="str">
         <v>To The Last Breath - Arch Enemy</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L94"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L96"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L97"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1006,13 +1006,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Begging for Change</v>
+        <v>Iris (Live from Apple Music Studios)</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/begging-for-change/1870313832</v>
+        <v>https://music.apple.com/us/song/iris-live-from-apple-music-studios/1877215177</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-20</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>HELP(2)</v>
+        <v>Iris (Live from Apple Music Studios) - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>4:20</v>
+        <v>4:18</v>
       </c>
       <c r="H17" t="str">
-        <v>Pulp</v>
+        <v>The Goo Goo Dolls</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/pulp/312518</v>
+        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/begging-for-change/1870313498</v>
+        <v>https://music.apple.com/us/album/iris-live-from-apple-music-studios/1877215171</v>
       </c>
       <c r="L17" t="str">
-        <v>Begging for Change - Pulp</v>
+        <v>Iris (Live from Apple Music Studios) - The Goo Goo Dolls</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>My Maker</v>
+        <v>Begging for Change</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/my-maker/1862845748</v>
+        <v>https://music.apple.com/us/song/begging-for-change/1870313832</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-20</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Ricochet</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G18" t="str">
-        <v>4:19</v>
+        <v>4:20</v>
       </c>
       <c r="H18" t="str">
-        <v>Snail Mail</v>
+        <v>Pulp</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/pulp/312518</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/my-maker/1862845733</v>
+        <v>https://music.apple.com/us/album/begging-for-change/1870313498</v>
       </c>
       <c r="L18" t="str">
-        <v>My Maker - Snail Mail</v>
+        <v>Begging for Change - Pulp</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Opalite (BUNT. Remix)</v>
+        <v>My Maker</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/opalite-bunt-remix/1878183696</v>
+        <v>https://music.apple.com/us/song/my-maker/1862845748</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-20</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Opalite (BUNT. Remix) - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G19" t="str">
-        <v>3:32</v>
+        <v>4:19</v>
       </c>
       <c r="H19" t="str">
-        <v>Taylor Swift</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/opalite-bunt-remix/1878183335</v>
+        <v>https://music.apple.com/us/album/my-maker/1862845733</v>
       </c>
       <c r="L19" t="str">
-        <v>Opalite (BUNT. Remix) - Taylor Swift</v>
+        <v>My Maker - Snail Mail</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)")</v>
+        <v>Opalite (BUNT. Remix)</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/such-great-heights-from-tell-me-lies-season-3/1872222695</v>
+        <v>https://music.apple.com/us/song/opalite-bunt-remix/1878183696</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-20</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - Single</v>
+        <v>Opalite (BUNT. Remix) - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>4:27</v>
+        <v>3:32</v>
       </c>
       <c r="H20" t="str">
-        <v>CHVRCHES</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/such-great-heights-from-tell-me-lies-season-3/1872222683</v>
+        <v>https://music.apple.com/us/album/opalite-bunt-remix/1878183335</v>
       </c>
       <c r="L20" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
+        <v>Opalite (BUNT. Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>She Knows Too Much</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)")</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/she-knows-too-much/1861531670</v>
+        <v>https://music.apple.com/us/song/such-great-heights-from-tell-me-lies-season-3/1872222695</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-20</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Distracted</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>3:33</v>
+        <v>4:27</v>
       </c>
       <c r="H21" t="str">
-        <v>Thundercat</v>
+        <v>CHVRCHES</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/she-knows-too-much/1861531667</v>
+        <v>https://music.apple.com/us/album/such-great-heights-from-tell-me-lies-season-3/1872222683</v>
       </c>
       <c r="L21" t="str">
-        <v>She Knows Too Much - Thundercat</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Tea Time</v>
+        <v>She Knows Too Much</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/tea-time/1877002914</v>
+        <v>https://music.apple.com/us/song/she-knows-too-much/1861531670</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-20</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Tea Time - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G22" t="str">
-        <v>2:25</v>
+        <v>3:33</v>
       </c>
       <c r="H22" t="str">
-        <v>Yung Miami</v>
+        <v>Thundercat</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/yung-miami/1476226954</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/tea-time/1877002906</v>
+        <v>https://music.apple.com/us/album/she-knows-too-much/1861531667</v>
       </c>
       <c r="L22" t="str">
-        <v>Tea Time - Yung Miami</v>
+        <v>She Knows Too Much - Thundercat</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>full moon. (fall in tokyo) [bonus track]</v>
+        <v>Tea Time</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/full-moon-fall-in-tokyo-bonus-track/1877180113</v>
+        <v>https://music.apple.com/us/song/tea-time/1877002914</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-20</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Icon (Director's Cut)</v>
+        <v>Tea Time - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>3:12</v>
+        <v>2:25</v>
       </c>
       <c r="H23" t="str">
-        <v>Brent Faiyaz</v>
+        <v>Yung Miami</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/yung-miami/1476226954</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/full-moon-fall-in-tokyo-bonus-track/1877179580</v>
+        <v>https://music.apple.com/us/album/tea-time/1877002906</v>
       </c>
       <c r="L23" t="str">
-        <v>full moon. (fall in tokyo) [bonus track] - Brent Faiyaz</v>
+        <v>Tea Time - Yung Miami</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Save My Love</v>
+        <v>full moon. (fall in tokyo) [bonus track]</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/save-my-love/1876235280</v>
+        <v>https://music.apple.com/us/song/full-moon-fall-in-tokyo-bonus-track/1877180113</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-20</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Save My Love - Single</v>
+        <v>Icon (Director's Cut)</v>
       </c>
       <c r="G24" t="str">
-        <v>3:30</v>
+        <v>3:12</v>
       </c>
       <c r="H24" t="str">
-        <v>Kygo</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/save-my-love/1876235273</v>
+        <v>https://music.apple.com/us/album/full-moon-fall-in-tokyo-bonus-track/1877179580</v>
       </c>
       <c r="L24" t="str">
-        <v>Save My Love - Kygo</v>
+        <v>full moon. (fall in tokyo) [bonus track] - Brent Faiyaz</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>FOREVER TU GANTEL</v>
+        <v>Save My Love</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/forever-tu-gantel/1877482427</v>
+        <v>https://music.apple.com/us/song/save-my-love/1876235280</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-20</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>POR SI MAÑANA NO ESTOY</v>
+        <v>Save My Love - Single</v>
       </c>
       <c r="G25" t="str">
-        <v>3:46</v>
+        <v>3:30</v>
       </c>
       <c r="H25" t="str">
-        <v>Omar Courtz</v>
+        <v>Kygo</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/omar-courtz/1370744631</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/forever-tu-gantel/1877481995</v>
+        <v>https://music.apple.com/us/album/save-my-love/1876235273</v>
       </c>
       <c r="L25" t="str">
-        <v>FOREVER TU GANTEL - Omar Courtz</v>
+        <v>Save My Love - Kygo</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Suburban Requiem</v>
+        <v>FOREVER TU GANTEL</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/suburban-requiem/1874720791</v>
+        <v>https://music.apple.com/us/song/forever-tu-gantel/1877482427</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-20</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Idols (Complete)</v>
+        <v>POR SI MAÑANA NO ESTOY</v>
       </c>
       <c r="G26" t="str">
-        <v>4:39</v>
+        <v>3:46</v>
       </c>
       <c r="H26" t="str">
-        <v>YUNGBLUD</v>
+        <v>Omar Courtz</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/yungblud/213048599</v>
+        <v>https://music.apple.com/us/artist/omar-courtz/1370744631</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/suburban-requiem/1874720357</v>
+        <v>https://music.apple.com/us/album/forever-tu-gantel/1877481995</v>
       </c>
       <c r="L26" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>FOREVER TU GANTEL - Omar Courtz</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Good Grief</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/good-grief/1869516030</v>
+        <v>https://music.apple.com/us/song/suburban-requiem/1874720791</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-20</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>(((((ultraSOUND)))))+</v>
+        <v>Idols (Complete)</v>
       </c>
       <c r="G27" t="str">
-        <v>4:21</v>
+        <v>4:39</v>
       </c>
       <c r="H27" t="str">
-        <v>The Neighbourhood</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/the-neighbourhood/219350813</v>
+        <v>https://music.apple.com/us/artist/yungblud/213048599</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/good-grief/1869516027</v>
+        <v>https://music.apple.com/us/album/suburban-requiem/1874720357</v>
       </c>
       <c r="L27" t="str">
-        <v>Good Grief - The Neighbourhood</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Freak On</v>
+        <v>Good Grief</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/freak-on/1874265564</v>
+        <v>https://music.apple.com/us/song/good-grief/1869516030</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-20</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Freak On - Single</v>
+        <v>(((((ultraSOUND)))))+</v>
       </c>
       <c r="G28" t="str">
-        <v>2:49</v>
+        <v>4:21</v>
       </c>
       <c r="H28" t="str">
-        <v>Steve Aoki</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/the-neighbourhood/219350813</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/freak-on/1874265561</v>
+        <v>https://music.apple.com/us/album/good-grief/1869516027</v>
       </c>
       <c r="L28" t="str">
-        <v>Freak On - Steve Aoki</v>
+        <v>Good Grief - The Neighbourhood</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Science (feat. Stevie Appleton) [Radio Edit]</v>
+        <v>Freak On</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/science-feat-stevie-appleton-radio-edit/1871036143</v>
+        <v>https://music.apple.com/us/song/freak-on/1874265564</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-20</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Science (feat. Stevie Appleton) - Single</v>
+        <v>Freak On - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>3:32</v>
+        <v>2:49</v>
       </c>
       <c r="H29" t="str">
-        <v>deadmau5</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/science-feat-stevie-appleton-radio-edit/1871036141</v>
+        <v>https://music.apple.com/us/album/freak-on/1874265561</v>
       </c>
       <c r="L29" t="str">
-        <v>Science (feat. Stevie Appleton) [Radio Edit] - deadmau5</v>
+        <v>Freak On - Steve Aoki</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Opalite (Skream Remix)</v>
+        <v>Science (feat. Stevie Appleton) [Radio Edit]</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/opalite-skream-remix/1878173708</v>
+        <v>https://music.apple.com/us/song/science-feat-stevie-appleton-radio-edit/1871036143</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-20</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Opalite (Skream Remix) - Single</v>
+        <v>Science (feat. Stevie Appleton) - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>3:55</v>
+        <v>3:32</v>
       </c>
       <c r="H30" t="str">
-        <v>Taylor Swift</v>
+        <v>deadmau5</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/opalite-skream-remix/1878173707</v>
+        <v>https://music.apple.com/us/album/science-feat-stevie-appleton-radio-edit/1871036141</v>
       </c>
       <c r="L30" t="str">
-        <v>Opalite (Skream Remix) - Taylor Swift</v>
+        <v>Science (feat. Stevie Appleton) [Radio Edit] - deadmau5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Yellow Eyes</v>
+        <v>Opalite (Skream Remix)</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
+        <v>https://music.apple.com/us/song/opalite-skream-remix/1878173708</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-20</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Jean</v>
+        <v>Opalite (Skream Remix) - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>2:42</v>
+        <v>3:55</v>
       </c>
       <c r="H31" t="str">
-        <v>Yebba</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/yellow-eyes/1877157664</v>
+        <v>https://music.apple.com/us/album/opalite-skream-remix/1878173707</v>
       </c>
       <c r="L31" t="str">
-        <v>Yellow Eyes - Yebba</v>
+        <v>Opalite (Skream Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Word On The Street</v>
+        <v>Yellow Eyes</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
+        <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-20</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Word On The Street - Single</v>
+        <v>Jean</v>
       </c>
       <c r="G32" t="str">
-        <v>2:56</v>
+        <v>2:42</v>
       </c>
       <c r="H32" t="str">
-        <v>Luke Bryan</v>
+        <v>Yebba</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/word-on-the-street/1876607713</v>
+        <v>https://music.apple.com/us/album/yellow-eyes/1877157664</v>
       </c>
       <c r="L32" t="str">
-        <v>Word On The Street - Luke Bryan</v>
+        <v>Yellow Eyes - Yebba</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>only the best</v>
+        <v>Word On The Street</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
+        <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-20</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>only the best - Single</v>
+        <v>Word On The Street - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>3:22</v>
+        <v>2:56</v>
       </c>
       <c r="H33" t="str">
-        <v>horsegiirL</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/only-the-best/1876048174</v>
+        <v>https://music.apple.com/us/album/word-on-the-street/1876607713</v>
       </c>
       <c r="L33" t="str">
-        <v>only the best - horsegiirL</v>
+        <v>Word On The Street - Luke Bryan</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Beautiful Places</v>
+        <v>only the best</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/beautiful-places/1876326643</v>
+        <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-20</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Beautiful Places - Single</v>
+        <v>only the best - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>2:59</v>
+        <v>3:22</v>
       </c>
       <c r="H34" t="str">
-        <v>Tiësto</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/ti%C3%ABsto/4091218</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/beautiful-places/1876326642</v>
+        <v>https://music.apple.com/us/album/only-the-best/1876048174</v>
       </c>
       <c r="L34" t="str">
-        <v>Beautiful Places - Tiësto</v>
+        <v>only the best - horsegiirL</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>STAMPEDE</v>
+        <v>Beautiful Places</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/stampede/1868995802</v>
+        <v>https://music.apple.com/us/song/beautiful-places/1876326643</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-20</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>STAMPEDE - Single</v>
+        <v>Beautiful Places - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>3:09</v>
+        <v>2:59</v>
       </c>
       <c r="H35" t="str">
-        <v>Genesis Owusu</v>
+        <v>Tiësto</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/ti%C3%ABsto/4091218</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/stampede/1868995797</v>
+        <v>https://music.apple.com/us/album/beautiful-places/1876326642</v>
       </c>
       <c r="L35" t="str">
-        <v>STAMPEDE - Genesis Owusu</v>
+        <v>Beautiful Places - Tiësto</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Infinite Beach</v>
+        <v>STAMPEDE</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/infinite-beach/1858554535</v>
+        <v>https://music.apple.com/us/song/stampede/1868995802</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-20</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Mārara</v>
+        <v>STAMPEDE - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>3:10</v>
+        <v>3:09</v>
       </c>
       <c r="H36" t="str">
-        <v>15 15</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/infinite-beach/1858554036</v>
+        <v>https://music.apple.com/us/album/stampede/1868995797</v>
       </c>
       <c r="L36" t="str">
-        <v>Infinite Beach - 15 15</v>
+        <v>STAMPEDE - Genesis Owusu</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Championship Ring</v>
+        <v>Infinite Beach</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/championship-ring/1875186768</v>
+        <v>https://music.apple.com/us/song/infinite-beach/1858554535</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-20</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>I Want Blood</v>
+        <v>Mārara</v>
       </c>
       <c r="G37" t="str">
-        <v>3:41</v>
+        <v>3:10</v>
       </c>
       <c r="H37" t="str">
-        <v>SleazyWorld Go</v>
+        <v>15 15</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/sleazyworld-go/1503917115</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/championship-ring/1875186762</v>
+        <v>https://music.apple.com/us/album/infinite-beach/1858554036</v>
       </c>
       <c r="L37" t="str">
-        <v>Championship Ring - SleazyWorld Go</v>
+        <v>Infinite Beach - 15 15</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>miss u 2 (with Leon Thomas)</v>
+        <v>Championship Ring</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
+        <v>https://music.apple.com/us/song/championship-ring/1875186768</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-20</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>girl music vol. 1 - EP</v>
+        <v>I Want Blood</v>
       </c>
       <c r="G38" t="str">
-        <v>2:28</v>
+        <v>3:41</v>
       </c>
       <c r="H38" t="str">
-        <v>Ty Dolla $ign</v>
+        <v>SleazyWorld Go</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
+        <v>https://music.apple.com/us/artist/sleazyworld-go/1503917115</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/miss-u-2-with-leon-thomas/1878416755</v>
+        <v>https://music.apple.com/us/album/championship-ring/1875186762</v>
       </c>
       <c r="L38" t="str">
-        <v>miss u 2 (with Leon Thomas) - Ty Dolla $ign</v>
+        <v>Championship Ring - SleazyWorld Go</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ILRB (feat. Babyface Ray)</v>
+        <v>miss u 2 (with Leon Thomas)</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
+        <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-20</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Da Realest</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G39" t="str">
-        <v>1:51</v>
+        <v>2:28</v>
       </c>
       <c r="H39" t="str">
-        <v>Babyfxce E</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/ilrb-feat-babyface-ray/1860991661</v>
+        <v>https://music.apple.com/us/album/miss-u-2-with-leon-thomas/1878416755</v>
       </c>
       <c r="L39" t="str">
-        <v>ILRB (feat. Babyface Ray) - Babyfxce E</v>
+        <v>miss u 2 (with Leon Thomas) - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Fine Shit</v>
+        <v>ILRB (feat. Babyface Ray)</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
+        <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-20</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Fine Shit - Single</v>
+        <v>Da Realest</v>
       </c>
       <c r="G40" t="str">
-        <v>1:53</v>
+        <v>1:51</v>
       </c>
       <c r="H40" t="str">
-        <v>Real Boston Richey</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/fine-shit/1878172115</v>
+        <v>https://music.apple.com/us/album/ilrb-feat-babyface-ray/1860991661</v>
       </c>
       <c r="L40" t="str">
-        <v>Fine Shit - Real Boston Richey</v>
+        <v>ILRB (feat. Babyface Ray) - Babyfxce E</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>What's Your Name</v>
+        <v>Fine Shit</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
+        <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-20</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>What's Your Name - Single</v>
+        <v>Fine Shit - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>2:20</v>
+        <v>1:53</v>
       </c>
       <c r="H41" t="str">
-        <v>Soulidified</v>
+        <v>Real Boston Richey</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/soulidified/1824036220</v>
+        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/whats-your-name/1878121935</v>
+        <v>https://music.apple.com/us/album/fine-shit/1878172115</v>
       </c>
       <c r="L41" t="str">
-        <v>What's Your Name - Soulidified</v>
+        <v>Fine Shit - Real Boston Richey</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Ends In Y</v>
+        <v>What's Your Name</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
+        <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-20</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>What's Your Name - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>2:53</v>
+        <v>2:20</v>
       </c>
       <c r="H42" t="str">
-        <v>Mimi Webb</v>
+        <v>Soulidified</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/soulidified/1824036220</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/ends-in-y/1870981483</v>
+        <v>https://music.apple.com/us/album/whats-your-name/1878121935</v>
       </c>
       <c r="L42" t="str">
-        <v>Ends In Y - Mimi Webb</v>
+        <v>What's Your Name - Soulidified</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Bully</v>
+        <v>Ends In Y</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/bully/1874401861</v>
+        <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-20</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Bully - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G43" t="str">
-        <v>3:05</v>
+        <v>2:53</v>
       </c>
       <c r="H43" t="str">
-        <v>Iris Copperman</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/bully/1874401857</v>
+        <v>https://music.apple.com/us/album/ends-in-y/1870981483</v>
       </c>
       <c r="L43" t="str">
-        <v>Bully - Iris Copperman</v>
+        <v>Ends In Y - Mimi Webb</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>MC24 (1:4)</v>
+        <v>Bully</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
+        <v>https://music.apple.com/us/song/bully/1874401861</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-20</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>MC24 &amp; SIN24 - Single</v>
+        <v>Bully - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>3:16</v>
+        <v>3:05</v>
       </c>
       <c r="H44" t="str">
-        <v>Charles Leclerc</v>
+        <v>Iris Copperman</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/charles-leclerc/1687977492</v>
+        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/mc24-1-4/1793396725</v>
+        <v>https://music.apple.com/us/album/bully/1874401857</v>
       </c>
       <c r="L44" t="str">
-        <v>MC24 (1:4) - Charles Leclerc</v>
+        <v>Bully - Iris Copperman</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Ride</v>
+        <v>MC24 (1:4)</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/ride/1869414360</v>
+        <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-20</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Superbloom</v>
+        <v>MC24 &amp; SIN24 - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>4:39</v>
+        <v>3:16</v>
       </c>
       <c r="H45" t="str">
-        <v>Jessie Ware</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/charles-leclerc/1687977492</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/ride/1869414259</v>
+        <v>https://music.apple.com/us/album/mc24-1-4/1793396725</v>
       </c>
       <c r="L45" t="str">
-        <v>Ride - Jessie Ware</v>
+        <v>MC24 (1:4) - Charles Leclerc</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Arkansas Mud</v>
+        <v>Ride</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
+        <v>https://music.apple.com/us/song/ride/1869414360</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-20</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Arkansas Mud - Single</v>
+        <v>Superbloom</v>
       </c>
       <c r="G46" t="str">
-        <v>4:18</v>
+        <v>4:39</v>
       </c>
       <c r="H46" t="str">
-        <v>Ashley McBryde</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/arkansas-mud/1874413516</v>
+        <v>https://music.apple.com/us/album/ride/1869414259</v>
       </c>
       <c r="L46" t="str">
-        <v>Arkansas Mud - Ashley McBryde</v>
+        <v>Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Don't Leave</v>
+        <v>Arkansas Mud</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
+        <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-20</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Don't Leave - Single</v>
+        <v>Arkansas Mud - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>2:10</v>
+        <v>4:18</v>
       </c>
       <c r="H47" t="str">
-        <v>Jorja Smith</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/dont-leave/1872418571</v>
+        <v>https://music.apple.com/us/album/arkansas-mud/1874413516</v>
       </c>
       <c r="L47" t="str">
-        <v>Don't Leave - Jorja Smith</v>
+        <v>Arkansas Mud - Ashley McBryde</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>FLAMED UP</v>
+        <v>Don't Leave</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
+        <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-20</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>FLAMED UP - Single</v>
+        <v>Don't Leave - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>2:31</v>
+        <v>2:10</v>
       </c>
       <c r="H48" t="str">
-        <v>JayDon</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/jaydon/1773146127</v>
+        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/flamed-up/1876888777</v>
+        <v>https://music.apple.com/us/album/dont-leave/1872418571</v>
       </c>
       <c r="L48" t="str">
-        <v>FLAMED UP - JayDon</v>
+        <v>Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>3am in Paris</v>
+        <v>FLAMED UP</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
+        <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-20</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>3am in Paris - Single</v>
+        <v>FLAMED UP - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>2:49</v>
+        <v>2:31</v>
       </c>
       <c r="H49" t="str">
-        <v>Anais Cardot</v>
+        <v>JayDon</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/jaydon/1773146127</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/3am-in-paris/1838055453</v>
+        <v>https://music.apple.com/us/album/flamed-up/1876888777</v>
       </c>
       <c r="L49" t="str">
-        <v>3am in Paris - Anais Cardot</v>
+        <v>FLAMED UP - JayDon</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>I Got Saved (feat. Chris Brown) [Live]</v>
+        <v>3am in Paris</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
+        <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-20</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>3am in Paris - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>5:13</v>
+        <v>2:49</v>
       </c>
       <c r="H50" t="str">
-        <v>Elevation Worship</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/i-got-saved-feat-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/3am-in-paris/1838055453</v>
       </c>
       <c r="L50" t="str">
-        <v>I Got Saved (feat. Chris Brown) [Live] - Elevation Worship</v>
+        <v>3am in Paris - Anais Cardot</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Migajero</v>
+        <v>I Got Saved (feat. Chris Brown) [Live]</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/migajero/1873051149</v>
+        <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-20</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Migajero - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G51" t="str">
-        <v>3:18</v>
+        <v>5:13</v>
       </c>
       <c r="H51" t="str">
-        <v>Grupo Marca Registrada</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/grupo-marca-registrada/1051127522</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/migajero/1873051145</v>
+        <v>https://music.apple.com/us/album/i-got-saved-feat-chris-brown-live/1870678481</v>
       </c>
       <c r="L51" t="str">
-        <v>Migajero - Grupo Marca Registrada</v>
+        <v>I Got Saved (feat. Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Opalite (Ely Oaks Remix)</v>
+        <v>Migajero</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
+        <v>https://music.apple.com/us/song/migajero/1873051149</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-20</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Opalite (Ely Oaks Remix) - Single</v>
+        <v>Migajero - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>3:26</v>
+        <v>3:18</v>
       </c>
       <c r="H52" t="str">
-        <v>Taylor Swift</v>
+        <v>Grupo Marca Registrada</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/grupo-marca-registrada/1051127522</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/opalite-ely-oaks-remix/1878155587</v>
+        <v>https://music.apple.com/us/album/migajero/1873051145</v>
       </c>
       <c r="L52" t="str">
-        <v>Opalite (Ely Oaks Remix) - Taylor Swift</v>
+        <v>Migajero - Grupo Marca Registrada</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Old Man</v>
+        <v>Opalite (Ely Oaks Remix)</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/old-man/1872189176</v>
+        <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-20</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Old Man - Single</v>
+        <v>Opalite (Ely Oaks Remix) - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>4:05</v>
+        <v>3:26</v>
       </c>
       <c r="H53" t="str">
-        <v>Trousdale</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/old-man/1872189159</v>
+        <v>https://music.apple.com/us/album/opalite-ely-oaks-remix/1878155587</v>
       </c>
       <c r="L53" t="str">
-        <v>Old Man - Trousdale</v>
+        <v>Opalite (Ely Oaks Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Of Joy (feat. ARY)</v>
+        <v>Old Man</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
+        <v>https://music.apple.com/us/song/old-man/1872189176</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-20</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Of Joy (feat. ARY) - Single</v>
+        <v>Old Man - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>3:19</v>
+        <v>4:05</v>
       </c>
       <c r="H54" t="str">
-        <v>DJ Seinfeld</v>
+        <v>Trousdale</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/of-joy-feat-ary/1870539616</v>
+        <v>https://music.apple.com/us/album/old-man/1872189159</v>
       </c>
       <c r="L54" t="str">
-        <v>Of Joy (feat. ARY) - DJ Seinfeld</v>
+        <v>Old Man - Trousdale</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg)</v>
+        <v>Of Joy (feat. ARY)</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
+        <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-20</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>Of Joy (feat. ARY) - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>2:56</v>
+        <v>3:19</v>
       </c>
       <c r="H55" t="str">
-        <v>Denzel Curry</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/the-scythe-feat-tiacorine-a%24ap-ferg/1868519270</v>
+        <v>https://music.apple.com/us/album/of-joy-feat-ary/1870539616</v>
       </c>
       <c r="L55" t="str">
-        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg) - Denzel Curry</v>
+        <v>Of Joy (feat. ARY) - DJ Seinfeld</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Refuge</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg)</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/refuge/1867616924</v>
+        <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-20</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G56" t="str">
-        <v>3:38</v>
+        <v>2:56</v>
       </c>
       <c r="H56" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/refuge/1867616617</v>
+        <v>https://music.apple.com/us/album/the-scythe-feat-tiacorine-a%24ap-ferg/1868519270</v>
       </c>
       <c r="L56" t="str">
-        <v>Refuge - Dermot Kennedy</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg) - Denzel Curry</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Goodbye Goodmorning</v>
+        <v>Refuge</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
+        <v>https://music.apple.com/us/song/refuge/1867616924</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-20</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>My Ego Told Me To</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G57" t="str">
-        <v>3:24</v>
+        <v>3:38</v>
       </c>
       <c r="H57" t="str">
-        <v>Leigh-Anne</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/goodbye-goodmorning/1844865923</v>
+        <v>https://music.apple.com/us/album/refuge/1867616617</v>
       </c>
       <c r="L57" t="str">
-        <v>Goodbye Goodmorning - Leigh-Anne</v>
+        <v>Refuge - Dermot Kennedy</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Smoke Screen</v>
+        <v>Goodbye Goodmorning</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
+        <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-20</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Still There’s a Glow</v>
+        <v>My Ego Told Me To</v>
       </c>
       <c r="G58" t="str">
-        <v>2:51</v>
+        <v>3:24</v>
       </c>
       <c r="H58" t="str">
-        <v>Sweet Pill</v>
+        <v>Leigh-Anne</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/smoke-screen/1851033857</v>
+        <v>https://music.apple.com/us/album/goodbye-goodmorning/1844865923</v>
       </c>
       <c r="L58" t="str">
-        <v>Smoke Screen - Sweet Pill</v>
+        <v>Goodbye Goodmorning - Leigh-Anne</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace)</v>
+        <v>Smoke Screen</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
+        <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-20</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace) - Single</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G59" t="str">
-        <v>3:21</v>
+        <v>2:51</v>
       </c>
       <c r="H59" t="str">
-        <v>ICE NINE KILLS</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/ice-nine-kills/204318665</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/twisting-the-knife-feat-mckenna-grace/1871023713</v>
+        <v>https://music.apple.com/us/album/smoke-screen/1851033857</v>
       </c>
       <c r="L59" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace) - ICE NINE KILLS</v>
+        <v>Smoke Screen - Sweet Pill</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Angel Wings</v>
+        <v>Twisting The Knife (feat. Mckenna Grace)</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
+        <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-20</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Angel Wings - Single</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>3:52</v>
+        <v>3:21</v>
       </c>
       <c r="H60" t="str">
-        <v>PRESIDENT</v>
+        <v>ICE NINE KILLS</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/ice-nine-kills/204318665</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/angel-wings/1876325893</v>
+        <v>https://music.apple.com/us/album/twisting-the-knife-feat-mckenna-grace/1871023713</v>
       </c>
       <c r="L60" t="str">
-        <v>Angel Wings - PRESIDENT</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - ICE NINE KILLS</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Roamer</v>
+        <v>Angel Wings</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/roamer/1852775825</v>
+        <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-20</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>AngieAngieAngie</v>
+        <v>Angel Wings - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>2:19</v>
+        <v>3:52</v>
       </c>
       <c r="H61" t="str">
-        <v>spill tab</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/spill-tab/1440467280</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/roamer/1852775506</v>
+        <v>https://music.apple.com/us/album/angel-wings/1876325893</v>
       </c>
       <c r="L61" t="str">
-        <v>Roamer - spill tab</v>
+        <v>Angel Wings - PRESIDENT</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>These Nights</v>
+        <v>Roamer</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/these-nights/1870989892</v>
+        <v>https://music.apple.com/us/song/roamer/1852775825</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-20</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Everything Glows</v>
+        <v>AngieAngieAngie</v>
       </c>
       <c r="G62" t="str">
-        <v>4:39</v>
+        <v>2:19</v>
       </c>
       <c r="H62" t="str">
-        <v>Cannons</v>
+        <v>spill tab</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/spill-tab/1440467280</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/these-nights/1870989672</v>
+        <v>https://music.apple.com/us/album/roamer/1852775506</v>
       </c>
       <c r="L62" t="str">
-        <v>These Nights - Cannons</v>
+        <v>Roamer - spill tab</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Locked and Loaded</v>
+        <v>These Nights</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
+        <v>https://music.apple.com/us/song/these-nights/1870989892</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-20</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Locked and Loaded - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G63" t="str">
-        <v>2:55</v>
+        <v>4:39</v>
       </c>
       <c r="H63" t="str">
-        <v>The Cab</v>
+        <v>Cannons</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/the-cab/135077748</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/locked-and-loaded/1876992433</v>
+        <v>https://music.apple.com/us/album/these-nights/1870989672</v>
       </c>
       <c r="L63" t="str">
-        <v>Locked and Loaded - The Cab</v>
+        <v>These Nights - Cannons</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Safe And Sound</v>
+        <v>Locked and Loaded</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
+        <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-20</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>EI8HT</v>
+        <v>Locked and Loaded - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>3:21</v>
+        <v>2:55</v>
       </c>
       <c r="H64" t="str">
-        <v>Shinedown</v>
+        <v>The Cab</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/the-cab/135077748</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/safe-and-sound/1877229738</v>
+        <v>https://music.apple.com/us/album/locked-and-loaded/1876992433</v>
       </c>
       <c r="L64" t="str">
-        <v>Safe And Sound - Shinedown</v>
+        <v>Locked and Loaded - The Cab</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Flinch</v>
+        <v>Safe And Sound</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/flinch/1863072401</v>
+        <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-20</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Autopilot</v>
+        <v>EI8HT</v>
       </c>
       <c r="G65" t="str">
-        <v>2:15</v>
+        <v>3:21</v>
       </c>
       <c r="H65" t="str">
-        <v>alexsucks</v>
+        <v>Shinedown</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/flinch/1863072393</v>
+        <v>https://music.apple.com/us/album/safe-and-sound/1877229738</v>
       </c>
       <c r="L65" t="str">
-        <v>Flinch - alexsucks</v>
+        <v>Safe And Sound - Shinedown</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Fall Up</v>
+        <v>Flinch</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/fall-up/1874959467</v>
+        <v>https://music.apple.com/us/song/flinch/1863072401</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-20</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Fall Up - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G66" t="str">
-        <v>3:10</v>
+        <v>2:15</v>
       </c>
       <c r="H66" t="str">
-        <v>VOILÀ</v>
+        <v>alexsucks</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/fall-up/1874959466</v>
+        <v>https://music.apple.com/us/album/flinch/1863072393</v>
       </c>
       <c r="L66" t="str">
-        <v>Fall Up - VOILÀ</v>
+        <v>Flinch - alexsucks</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>No Typo</v>
+        <v>Fall Up</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/no-typo/1872454952</v>
+        <v>https://music.apple.com/us/song/fall-up/1874959467</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-20</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Free (Deluxe)</v>
+        <v>Fall Up - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>1:43</v>
+        <v>3:10</v>
       </c>
       <c r="H67" t="str">
-        <v>Nasty C</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/no-typo/1872454582</v>
+        <v>https://music.apple.com/us/album/fall-up/1874959466</v>
       </c>
       <c r="L67" t="str">
-        <v>No Typo - Nasty C</v>
+        <v>Fall Up - VOILÀ</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Desiree</v>
+        <v>No Typo</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/desiree/1852556464</v>
+        <v>https://music.apple.com/us/song/no-typo/1872454952</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-20</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Wings of Desire</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G68" t="str">
-        <v>3:46</v>
+        <v>1:43</v>
       </c>
       <c r="H68" t="str">
-        <v>Hemi Hemingway</v>
+        <v>Nasty C</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/hemi-hemingway/1560734927</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/desiree/1852556460</v>
+        <v>https://music.apple.com/us/album/no-typo/1872454582</v>
       </c>
       <c r="L68" t="str">
-        <v>Desiree - Hemi Hemingway</v>
+        <v>No Typo - Nasty C</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Goliath (feat. Katie Jacoby)</v>
+        <v>Desiree</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
+        <v>https://music.apple.com/us/song/desiree/1852556464</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-20</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Goliath</v>
+        <v>Wings of Desire</v>
       </c>
       <c r="G69" t="str">
-        <v>5:04</v>
+        <v>3:46</v>
       </c>
       <c r="H69" t="str">
-        <v>Exodus</v>
+        <v>Hemi Hemingway</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/hemi-hemingway/1560734927</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/goliath-feat-katie-jacoby/1862225385</v>
+        <v>https://music.apple.com/us/album/desiree/1852556460</v>
       </c>
       <c r="L69" t="str">
-        <v>Goliath (feat. Katie Jacoby) - Exodus</v>
+        <v>Desiree - Hemi Hemingway</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Nomad</v>
+        <v>Goliath (feat. Katie Jacoby)</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/nomad/1843578167</v>
+        <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-20</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Loss</v>
+        <v>Goliath</v>
       </c>
       <c r="G70" t="str">
-        <v>5:30</v>
+        <v>5:04</v>
       </c>
       <c r="H70" t="str">
-        <v>Gaerea</v>
+        <v>Exodus</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/nomad/1843578156</v>
+        <v>https://music.apple.com/us/album/goliath-feat-katie-jacoby/1862225385</v>
       </c>
       <c r="L70" t="str">
-        <v>Nomad - Gaerea</v>
+        <v>Goliath (feat. Katie Jacoby) - Exodus</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Empty Words</v>
+        <v>Nomad</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/empty-words/1876625198</v>
+        <v>https://music.apple.com/us/song/nomad/1843578167</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-20</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Empty Words - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G71" t="str">
-        <v>2:32</v>
+        <v>5:30</v>
       </c>
       <c r="H71" t="str">
-        <v>Corey Kent</v>
+        <v>Gaerea</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/empty-words/1876625197</v>
+        <v>https://music.apple.com/us/album/nomad/1843578156</v>
       </c>
       <c r="L71" t="str">
-        <v>Empty Words - Corey Kent</v>
+        <v>Nomad - Gaerea</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Didn't Forget</v>
+        <v>Empty Words</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
+        <v>https://music.apple.com/us/song/empty-words/1876625198</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-20</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Didn't Forget - Single</v>
+        <v>Empty Words - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:48</v>
+        <v>2:32</v>
       </c>
       <c r="H72" t="str">
-        <v>Waylon Wyatt</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/waylon-wyatt/1713519329</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/didnt-forget/1876997982</v>
+        <v>https://music.apple.com/us/album/empty-words/1876625197</v>
       </c>
       <c r="L72" t="str">
-        <v>Didn't Forget - Waylon Wyatt</v>
+        <v>Empty Words - Corey Kent</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Euphoria</v>
+        <v>Didn't Forget</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1874295624</v>
+        <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-20</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Euphoria - Single</v>
+        <v>Didn't Forget - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>2:14</v>
+        <v>3:48</v>
       </c>
       <c r="H73" t="str">
-        <v>Bluff City</v>
+        <v>Waylon Wyatt</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/bluff-city/1491129891</v>
+        <v>https://music.apple.com/us/artist/waylon-wyatt/1713519329</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1874295623</v>
+        <v>https://music.apple.com/us/album/didnt-forget/1876997982</v>
       </c>
       <c r="L73" t="str">
-        <v>Euphoria - Bluff City</v>
+        <v>Didn't Forget - Waylon Wyatt</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>hopeless romantic</v>
+        <v>Euphoria</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
+        <v>https://music.apple.com/us/song/euphoria/1874295624</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-20</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>hopeless romantic - Single</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>3:03</v>
+        <v>2:14</v>
       </c>
       <c r="H74" t="str">
-        <v>kwn</v>
+        <v>Bluff City</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/bluff-city/1491129891</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/hopeless-romantic/1877131450</v>
+        <v>https://music.apple.com/us/album/euphoria/1874295623</v>
       </c>
       <c r="L74" t="str">
-        <v>hopeless romantic - kwn</v>
+        <v>Euphoria - Bluff City</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Stay Close</v>
+        <v>hopeless romantic</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/stay-close/1871555365</v>
+        <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-20</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Stay Close - Single</v>
+        <v>hopeless romantic - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>2:58</v>
+        <v>3:03</v>
       </c>
       <c r="H75" t="str">
-        <v>Evelyn Cormier</v>
+        <v>kwn</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/evelyn-cormier/1222282253</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/stay-close/1871555119</v>
+        <v>https://music.apple.com/us/album/hopeless-romantic/1877131450</v>
       </c>
       <c r="L75" t="str">
-        <v>Stay Close - Evelyn Cormier</v>
+        <v>hopeless romantic - kwn</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Metamorphosis</v>
+        <v>Stay Close</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
+        <v>https://music.apple.com/us/song/stay-close/1871555365</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-20</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Metamorphosis</v>
+        <v>Stay Close - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>2:54</v>
+        <v>2:58</v>
       </c>
       <c r="H76" t="str">
-        <v>lydi lynn</v>
+        <v>Evelyn Cormier</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/evelyn-cormier/1222282253</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/metamorphosis/1870994803</v>
+        <v>https://music.apple.com/us/album/stay-close/1871555119</v>
       </c>
       <c r="L76" t="str">
-        <v>Metamorphosis - lydi lynn</v>
+        <v>Stay Close - Evelyn Cormier</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>peace at last</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
+        <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-20</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>peace at last - Single</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="G77" t="str">
-        <v>2:34</v>
+        <v>2:54</v>
       </c>
       <c r="H77" t="str">
-        <v>Aaron Cole</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/peace-at-last/1870895278</v>
+        <v>https://music.apple.com/us/album/metamorphosis/1870994803</v>
       </c>
       <c r="L77" t="str">
-        <v>peace at last - Aaron Cole</v>
+        <v>Metamorphosis - lydi lynn</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Aguántame</v>
+        <v>peace at last</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
+        <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-20</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Aguántame - Single</v>
+        <v>peace at last - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>2:08</v>
+        <v>2:34</v>
       </c>
       <c r="H78" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>Aaron Cole</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/agu%C3%A1ntame/1873075917</v>
+        <v>https://music.apple.com/us/album/peace-at-last/1870895278</v>
       </c>
       <c r="L78" t="str">
-        <v>Aguántame - Banda MS de Sergio Lizárraga</v>
+        <v>peace at last - Aaron Cole</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Para No Hacernos Daño</v>
+        <v>Aguántame</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
+        <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-20</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Para No Hacernos Daño - Single</v>
+        <v>Aguántame - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>2:40</v>
+        <v>2:08</v>
       </c>
       <c r="H79" t="str">
-        <v>Codiciado</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/para-no-hacernos-da%C3%B1o/1872743927</v>
+        <v>https://music.apple.com/us/album/agu%C3%A1ntame/1873075917</v>
       </c>
       <c r="L79" t="str">
-        <v>Para No Hacernos Daño - Codiciado</v>
+        <v>Aguántame - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>NADA PERSONAL</v>
+        <v>Para No Hacernos Daño</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
+        <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-20</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>NADA PERSONAL - Single</v>
+        <v>Para No Hacernos Daño - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:11</v>
+        <v>2:40</v>
       </c>
       <c r="H80" t="str">
-        <v>La Joaqui</v>
+        <v>Codiciado</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/la-joaqui/1222726669</v>
+        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/nada-personal/1875350196</v>
+        <v>https://music.apple.com/us/album/para-no-hacernos-da%C3%B1o/1872743927</v>
       </c>
       <c r="L80" t="str">
-        <v>NADA PERSONAL - La Joaqui</v>
+        <v>Para No Hacernos Daño - Codiciado</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>V3n3n0</v>
+        <v>NADA PERSONAL</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
+        <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-20</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>V3n3n0 - Single</v>
+        <v>NADA PERSONAL - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>2:32</v>
+        <v>3:11</v>
       </c>
       <c r="H81" t="str">
-        <v>Esty</v>
+        <v>La Joaqui</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/esty/255471858</v>
+        <v>https://music.apple.com/us/artist/la-joaqui/1222726669</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/v3n3n0/1874454944</v>
+        <v>https://music.apple.com/us/album/nada-personal/1875350196</v>
       </c>
       <c r="L81" t="str">
-        <v>V3n3n0 - Esty</v>
+        <v>NADA PERSONAL - La Joaqui</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Moth In The Headlights</v>
+        <v>V3n3n0</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
+        <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-20</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Inanimate Objects of the 21st Century</v>
+        <v>V3n3n0 - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>4:23</v>
+        <v>2:32</v>
       </c>
       <c r="H82" t="str">
-        <v>The Pale White</v>
+        <v>Esty</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/the-pale-white/1127116907</v>
+        <v>https://music.apple.com/us/artist/esty/255471858</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/moth-in-the-headlights/1870538540</v>
+        <v>https://music.apple.com/us/album/v3n3n0/1874454944</v>
       </c>
       <c r="L82" t="str">
-        <v>Moth In The Headlights - The Pale White</v>
+        <v>V3n3n0 - Esty</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>lately in the void</v>
+        <v>Moth In The Headlights</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
+        <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-20</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>lately in the void - EP</v>
+        <v>Inanimate Objects of the 21st Century</v>
       </c>
       <c r="G83" t="str">
-        <v>3:41</v>
+        <v>4:23</v>
       </c>
       <c r="H83" t="str">
-        <v>bad tuner</v>
+        <v>The Pale White</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/bad-tuner/1051446214</v>
+        <v>https://music.apple.com/us/artist/the-pale-white/1127116907</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/lately-in-the-void/1847993191</v>
+        <v>https://music.apple.com/us/album/moth-in-the-headlights/1870538540</v>
       </c>
       <c r="L83" t="str">
-        <v>lately in the void - bad tuner</v>
+        <v>Moth In The Headlights - The Pale White</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>When I Fall in Love</v>
+        <v>lately in the void</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
+        <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-20</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Nightjar</v>
+        <v>lately in the void - EP</v>
       </c>
       <c r="G84" t="str">
-        <v>4:45</v>
+        <v>3:41</v>
       </c>
       <c r="H84" t="str">
-        <v>David Gray</v>
+        <v>bad tuner</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/david-gray/316381</v>
+        <v>https://music.apple.com/us/artist/bad-tuner/1051446214</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/when-i-fall-in-love/1860381106</v>
+        <v>https://music.apple.com/us/album/lately-in-the-void/1847993191</v>
       </c>
       <c r="L84" t="str">
-        <v>When I Fall in Love - David Gray</v>
+        <v>lately in the void - bad tuner</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Repeat Offender</v>
+        <v>When I Fall in Love</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
+        <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-20</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Repeat Offender - Single</v>
+        <v>Nightjar</v>
       </c>
       <c r="G85" t="str">
-        <v>2:33</v>
+        <v>4:45</v>
       </c>
       <c r="H85" t="str">
-        <v>yeemz</v>
+        <v>David Gray</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/yeemz/1561474492</v>
+        <v>https://music.apple.com/us/artist/david-gray/316381</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/repeat-offender/1873099828</v>
+        <v>https://music.apple.com/us/album/when-i-fall-in-love/1860381106</v>
       </c>
       <c r="L85" t="str">
-        <v>Repeat Offender - yeemz</v>
+        <v>When I Fall in Love - David Gray</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Class Reunion</v>
+        <v>Repeat Offender</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
+        <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-20</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>We Swallowed The Sky</v>
+        <v>Repeat Offender - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>4:11</v>
+        <v>2:33</v>
       </c>
       <c r="H86" t="str">
-        <v>Beatrix</v>
+        <v>yeemz</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/beatrix/1732651124</v>
+        <v>https://music.apple.com/us/artist/yeemz/1561474492</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/class-reunion/1876698281</v>
+        <v>https://music.apple.com/us/album/repeat-offender/1873099828</v>
       </c>
       <c r="L86" t="str">
-        <v>Class Reunion - Beatrix</v>
+        <v>Repeat Offender - yeemz</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Promise Me</v>
+        <v>Class Reunion</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/promise-me/1848977981</v>
+        <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-20</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Instant Comfort</v>
+        <v>We Swallowed The Sky</v>
       </c>
       <c r="G87" t="str">
-        <v>5:34</v>
+        <v>4:11</v>
       </c>
       <c r="H87" t="str">
-        <v>Lucid Express</v>
+        <v>Beatrix</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/lucid-express/1560683497</v>
+        <v>https://music.apple.com/us/artist/beatrix/1732651124</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/promise-me/1848977978</v>
+        <v>https://music.apple.com/us/album/class-reunion/1876698281</v>
       </c>
       <c r="L87" t="str">
-        <v>Promise Me - Lucid Express</v>
+        <v>Class Reunion - Beatrix</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions)</v>
+        <v>Promise Me</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
+        <v>https://music.apple.com/us/song/promise-me/1848977981</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-20</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Awe Mah (feat. Shakes &amp; Les, MK Productions &amp; Funky Qla) - Single</v>
+        <v>Instant Comfort</v>
       </c>
       <c r="G88" t="str">
-        <v>3:33</v>
+        <v>5:34</v>
       </c>
       <c r="H88" t="str">
-        <v>Zee Nxumalo</v>
+        <v>Lucid Express</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
+        <v>https://music.apple.com/us/artist/lucid-express/1560683497</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873675</v>
+        <v>https://music.apple.com/us/album/promise-me/1848977978</v>
       </c>
       <c r="L88" t="str">
-        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions) - Zee Nxumalo</v>
+        <v>Promise Me - Lucid Express</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Hit and Run (feat. AZ Chike)</v>
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions)</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
+        <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-20</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Hit and Run (feat. AZ Chike) - Single</v>
+        <v>Awe Mah (feat. Shakes &amp; Les, MK Productions &amp; Funky Qla) - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>3:19</v>
+        <v>3:33</v>
       </c>
       <c r="H89" t="str">
-        <v>Ray Vaughn</v>
+        <v>Zee Nxumalo</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/hit-and-run-feat-az-chike/1877912892</v>
+        <v>https://music.apple.com/us/album/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873675</v>
       </c>
       <c r="L89" t="str">
-        <v>Hit and Run (feat. AZ Chike) - Ray Vaughn</v>
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions) - Zee Nxumalo</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>So Good</v>
+        <v>Hit and Run (feat. AZ Chike)</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/so-good/1874733689</v>
+        <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-20</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>So Good - Single</v>
+        <v>Hit and Run (feat. AZ Chike) - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>2:47</v>
+        <v>3:19</v>
       </c>
       <c r="H90" t="str">
-        <v>Ari Abdul</v>
+        <v>Ray Vaughn</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/ari-abdul/1606828852</v>
+        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/so-good/1874733688</v>
+        <v>https://music.apple.com/us/album/hit-and-run-feat-az-chike/1877912892</v>
       </c>
       <c r="L90" t="str">
-        <v>So Good - Ari Abdul</v>
+        <v>Hit and Run (feat. AZ Chike) - Ray Vaughn</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>YDH</v>
+        <v>So Good</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/ydh/1874940744</v>
+        <v>https://music.apple.com/us/song/so-good/1874733689</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-20</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>YDH - Single</v>
+        <v>So Good - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>3:17</v>
+        <v>2:47</v>
       </c>
       <c r="H91" t="str">
-        <v>Chloe Qisha</v>
+        <v>Ari Abdul</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
+        <v>https://music.apple.com/us/artist/ari-abdul/1606828852</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/ydh/1874940739</v>
+        <v>https://music.apple.com/us/album/so-good/1874733688</v>
       </c>
       <c r="L91" t="str">
-        <v>YDH - Chloe Qisha</v>
+        <v>So Good - Ari Abdul</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Eucalyptus</v>
+        <v>YDH</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
+        <v>https://music.apple.com/us/song/ydh/1874940744</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-20</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Porcelain</v>
+        <v>YDH - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>3:00</v>
+        <v>3:17</v>
       </c>
       <c r="H92" t="str">
-        <v>Peach PRC</v>
+        <v>Chloe Qisha</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
+        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/eucalyptus/1861380240</v>
+        <v>https://music.apple.com/us/album/ydh/1874940739</v>
       </c>
       <c r="L92" t="str">
-        <v>Eucalyptus - Peach PRC</v>
+        <v>YDH - Chloe Qisha</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Pearls In The Trap</v>
+        <v>Eucalyptus</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
+        <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-20</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Pearls In The Trap - Single</v>
+        <v>Porcelain</v>
       </c>
       <c r="G93" t="str">
-        <v>1:38</v>
+        <v>3:00</v>
       </c>
       <c r="H93" t="str">
-        <v>carolesdaughter</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/carolesdaughter/1502564996</v>
+        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/pearls-in-the-trap/1877892476</v>
+        <v>https://music.apple.com/us/album/eucalyptus/1861380240</v>
       </c>
       <c r="L93" t="str">
-        <v>Pearls In The Trap - carolesdaughter</v>
+        <v>Eucalyptus - Peach PRC</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>The Fever Mask</v>
+        <v>Pearls In The Trap</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
+        <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-20</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>Pearls In The Trap - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>3:12</v>
+        <v>1:38</v>
       </c>
       <c r="H94" t="str">
-        <v>At The Gates</v>
+        <v>carolesdaughter</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/carolesdaughter/1502564996</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/the-fever-mask/1873364809</v>
+        <v>https://music.apple.com/us/album/pearls-in-the-trap/1877892476</v>
       </c>
       <c r="L94" t="str">
-        <v>The Fever Mask - At The Gates</v>
+        <v>Pearls In The Trap - carolesdaughter</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>The Air's on Fire</v>
+        <v>The Fever Mask</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
+        <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-20</v>
@@ -3985,68 +3985,106 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Location Lost</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G95" t="str">
-        <v>5:15</v>
+        <v>3:12</v>
       </c>
       <c r="H95" t="str">
-        <v>Failure</v>
+        <v>At The Gates</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/failure/1646309</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/the-airs-on-fire/1867015665</v>
+        <v>https://music.apple.com/us/album/the-fever-mask/1873364809</v>
       </c>
       <c r="L95" t="str">
-        <v>The Air's on Fire - Failure</v>
+        <v>The Fever Mask - At The Gates</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
+        <v>The Air's on Fire</v>
+      </c>
+      <c r="B96" t="str">
+        <v/>
+      </c>
+      <c r="C96" t="str">
+        <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
+      </c>
+      <c r="D96" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v>Location Lost</v>
+      </c>
+      <c r="G96" t="str">
+        <v>5:15</v>
+      </c>
+      <c r="H96" t="str">
+        <v>Failure</v>
+      </c>
+      <c r="I96" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J96" t="str">
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
+      </c>
+      <c r="K96" t="str">
+        <v>https://music.apple.com/us/album/the-airs-on-fire/1867015665</v>
+      </c>
+      <c r="L96" t="str">
+        <v>The Air's on Fire - Failure</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
         <v>To The Last Breath</v>
       </c>
-      <c r="B96" t="str">
-        <v/>
-      </c>
-      <c r="C96" t="str">
+      <c r="B97" t="str">
+        <v/>
+      </c>
+      <c r="C97" t="str">
         <v>https://music.apple.com/us/song/to-the-last-breath/1874618974</v>
       </c>
-      <c r="D96" t="str">
-        <v>2026-02-20</v>
-      </c>
-      <c r="E96" t="str">
-        <v/>
-      </c>
-      <c r="F96" t="str">
+      <c r="D97" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
         <v>To The Last Breath - Single</v>
       </c>
-      <c r="G96" t="str">
+      <c r="G97" t="str">
         <v>4:57</v>
       </c>
-      <c r="H96" t="str">
+      <c r="H97" t="str">
         <v>Arch Enemy</v>
       </c>
-      <c r="I96" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J96" t="str">
+      <c r="I97" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J97" t="str">
         <v>https://music.apple.com/us/artist/arch-enemy/18098340</v>
       </c>
-      <c r="K96" t="str">
+      <c r="K97" t="str">
         <v>https://music.apple.com/us/album/to-the-last-breath/1874618973</v>
       </c>
-      <c r="L96" t="str">
+      <c r="L97" t="str">
         <v>To The Last Breath - Arch Enemy</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L96"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L97"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-02-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/badlands/1848218132</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/opalite-chris-lake-remix/1878187199</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/rosita/1877264687</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/good-flirts-feat-kendrick-lamar-momo-boyd/1878400231</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/save-the-day-from-hoppers/1877213780</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/medicine/1851297056</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/weather-for-tennis/1854567104</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/ear-to-the-cocoon/1872767745</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/drag-path/1876977596</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/song-of-the-future/1875348244</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/your-favorite-toy/1877913734</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/trimski/1876695030</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/paracosm/1869706756</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/iris-live-from-apple-music-studios/1877215177</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/begging-for-change/1870313832</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/my-maker/1862845748</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/opalite-bunt-remix/1878183696</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/such-great-heights-from-tell-me-lies-season-3/1872222695</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/she-knows-too-much/1861531670</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/tea-time/1877002914</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/full-moon-fall-in-tokyo-bonus-track/1877180113</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/save-my-love/1876235280</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/forever-tu-gantel/1877482427</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/suburban-requiem/1874720791</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/good-grief/1869516030</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/freak-on/1874265564</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/science-feat-stevie-appleton-radio-edit/1871036143</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/opalite-skream-remix/1878173708</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/beautiful-places/1876326643</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/stampede/1868995802</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/infinite-beach/1858554535</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/championship-ring/1875186768</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/bully/1874401861</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/ride/1869414360</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/migajero/1873051149</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/old-man/1872189176</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/refuge/1867616924</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/roamer/1852775825</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/these-nights/1870989892</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/flinch/1863072401</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/fall-up/1874959467</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/no-typo/1872454952</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/desiree/1852556464</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/nomad/1843578167</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/empty-words/1876625198</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/euphoria/1874295624</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/stay-close/1871555365</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/promise-me/1848977981</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/so-good/1874733689</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/ydh/1874940744</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/to-the-last-breath/1874618974</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E97" t="str">
         <v/>
